--- a/google-sheet/3_SPARE_SHEET_WordNest_Sync.xlsx
+++ b/google-sheet/3_SPARE_SHEET_WordNest_Sync.xlsx
@@ -1692,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T277"/>
+  <dimension ref="A1:T324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.42857142857143" customWidth="1" min="1" max="1"/>
@@ -20812,61 +20812,61 @@
     <row r="213">
       <c r="A213" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B213" s="34" t="inlineStr">
         <is>
-          <t>authenticate</t>
+          <t>active listening</t>
         </is>
       </c>
       <c r="C213" s="35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D213" s="14" t="inlineStr">
         <is>
-          <t>To prove who you are, for example with a code or password.</t>
+          <t>Listening fully, then showing you understood, for example by repeating the key points.</t>
         </is>
       </c>
       <c r="E213" s="14" t="inlineStr">
         <is>
-          <t>aw-THEN-ti-kayt</t>
+          <t>AK-tiv LIS-ning</t>
         </is>
       </c>
       <c r="F213" s="14" t="inlineStr">
         <is>
-          <t>/ɔːˈθentɪkeɪt/</t>
+          <t>/ˈæktɪv ˈlɪsnɪŋ/</t>
         </is>
       </c>
       <c r="G213" s="14" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H213" s="14" t="inlineStr">
         <is>
-          <t>He authenticated his account using Google.</t>
+          <t>Active listening helped me find the real problem.</t>
         </is>
       </c>
       <c r="I213" s="14" t="inlineStr">
         <is>
-          <t>Users authenticate with a code sent to their phone.</t>
+          <t>Active listening means you don't interrupt.</t>
         </is>
       </c>
       <c r="J213" s="14" t="inlineStr">
         <is>
-          <t>You will need to authenticate again after the update.</t>
+          <t>Active listening will make customers feel heard.</t>
         </is>
       </c>
       <c r="K213" s="14" t="inlineStr"/>
       <c r="L213" s="36" t="inlineStr">
         <is>
-          <t>प्रमाणित करना</t>
+          <t>सक्रिय रूप से सुनना</t>
         </is>
       </c>
       <c r="M213" s="36" t="inlineStr">
         <is>
-          <t>साबित करना कि आप वही हैं जो आप कहते हैं, जैसे कोड या पासवर्ड से।</t>
+          <t>पूरे ध्यान से सुनना और दिखाना कि आपने समझा, जैसे मुख्य बातें दोहराना।</t>
         </is>
       </c>
       <c r="N213" s="37" t="inlineStr">
@@ -20890,42 +20890,42 @@
       <c r="R213" s="37" t="inlineStr"/>
       <c r="S213" s="39" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T213" s="39" t="inlineStr">
         <is>
-          <t>s:authenticate</t>
+          <t>s:active-listening</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B214" s="34" t="inlineStr">
         <is>
-          <t>bug report</t>
+          <t>AI fluency</t>
         </is>
       </c>
       <c r="C214" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D214" s="14" t="inlineStr">
         <is>
-          <t>A message telling the tech team about a problem in the product.</t>
+          <t>The skill of using AI well, safely and with good judgment.</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
         <is>
-          <t>bug ri-PORT</t>
+          <t>ay EYE FLOO-un-see</t>
         </is>
       </c>
       <c r="F214" s="14" t="inlineStr">
         <is>
-          <t>/bʌɡ rɪˈpɔːt/</t>
+          <t>/ˌeɪ ˈaɪ ˈfluːənsi/</t>
         </is>
       </c>
       <c r="G214" s="14" t="inlineStr">
@@ -20935,28 +20935,28 @@
       </c>
       <c r="H214" s="14" t="inlineStr">
         <is>
-          <t>I filed a bug report this morning.</t>
+          <t>Her AI fluency improved after the course.</t>
         </is>
       </c>
       <c r="I214" s="14" t="inlineStr">
         <is>
-          <t>A good bug report has clear steps.</t>
+          <t>AI fluency is part of our training.</t>
         </is>
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>The team will read your bug report today.</t>
+          <t>AI fluency will be a key skill for agents.</t>
         </is>
       </c>
       <c r="K214" s="14" t="inlineStr"/>
       <c r="L214" s="36" t="inlineStr">
         <is>
-          <t>बग रिपोर्ट, गड़बड़ी की रिपोर्ट</t>
+          <t>AI में दक्षता</t>
         </is>
       </c>
       <c r="M214" s="36" t="inlineStr">
         <is>
-          <t>प्रोडक्ट की समस्या के बारे में टेक टीम को भेजा गया संदेश।</t>
+          <t>AI को अच्छे से, सुरक्षित और समझदारी से इस्तेमाल करने का कौशल।</t>
         </is>
       </c>
       <c r="N214" s="37" t="inlineStr">
@@ -20980,73 +20980,73 @@
       <c r="R214" s="37" t="inlineStr"/>
       <c r="S214" s="39" t="inlineStr">
         <is>
-          <t>tech,cs</t>
+          <t>training,ai,cs</t>
         </is>
       </c>
       <c r="T214" s="39" t="inlineStr">
         <is>
-          <t>s:bug-report</t>
+          <t>s:ai-fluency</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B215" s="34" t="inlineStr">
         <is>
-          <t>clear the cache</t>
+          <t>AI winter</t>
         </is>
       </c>
       <c r="C215" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D215" s="14" t="inlineStr">
         <is>
-          <t>To delete saved website data so a page loads fresh.</t>
+          <t>A period when AI funding and interest dropped after big promises were not met.</t>
         </is>
       </c>
       <c r="E215" s="14" t="inlineStr">
         <is>
-          <t>kleer thuh KASH</t>
+          <t>ay EYE WIN-ter</t>
         </is>
       </c>
       <c r="F215" s="14" t="inlineStr">
         <is>
-          <t>/klɪə ðə kæʃ/</t>
+          <t>/ˌeɪ ˈaɪ ˈwɪntə/</t>
         </is>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H215" s="14" t="inlineStr">
         <is>
-          <t>She cleared the cache and it worked.</t>
+          <t>The first AI winter came in the mid-1970s.</t>
         </is>
       </c>
       <c r="I215" s="14" t="inlineStr">
         <is>
-          <t>Try to clear the cache and reload the page.</t>
+          <t>An AI winter can follow too much hype.</t>
         </is>
       </c>
       <c r="J215" s="14" t="inlineStr">
         <is>
-          <t>You will need to clear the cache after the update.</t>
+          <t>Some fear another AI winter will come.</t>
         </is>
       </c>
       <c r="K215" s="14" t="inlineStr"/>
       <c r="L215" s="36" t="inlineStr">
         <is>
-          <t>कैश साफ़ करना</t>
+          <t>AI विंटर (मंदी का दौर)</t>
         </is>
       </c>
       <c r="M215" s="36" t="inlineStr">
         <is>
-          <t>ब्राउज़र में सेव डेटा हटाना ताकि पेज नए सिरे से खुले।</t>
+          <t>वह दौर जब बड़े वादे पूरे न होने पर AI में निवेश और रुचि घट गई।</t>
         </is>
       </c>
       <c r="N215" s="37" t="inlineStr">
@@ -21070,42 +21070,42 @@
       <c r="R215" s="37" t="inlineStr"/>
       <c r="S215" s="39" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T215" s="39" t="inlineStr">
         <is>
-          <t>s:clear-the-cache</t>
+          <t>s:ai-winter</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B216" s="34" t="inlineStr">
         <is>
-          <t>credentials</t>
+          <t>artificial general intelligence</t>
         </is>
       </c>
       <c r="C216" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D216" s="14" t="inlineStr">
         <is>
-          <t>Login details like your email and password.</t>
+          <t>AI that could learn and reason like a human in any field. It does not exist yet. Often called AGI.</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
         <is>
-          <t>kruh-DEN-shulz</t>
+          <t>ar-ti-FISH-ul JEN-ruhl in-TEL-i-juns</t>
         </is>
       </c>
       <c r="F216" s="14" t="inlineStr">
         <is>
-          <t>/krəˈdenʃlz/</t>
+          <t>/ˌɑːtɪfɪʃl ˈdʒenrəl ɪnˈtelɪdʒəns/</t>
         </is>
       </c>
       <c r="G216" s="14" t="inlineStr">
@@ -21115,28 +21115,28 @@
       </c>
       <c r="H216" s="14" t="inlineStr">
         <is>
-          <t>She entered the wrong credentials three times.</t>
+          <t>Experts discussed artificial general intelligence in the 1960s too.</t>
         </is>
       </c>
       <c r="I216" s="14" t="inlineStr">
         <is>
-          <t>Never share your credentials with anyone.</t>
+          <t>Artificial general intelligence is still only a theory.</t>
         </is>
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>You will get new credentials by email.</t>
+          <t>Nobody knows when artificial general intelligence will arrive.</t>
         </is>
       </c>
       <c r="K216" s="14" t="inlineStr"/>
       <c r="L216" s="36" t="inlineStr">
         <is>
-          <t>लॉगिन विवरण</t>
+          <t>सामान्य कृत्रिम बुद्धिमत्ता (AGI)</t>
         </is>
       </c>
       <c r="M216" s="36" t="inlineStr">
         <is>
-          <t>लॉगिन करने की जानकारी, जैसे ईमेल और पासवर्ड।</t>
+          <t>ऐसी AI जो किसी भी क्षेत्र में इंसान की तरह सीख और सोच सके; यह अभी मौजूद नहीं है।</t>
         </is>
       </c>
       <c r="N216" s="37" t="inlineStr">
@@ -21160,42 +21160,42 @@
       <c r="R216" s="37" t="inlineStr"/>
       <c r="S216" s="39" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>training,ai</t>
         </is>
       </c>
       <c r="T216" s="39" t="inlineStr">
         <is>
-          <t>s:credentials</t>
+          <t>s:artificial-general-intelligence</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B217" s="34" t="inlineStr">
         <is>
-          <t>data privacy</t>
+          <t>artificial intelligence</t>
         </is>
       </c>
       <c r="C217" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D217" s="14" t="inlineStr">
         <is>
-          <t>Keeping people's personal information safe and private.</t>
+          <t>Computer systems that learn from data to do tasks that usually need human thinking.</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
         <is>
-          <t>DAY-tuh PRIV-uh-see</t>
+          <t>ar-ti-FISH-ul in-TEL-i-juns</t>
         </is>
       </c>
       <c r="F217" s="14" t="inlineStr">
         <is>
-          <t>/ˈdeɪtə ˈprɪvəsi/</t>
+          <t>/ˌɑːtɪfɪʃl ɪnˈtelɪdʒəns/</t>
         </is>
       </c>
       <c r="G217" s="14" t="inlineStr">
@@ -21205,28 +21205,28 @@
       </c>
       <c r="H217" s="14" t="inlineStr">
         <is>
-          <t>The training covered data privacy.</t>
+          <t>The term artificial intelligence was first used in 1956.</t>
         </is>
       </c>
       <c r="I217" s="14" t="inlineStr">
         <is>
-          <t>Data privacy rules are strict in Europe.</t>
+          <t>Artificial intelligence helps us answer simple questions faster.</t>
         </is>
       </c>
       <c r="J217" s="14" t="inlineStr">
         <is>
-          <t>We will never break data privacy rules.</t>
+          <t>Artificial intelligence will keep changing customer service.</t>
         </is>
       </c>
       <c r="K217" s="14" t="inlineStr"/>
       <c r="L217" s="36" t="inlineStr">
         <is>
-          <t>डेटा गोपनीयता</t>
+          <t>कृत्रिम बुद्धिमत्ता</t>
         </is>
       </c>
       <c r="M217" s="36" t="inlineStr">
         <is>
-          <t>लोगों की निजी जानकारी को सुरक्षित और गोपनीय रखना।</t>
+          <t>कंप्यूटर सिस्टम जो डेटा से सीखकर ऐसे काम करते हैं जिनमें आम तौर पर इंसानी सोच लगती है।</t>
         </is>
       </c>
       <c r="N217" s="37" t="inlineStr">
@@ -21250,24 +21250,24 @@
       <c r="R217" s="37" t="inlineStr"/>
       <c r="S217" s="39" t="inlineStr">
         <is>
-          <t>tech,corp</t>
+          <t>training,ai</t>
         </is>
       </c>
       <c r="T217" s="39" t="inlineStr">
         <is>
-          <t>s:data-privacy</t>
+          <t>s:artificial-intelligence</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B218" s="34" t="inlineStr">
         <is>
-          <t>deactivate</t>
+          <t>bias</t>
         </is>
       </c>
       <c r="C218" s="35" t="n">
@@ -21275,48 +21275,48 @@
       </c>
       <c r="D218" s="14" t="inlineStr">
         <is>
-          <t>To turn off an account or feature.</t>
+          <t>An unfair leaning for or against someone or something.</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
         <is>
-          <t>dee-AK-ti-vayt</t>
+          <t>BY-us</t>
         </is>
       </c>
       <c r="F218" s="14" t="inlineStr">
         <is>
-          <t>/diˈæktɪveɪt/</t>
+          <t>/ˈbaɪəs/</t>
         </is>
       </c>
       <c r="G218" s="14" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H218" s="14" t="inlineStr">
         <is>
-          <t>She deactivated the old account.</t>
+          <t>We found bias in the old test questions.</t>
         </is>
       </c>
       <c r="I218" s="14" t="inlineStr">
         <is>
-          <t>You can deactivate your account in settings.</t>
+          <t>AI can show bias from its training data.</t>
         </is>
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>We will deactivate the feature tonight.</t>
+          <t>Careful review will reduce bias.</t>
         </is>
       </c>
       <c r="K218" s="14" t="inlineStr"/>
       <c r="L218" s="36" t="inlineStr">
         <is>
-          <t>निष्क्रिय करना</t>
+          <t>पक्षपात</t>
         </is>
       </c>
       <c r="M218" s="36" t="inlineStr">
         <is>
-          <t>किसी खाते या फीचर को बंद करना।</t>
+          <t>किसी के पक्ष या विरोध में अनुचित झुकाव।</t>
         </is>
       </c>
       <c r="N218" s="37" t="inlineStr">
@@ -21340,24 +21340,24 @@
       <c r="R218" s="37" t="inlineStr"/>
       <c r="S218" s="39" t="inlineStr">
         <is>
-          <t>tech,cs</t>
+          <t>training,ai,cs</t>
         </is>
       </c>
       <c r="T218" s="39" t="inlineStr">
         <is>
-          <t>s:deactivate</t>
+          <t>s:bias</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B219" s="34" t="inlineStr">
         <is>
-          <t>deprecate</t>
+          <t>chain of thought</t>
         </is>
       </c>
       <c r="C219" s="35" t="n">
@@ -21365,48 +21365,48 @@
       </c>
       <c r="D219" s="14" t="inlineStr">
         <is>
-          <t>To mark an old feature as no longer supported.</t>
+          <t>Working through a problem one step at a time before giving the answer.</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>DEP-ruh-kayt</t>
+          <t>chayn uv THAWT</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
         <is>
-          <t>/ˈdeprəkeɪt/</t>
+          <t>/tʃeɪn əv θɔːt/</t>
         </is>
       </c>
       <c r="G219" s="14" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H219" s="14" t="inlineStr">
         <is>
-          <t>They deprecated the old API last year.</t>
+          <t>The trainer showed chain of thought with a maths example.</t>
         </is>
       </c>
       <c r="I219" s="14" t="inlineStr">
         <is>
-          <t>The company deprecates old models over time.</t>
+          <t>Chain of thought helps the model avoid mistakes.</t>
         </is>
       </c>
       <c r="J219" s="14" t="inlineStr">
         <is>
-          <t>This feature will be deprecated in March.</t>
+          <t>Chain of thought will make the answer slower but better.</t>
         </is>
       </c>
       <c r="K219" s="14" t="inlineStr"/>
       <c r="L219" s="36" t="inlineStr">
         <is>
-          <t>बंद करने के लिए चिह्नित करना</t>
+          <t>विचारों की कड़ी</t>
         </is>
       </c>
       <c r="M219" s="36" t="inlineStr">
         <is>
-          <t>किसी पुराने फीचर को धीरे-धीरे बंद करने की घोषणा करना।</t>
+          <t>जवाब देने से पहले समस्या को एक-एक कदम करके सुलझाना।</t>
         </is>
       </c>
       <c r="N219" s="37" t="inlineStr">
@@ -21430,73 +21430,73 @@
       <c r="R219" s="37" t="inlineStr"/>
       <c r="S219" s="39" t="inlineStr">
         <is>
-          <t>tech,ai</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T219" s="39" t="inlineStr">
         <is>
-          <t>s:deprecate</t>
+          <t>s:chain-of-thought</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B220" s="34" t="inlineStr">
         <is>
-          <t>error message</t>
+          <t>coin a term</t>
         </is>
       </c>
       <c r="C220" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D220" s="14" t="inlineStr">
         <is>
-          <t>Text on the screen that says something went wrong.</t>
+          <t>To invent a new word or phrase that people start using.</t>
         </is>
       </c>
       <c r="E220" s="14" t="inlineStr">
         <is>
-          <t>ER-er MES-ij</t>
+          <t>koyn uh TURM</t>
         </is>
       </c>
       <c r="F220" s="14" t="inlineStr">
         <is>
-          <t>/ˈerə ˈmesɪdʒ/</t>
+          <t>/kɔɪn ə tɜːm/</t>
         </is>
       </c>
       <c r="G220" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="H220" s="14" t="inlineStr">
         <is>
-          <t>The error message appeared after login.</t>
+          <t>John McCarthy coined the term artificial intelligence in 1956.</t>
         </is>
       </c>
       <c r="I220" s="14" t="inlineStr">
         <is>
-          <t>What does the error message say?</t>
+          <t>Researchers often coin a term for a new idea.</t>
         </is>
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>The fix will remove this error message.</t>
+          <t>Someone will coin a term for this trend soon.</t>
         </is>
       </c>
       <c r="K220" s="14" t="inlineStr"/>
       <c r="L220" s="36" t="inlineStr">
         <is>
-          <t>त्रुटि संदेश</t>
+          <t>नया शब्द गढ़ना</t>
         </is>
       </c>
       <c r="M220" s="36" t="inlineStr">
         <is>
-          <t>स्क्रीन पर दिखने वाला संदेश कि कुछ गलत हुआ है।</t>
+          <t>कोई नया शब्द या वाक्यांश बनाना जिसे लोग इस्तेमाल करने लगें।</t>
         </is>
       </c>
       <c r="N220" s="37" t="inlineStr">
@@ -21520,42 +21520,42 @@
       <c r="R220" s="37" t="inlineStr"/>
       <c r="S220" s="39" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T220" s="39" t="inlineStr">
         <is>
-          <t>s:error-message</t>
+          <t>s:coin-a-term</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B221" s="34" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>composure</t>
         </is>
       </c>
       <c r="C221" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D221" s="14" t="inlineStr">
         <is>
-          <t>A customer's idea for something new the product should do.</t>
+          <t>Staying calm and in control, even under pressure.</t>
         </is>
       </c>
       <c r="E221" s="14" t="inlineStr">
         <is>
-          <t>FEE-cher ri-KWEST</t>
+          <t>kum-POH-zher</t>
         </is>
       </c>
       <c r="F221" s="14" t="inlineStr">
         <is>
-          <t>/ˈfiːtʃə rɪˈkwest/</t>
+          <t>/kəmˈpəʊʒə/</t>
         </is>
       </c>
       <c r="G221" s="14" t="inlineStr">
@@ -21565,28 +21565,28 @@
       </c>
       <c r="H221" s="14" t="inlineStr">
         <is>
-          <t>I logged his feature request for the product team.</t>
+          <t>He lost his composure for a moment.</t>
         </is>
       </c>
       <c r="I221" s="14" t="inlineStr">
         <is>
-          <t>Many users send the same feature request.</t>
+          <t>She keeps her composure on difficult calls.</t>
         </is>
       </c>
       <c r="J221" s="14" t="inlineStr">
         <is>
-          <t>The product team will review feature requests in June.</t>
+          <t>Deep breaths will help you keep your composure.</t>
         </is>
       </c>
       <c r="K221" s="14" t="inlineStr"/>
       <c r="L221" s="36" t="inlineStr">
         <is>
-          <t>नई सुविधा का अनुरोध</t>
+          <t>धैर्य, संयम</t>
         </is>
       </c>
       <c r="M221" s="36" t="inlineStr">
         <is>
-          <t>ग्राहक का सुझाव कि प्रोडक्ट में कोई नई चीज़ जोड़ी जाए।</t>
+          <t>दबाव में भी शांत और नियंत्रण में रहना।</t>
         </is>
       </c>
       <c r="N221" s="37" t="inlineStr">
@@ -21610,42 +21610,42 @@
       <c r="R221" s="37" t="inlineStr"/>
       <c r="S221" s="39" t="inlineStr">
         <is>
-          <t>tech,cs</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T221" s="39" t="inlineStr">
         <is>
-          <t>s:feature-request</t>
+          <t>s:composure</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B222" s="34" t="inlineStr">
         <is>
-          <t>glitch</t>
+          <t>conflict resolution</t>
         </is>
       </c>
       <c r="C222" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D222" s="14" t="inlineStr">
         <is>
-          <t>A small, short problem in a system.</t>
+          <t>Finding a fair way to end a disagreement.</t>
         </is>
       </c>
       <c r="E222" s="14" t="inlineStr">
         <is>
-          <t>glich</t>
+          <t>KON-flikt rez-uh-LOO-shun</t>
         </is>
       </c>
       <c r="F222" s="14" t="inlineStr">
         <is>
-          <t>/ɡlɪtʃ/</t>
+          <t>/ˈkɒnflɪkt ˌrezəˈluːʃn/</t>
         </is>
       </c>
       <c r="G222" s="14" t="inlineStr">
@@ -21655,28 +21655,28 @@
       </c>
       <c r="H222" s="14" t="inlineStr">
         <is>
-          <t>The glitch stopped after the restart.</t>
+          <t>The team lead handled the conflict resolution calmly.</t>
         </is>
       </c>
       <c r="I222" s="14" t="inlineStr">
         <is>
-          <t>A glitch sometimes logs users out.</t>
+          <t>Conflict resolution starts with listening to both sides.</t>
         </is>
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>This glitch will be fixed in the next update.</t>
+          <t>Conflict resolution training will start next week.</t>
         </is>
       </c>
       <c r="K222" s="14" t="inlineStr"/>
       <c r="L222" s="36" t="inlineStr">
         <is>
-          <t>छोटी तकनीकी गड़बड़ी</t>
+          <t>विवाद समाधान</t>
         </is>
       </c>
       <c r="M222" s="36" t="inlineStr">
         <is>
-          <t>सिस्टम में थोड़ी देर की छोटी खराबी।</t>
+          <t>किसी मतभेद को निष्पक्ष तरीके से खत्म करना।</t>
         </is>
       </c>
       <c r="N222" s="37" t="inlineStr">
@@ -21700,42 +21700,42 @@
       <c r="R222" s="37" t="inlineStr"/>
       <c r="S222" s="39" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T222" s="39" t="inlineStr">
         <is>
-          <t>s:glitch</t>
+          <t>s:conflict-resolution</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B223" s="34" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>cost-efficient</t>
         </is>
       </c>
       <c r="C223" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D223" s="14" t="inlineStr">
         <is>
-          <t>Stopping and starting again, not happening all the time.</t>
+          <t>Giving good results without spending much.</t>
         </is>
       </c>
       <c r="E223" s="14" t="inlineStr">
         <is>
-          <t>in-ter-MIT-unt</t>
+          <t>kost i-FISH-unt</t>
         </is>
       </c>
       <c r="F223" s="14" t="inlineStr">
         <is>
-          <t>/ˌɪntəˈmɪtənt/</t>
+          <t>/kɒst ɪˈfɪʃnt/</t>
         </is>
       </c>
       <c r="G223" s="14" t="inlineStr">
@@ -21745,28 +21745,28 @@
       </c>
       <c r="H223" s="14" t="inlineStr">
         <is>
-          <t>The errors were intermittent all morning.</t>
+          <t>The smaller model was more cost-efficient.</t>
         </is>
       </c>
       <c r="I223" s="14" t="inlineStr">
         <is>
-          <t>The user has intermittent connection problems.</t>
+          <t>GPT-4o mini is cost-efficient for simple tasks.</t>
         </is>
       </c>
       <c r="J223" s="14" t="inlineStr">
         <is>
-          <t>Intermittent issues will be harder to track.</t>
+          <t>A cost-efficient model will handle high volumes.</t>
         </is>
       </c>
       <c r="K223" s="14" t="inlineStr"/>
       <c r="L223" s="36" t="inlineStr">
         <is>
-          <t>रुक-रुककर होने वाला</t>
+          <t>किफ़ायती</t>
         </is>
       </c>
       <c r="M223" s="36" t="inlineStr">
         <is>
-          <t>जो लगातार न होकर बीच-बीच में होता है।</t>
+          <t>कम खर्च में अच्छा नतीजा देने वाला।</t>
         </is>
       </c>
       <c r="N223" s="37" t="inlineStr">
@@ -21790,24 +21790,24 @@
       <c r="R223" s="37" t="inlineStr"/>
       <c r="S223" s="39" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T223" s="39" t="inlineStr">
         <is>
-          <t>s:intermittent</t>
+          <t>s:cost-efficient</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B224" s="34" t="inlineStr">
         <is>
-          <t>latency</t>
+          <t>deep learning</t>
         </is>
       </c>
       <c r="C224" s="35" t="n">
@@ -21815,17 +21815,17 @@
       </c>
       <c r="D224" s="14" t="inlineStr">
         <is>
-          <t>The delay before a system responds.</t>
+          <t>Machine learning that uses large neural networks with many layers.</t>
         </is>
       </c>
       <c r="E224" s="14" t="inlineStr">
         <is>
-          <t>LAY-tun-see</t>
+          <t>deep LUR-ning</t>
         </is>
       </c>
       <c r="F224" s="14" t="inlineStr">
         <is>
-          <t>/ˈleɪtənsi/</t>
+          <t>/diːp ˈlɜːnɪŋ/</t>
         </is>
       </c>
       <c r="G224" s="14" t="inlineStr">
@@ -21835,28 +21835,28 @@
       </c>
       <c r="H224" s="14" t="inlineStr">
         <is>
-          <t>Latency was higher during the update.</t>
+          <t>Deep learning made voice assistants much better.</t>
         </is>
       </c>
       <c r="I224" s="14" t="inlineStr">
         <is>
-          <t>High latency makes the chat feel slow.</t>
+          <t>Deep learning needs a lot of data.</t>
         </is>
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>The fix will reduce latency.</t>
+          <t>Deep learning will keep improving image tools.</t>
         </is>
       </c>
       <c r="K224" s="14" t="inlineStr"/>
       <c r="L224" s="36" t="inlineStr">
         <is>
-          <t>विलंब, देरी</t>
+          <t>डीप लर्निंग</t>
         </is>
       </c>
       <c r="M224" s="36" t="inlineStr">
         <is>
-          <t>सिस्टम के जवाब देने से पहले होने वाली देरी।</t>
+          <t>मशीन लर्निंग जो कई परतों वाले बड़े न्यूरल नेटवर्क इस्तेमाल करती है।</t>
         </is>
       </c>
       <c r="N224" s="37" t="inlineStr">
@@ -21880,42 +21880,42 @@
       <c r="R224" s="37" t="inlineStr"/>
       <c r="S224" s="39" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T224" s="39" t="inlineStr">
         <is>
-          <t>s:latency</t>
+          <t>s:deep-learning</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B225" s="34" t="inlineStr">
         <is>
-          <t>limitation</t>
+          <t>delegation</t>
         </is>
       </c>
       <c r="C225" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D225" s="14" t="inlineStr">
         <is>
-          <t>Something a product or person cannot do.</t>
+          <t>Deciding which tasks to hand to AI or to others, and which to do yourself.</t>
         </is>
       </c>
       <c r="E225" s="14" t="inlineStr">
         <is>
-          <t>lim-i-TAY-shun</t>
+          <t>del-i-GAY-shun</t>
         </is>
       </c>
       <c r="F225" s="14" t="inlineStr">
         <is>
-          <t>/ˌlɪmɪˈteɪʃn/</t>
+          <t>/ˌdelɪˈɡeɪʃn/</t>
         </is>
       </c>
       <c r="G225" s="14" t="inlineStr">
@@ -21925,28 +21925,28 @@
       </c>
       <c r="H225" s="14" t="inlineStr">
         <is>
-          <t>We explained the limitation to the user.</t>
+          <t>Good delegation saved me an hour yesterday.</t>
         </is>
       </c>
       <c r="I225" s="14" t="inlineStr">
         <is>
-          <t>This is a known limitation of the model.</t>
+          <t>Delegation means AI drafts and I check.</t>
         </is>
       </c>
       <c r="J225" s="14" t="inlineStr">
         <is>
-          <t>The new version will remove this limitation.</t>
+          <t>Delegation will free up time for hard cases.</t>
         </is>
       </c>
       <c r="K225" s="14" t="inlineStr"/>
       <c r="L225" s="36" t="inlineStr">
         <is>
-          <t>सीमा, कमी</t>
+          <t>काम सौंपना</t>
         </is>
       </c>
       <c r="M225" s="36" t="inlineStr">
         <is>
-          <t>कोई चीज़ जो प्रोडक्ट या व्यक्ति नहीं कर सकता।</t>
+          <t>तय करना कि कौन से काम AI या दूसरों को देने हैं और कौन से खुद करने हैं।</t>
         </is>
       </c>
       <c r="N225" s="37" t="inlineStr">
@@ -21970,42 +21970,42 @@
       <c r="R225" s="37" t="inlineStr"/>
       <c r="S225" s="39" t="inlineStr">
         <is>
-          <t>tech,ai</t>
+          <t>training,ai,cs</t>
         </is>
       </c>
       <c r="T225" s="39" t="inlineStr">
         <is>
-          <t>s:limitation</t>
+          <t>s:delegation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B226" s="34" t="inlineStr">
         <is>
-          <t>outage</t>
+          <t>diligence</t>
         </is>
       </c>
       <c r="C226" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D226" s="14" t="inlineStr">
         <is>
-          <t>A time when a service stops working.</t>
+          <t>Careful, responsible work, including keeping customer data safe.</t>
         </is>
       </c>
       <c r="E226" s="14" t="inlineStr">
         <is>
-          <t>OW-tij</t>
+          <t>DIL-i-juns</t>
         </is>
       </c>
       <c r="F226" s="14" t="inlineStr">
         <is>
-          <t>/ˈaʊtɪdʒ/</t>
+          <t>/ˈdɪlɪdʒəns/</t>
         </is>
       </c>
       <c r="G226" s="14" t="inlineStr">
@@ -22015,28 +22015,28 @@
       </c>
       <c r="H226" s="14" t="inlineStr">
         <is>
-          <t>The outage lasted two hours.</t>
+          <t>His diligence kept the case notes accurate.</t>
         </is>
       </c>
       <c r="I226" s="14" t="inlineStr">
         <is>
-          <t>There is an outage in Europe right now.</t>
+          <t>Diligence means no customer data in public AI tools.</t>
         </is>
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>We will post an update if there is another outage.</t>
+          <t>Diligence will matter more as we use more AI.</t>
         </is>
       </c>
       <c r="K226" s="14" t="inlineStr"/>
       <c r="L226" s="36" t="inlineStr">
         <is>
-          <t>सेवा ठप होना, आउटेज</t>
+          <t>लगन, सावधानी</t>
         </is>
       </c>
       <c r="M226" s="36" t="inlineStr">
         <is>
-          <t>वह समय जब कोई सेवा काम करना बंद कर देती है।</t>
+          <t>सावधानी और ज़िम्मेदारी से काम करना, जैसे ग्राहक का डेटा सुरक्षित रखना।</t>
         </is>
       </c>
       <c r="N226" s="37" t="inlineStr">
@@ -22060,42 +22060,42 @@
       <c r="R226" s="37" t="inlineStr"/>
       <c r="S226" s="39" t="inlineStr">
         <is>
-          <t>tech,cs</t>
+          <t>training,ai,cs</t>
         </is>
       </c>
       <c r="T226" s="39" t="inlineStr">
         <is>
-          <t>s:outage</t>
+          <t>s:diligence</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B227" s="34" t="inlineStr">
         <is>
-          <t>password reset</t>
+          <t>discernment</t>
         </is>
       </c>
       <c r="C227" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D227" s="14" t="inlineStr">
         <is>
-          <t>Making a new password when you forget the old one.</t>
+          <t>Judging carefully whether something, like an AI answer, is true and right to use.</t>
         </is>
       </c>
       <c r="E227" s="14" t="inlineStr">
         <is>
-          <t>PASS-wurd ree-SET</t>
+          <t>di-SURN-munt</t>
         </is>
       </c>
       <c r="F227" s="14" t="inlineStr">
         <is>
-          <t>/ˈpɑːswɜːd ˌriːˈset/</t>
+          <t>/dɪˈsɜːnmənt/</t>
         </is>
       </c>
       <c r="G227" s="14" t="inlineStr">
@@ -22105,28 +22105,28 @@
       </c>
       <c r="H227" s="14" t="inlineStr">
         <is>
-          <t>I sent him a password reset email.</t>
+          <t>Her discernment caught a wrong refund date.</t>
         </is>
       </c>
       <c r="I227" s="14" t="inlineStr">
         <is>
-          <t>The password reset link lasts one hour.</t>
+          <t>Discernment means checking AI answers before sending.</t>
         </is>
       </c>
       <c r="J227" s="14" t="inlineStr">
         <is>
-          <t>The password reset will log you out everywhere.</t>
+          <t>Discernment will protect customers from hallucinations.</t>
         </is>
       </c>
       <c r="K227" s="14" t="inlineStr"/>
       <c r="L227" s="36" t="inlineStr">
         <is>
-          <t>पासवर्ड रीसेट</t>
+          <t>विवेक, परख</t>
         </is>
       </c>
       <c r="M227" s="36" t="inlineStr">
         <is>
-          <t>पुराना पासवर्ड भूलने पर नया पासवर्ड बनाना।</t>
+          <t>किसी चीज़, जैसे AI जवाब, को ध्यान से परखना कि वह सही है या नहीं।</t>
         </is>
       </c>
       <c r="N227" s="37" t="inlineStr">
@@ -22150,73 +22150,73 @@
       <c r="R227" s="37" t="inlineStr"/>
       <c r="S227" s="39" t="inlineStr">
         <is>
-          <t>tech,cs</t>
+          <t>training,ai,cs</t>
         </is>
       </c>
       <c r="T227" s="39" t="inlineStr">
         <is>
-          <t>s:password-reset</t>
+          <t>s:discernment</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B228" s="34" t="inlineStr">
         <is>
-          <t>remediate</t>
+          <t>emotional contagion</t>
         </is>
       </c>
       <c r="C228" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D228" s="14" t="inlineStr">
         <is>
-          <t>To fix a problem, often a serious or risky one.</t>
+          <t>When one person's mood spreads to another, for example your calm tone calming a customer.</t>
         </is>
       </c>
       <c r="E228" s="14" t="inlineStr">
         <is>
-          <t>ri-MEE-dee-ayt</t>
+          <t>i-MOH-shuh-nul kun-TAY-jun</t>
         </is>
       </c>
       <c r="F228" s="14" t="inlineStr">
         <is>
-          <t>/rɪˈmiːdieɪt/</t>
+          <t>/ɪˈməʊʃənl kənˈteɪdʒən/</t>
         </is>
       </c>
       <c r="G228" s="14" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H228" s="14" t="inlineStr">
         <is>
-          <t>They remediated the data issue overnight.</t>
+          <t>Emotional contagion made the whole team tense that day.</t>
         </is>
       </c>
       <c r="I228" s="14" t="inlineStr">
         <is>
-          <t>The security team remediates risks quickly.</t>
+          <t>Emotional contagion means your tone can calm a caller.</t>
         </is>
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>We will remediate the bug in the next release.</t>
+          <t>Emotional contagion will work for you if you stay positive.</t>
         </is>
       </c>
       <c r="K228" s="14" t="inlineStr"/>
       <c r="L228" s="36" t="inlineStr">
         <is>
-          <t>सुधार करना, ठीक करना</t>
+          <t>भावनाओं का फैलना</t>
         </is>
       </c>
       <c r="M228" s="36" t="inlineStr">
         <is>
-          <t>किसी गंभीर समस्या या जोखिम को ठीक करना।</t>
+          <t>जब एक व्यक्ति का मूड दूसरे में फैल जाता है, जैसे आपकी शांत आवाज़ से ग्राहक शांत होना।</t>
         </is>
       </c>
       <c r="N228" s="37" t="inlineStr">
@@ -22240,73 +22240,73 @@
       <c r="R228" s="37" t="inlineStr"/>
       <c r="S228" s="39" t="inlineStr">
         <is>
-          <t>tech,corp</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T228" s="39" t="inlineStr">
         <is>
-          <t>s:remediate</t>
+          <t>s:emotional-contagion</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B229" s="34" t="inlineStr">
         <is>
-          <t>reproduce</t>
+          <t>emotional intelligence</t>
         </is>
       </c>
       <c r="C229" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D229" s="14" t="inlineStr">
         <is>
-          <t>To make a bug happen again so you can see it.</t>
+          <t>The skill of understanding and managing your own feelings and other people's feelings.</t>
         </is>
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>ree-pruh-DYOOS</t>
+          <t>i-MOH-shuh-nul in-TEL-i-juns</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
         <is>
-          <t>/ˌriːprəˈdjuːs/</t>
+          <t>/ɪˈməʊʃənl ɪnˈtelɪdʒəns/</t>
         </is>
       </c>
       <c r="G229" s="14" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H229" s="14" t="inlineStr">
         <is>
-          <t>We reproduced the bug in five minutes.</t>
+          <t>Our trainer explained emotional intelligence on day one.</t>
         </is>
       </c>
       <c r="I229" s="14" t="inlineStr">
         <is>
-          <t>Can you reproduce the error on your phone?</t>
+          <t>Emotional intelligence helps me stay calm on hard calls.</t>
         </is>
       </c>
       <c r="J229" s="14" t="inlineStr">
         <is>
-          <t>The team will try to reproduce it tomorrow.</t>
+          <t>Good emotional intelligence will improve your CSAT.</t>
         </is>
       </c>
       <c r="K229" s="14" t="inlineStr"/>
       <c r="L229" s="36" t="inlineStr">
         <is>
-          <t>गड़बड़ी को दोबारा करके देखना</t>
+          <t>भावनात्मक बुद्धिमत्ता</t>
         </is>
       </c>
       <c r="M229" s="36" t="inlineStr">
         <is>
-          <t>बग को फिर से होते हुए देखना ताकि उसे समझा जा सके।</t>
+          <t>अपनी और दूसरों की भावनाओं को समझने और संभालने की क्षमता।</t>
         </is>
       </c>
       <c r="N229" s="37" t="inlineStr">
@@ -22330,42 +22330,42 @@
       <c r="R229" s="37" t="inlineStr"/>
       <c r="S229" s="39" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T229" s="39" t="inlineStr">
         <is>
-          <t>s:reproduce</t>
+          <t>s:emotional-intelligence</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B230" s="34" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>empathy</t>
         </is>
       </c>
       <c r="C230" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D230" s="14" t="inlineStr">
         <is>
-          <t>A picture of what is on your screen.</t>
+          <t>Understanding and sharing how another person feels.</t>
         </is>
       </c>
       <c r="E230" s="14" t="inlineStr">
         <is>
-          <t>SKREEN-shot</t>
+          <t>EM-puh-thee</t>
         </is>
       </c>
       <c r="F230" s="14" t="inlineStr">
         <is>
-          <t>/ˈskriːnʃɒt/</t>
+          <t>/ˈempəθi/</t>
         </is>
       </c>
       <c r="G230" s="14" t="inlineStr">
@@ -22375,28 +22375,28 @@
       </c>
       <c r="H230" s="14" t="inlineStr">
         <is>
-          <t>He shared a screenshot of the bill.</t>
+          <t>He showed empathy before he gave the steps.</t>
         </is>
       </c>
       <c r="I230" s="14" t="inlineStr">
         <is>
-          <t>Please send a screenshot of the error.</t>
+          <t>Empathy matters most when a customer is upset.</t>
         </is>
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>I will add your screenshot to the ticket.</t>
+          <t>Empathy will build trust faster than a script.</t>
         </is>
       </c>
       <c r="K230" s="14" t="inlineStr"/>
       <c r="L230" s="36" t="inlineStr">
         <is>
-          <t>स्क्रीनशॉट</t>
+          <t>सहानुभूति, समानुभूति</t>
         </is>
       </c>
       <c r="M230" s="36" t="inlineStr">
         <is>
-          <t>आपकी स्क्रीन पर जो दिख रहा है उसकी तस्वीर।</t>
+          <t>किसी दूसरे की भावना को समझना और महसूस करना।</t>
         </is>
       </c>
       <c r="N230" s="37" t="inlineStr">
@@ -22420,24 +22420,24 @@
       <c r="R230" s="37" t="inlineStr"/>
       <c r="S230" s="39" t="inlineStr">
         <is>
-          <t>tech,cs</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T230" s="39" t="inlineStr">
         <is>
-          <t>s:screenshot</t>
+          <t>s:empathy</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B231" s="34" t="inlineStr">
         <is>
-          <t>two-factor authentication</t>
+          <t>expert system</t>
         </is>
       </c>
       <c r="C231" s="35" t="n">
@@ -22445,17 +22445,17 @@
       </c>
       <c r="D231" s="14" t="inlineStr">
         <is>
-          <t>A second login step, like a code sent to your phone.</t>
+          <t>Early AI that followed a big set of if-then rules written by experts.</t>
         </is>
       </c>
       <c r="E231" s="14" t="inlineStr">
         <is>
-          <t>too FAK-ter aw-then-ti-KAY-shun</t>
+          <t>EKS-purt SIS-tum</t>
         </is>
       </c>
       <c r="F231" s="14" t="inlineStr">
         <is>
-          <t>/tuː ˈfæktə ɔːˌθentɪˈkeɪʃn/</t>
+          <t>/ˈekspɜːt ˈsɪstəm/</t>
         </is>
       </c>
       <c r="G231" s="14" t="inlineStr">
@@ -22465,28 +22465,28 @@
       </c>
       <c r="H231" s="14" t="inlineStr">
         <is>
-          <t>She turned on two-factor authentication yesterday.</t>
+          <t>Banks used expert systems in the 1980s.</t>
         </is>
       </c>
       <c r="I231" s="14" t="inlineStr">
         <is>
-          <t>Two-factor authentication keeps accounts safe.</t>
+          <t>An expert system follows fixed if-then rules.</t>
         </is>
       </c>
       <c r="J231" s="14" t="inlineStr">
         <is>
-          <t>You will need the code for two-factor authentication.</t>
+          <t>An expert system will fail when a case is new.</t>
         </is>
       </c>
       <c r="K231" s="14" t="inlineStr"/>
       <c r="L231" s="36" t="inlineStr">
         <is>
-          <t>दो-चरणीय सत्यापन</t>
+          <t>विशेषज्ञ प्रणाली</t>
         </is>
       </c>
       <c r="M231" s="36" t="inlineStr">
         <is>
-          <t>लॉगिन का दूसरा कदम, जैसे फ़ोन पर आया कोड।</t>
+          <t>शुरुआती AI जो विशेषज्ञों के लिखे "अगर-तो" नियमों पर चलती थी।</t>
         </is>
       </c>
       <c r="N231" s="37" t="inlineStr">
@@ -22510,42 +22510,42 @@
       <c r="R231" s="37" t="inlineStr"/>
       <c r="S231" s="39" t="inlineStr">
         <is>
-          <t>tech,cs</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T231" s="39" t="inlineStr">
         <is>
-          <t>s:two-factor-authentication</t>
+          <t>s:expert-system</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="33" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B232" s="34" t="inlineStr">
         <is>
-          <t>workaround</t>
+          <t>fine-tuning</t>
         </is>
       </c>
       <c r="C232" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D232" s="14" t="inlineStr">
         <is>
-          <t>A temporary way to avoid a problem until it is fixed.</t>
+          <t>Training an existing AI model a bit more on special data so it gets better at one job.</t>
         </is>
       </c>
       <c r="E232" s="14" t="inlineStr">
         <is>
-          <t>WURK-uh-round</t>
+          <t>fyn-TYOO-ning</t>
         </is>
       </c>
       <c r="F232" s="14" t="inlineStr">
         <is>
-          <t>/ˈwɜːkəraʊnd/</t>
+          <t>/ˌfaɪn ˈtjuːnɪŋ/</t>
         </is>
       </c>
       <c r="G232" s="14" t="inlineStr">
@@ -22555,28 +22555,28 @@
       </c>
       <c r="H232" s="14" t="inlineStr">
         <is>
-          <t>I shared a workaround with the user.</t>
+          <t>Fine-tuning improved the model's answers about billing.</t>
         </is>
       </c>
       <c r="I232" s="14" t="inlineStr">
         <is>
-          <t>There is a simple workaround for this bug.</t>
+          <t>Fine-tuning teaches a model a company's style.</t>
         </is>
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>We will find a workaround until the update is out.</t>
+          <t>Fine-tuning will cost more than better prompts.</t>
         </is>
       </c>
       <c r="K232" s="14" t="inlineStr"/>
       <c r="L232" s="36" t="inlineStr">
         <is>
-          <t>अस्थायी उपाय</t>
+          <t>फ़ाइन-ट्यूनिंग</t>
         </is>
       </c>
       <c r="M232" s="36" t="inlineStr">
         <is>
-          <t>समस्या ठीक होने तक काम चलाने का कोई दूसरा तरीका।</t>
+          <t>किसी मौजूदा AI मॉडल को खास डेटा पर थोड़ा और सिखाना ताकि वह एक काम में बेहतर हो।</t>
         </is>
       </c>
       <c r="N232" s="37" t="inlineStr">
@@ -22600,24 +22600,24 @@
       <c r="R232" s="37" t="inlineStr"/>
       <c r="S232" s="39" t="inlineStr">
         <is>
-          <t>tech,cs</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T232" s="39" t="inlineStr">
         <is>
-          <t>s:workaround</t>
+          <t>s:fine-tuning</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B233" s="34" t="inlineStr">
         <is>
-          <t>agenda</t>
+          <t>funding</t>
         </is>
       </c>
       <c r="C233" s="35" t="n">
@@ -22625,17 +22625,17 @@
       </c>
       <c r="D233" s="14" t="inlineStr">
         <is>
-          <t>The list of topics for a meeting.</t>
+          <t>Money given for a project or research.</t>
         </is>
       </c>
       <c r="E233" s="14" t="inlineStr">
         <is>
-          <t>uh-JEN-duh</t>
+          <t>FUN-ding</t>
         </is>
       </c>
       <c r="F233" s="14" t="inlineStr">
         <is>
-          <t>/əˈdʒendə/</t>
+          <t>/ˈfʌndɪŋ/</t>
         </is>
       </c>
       <c r="G233" s="14" t="inlineStr">
@@ -22645,28 +22645,28 @@
       </c>
       <c r="H233" s="14" t="inlineStr">
         <is>
-          <t>She shared the agenda before the call.</t>
+          <t>Funding was cut during the AI winter.</t>
         </is>
       </c>
       <c r="I233" s="14" t="inlineStr">
         <is>
-          <t>The agenda has four points.</t>
+          <t>Research needs steady funding.</t>
         </is>
       </c>
       <c r="J233" s="14" t="inlineStr">
         <is>
-          <t>I will send the agenda tonight.</t>
+          <t>New funding will speed up the project.</t>
         </is>
       </c>
       <c r="K233" s="14" t="inlineStr"/>
       <c r="L233" s="36" t="inlineStr">
         <is>
-          <t>कार्यसूची, एजेंडा</t>
+          <t>धन, फंडिंग</t>
         </is>
       </c>
       <c r="M233" s="36" t="inlineStr">
         <is>
-          <t>मीटिंग में बात होने वाले विषयों की सूची।</t>
+          <t>किसी प्रोजेक्ट या शोध के लिए दिया गया पैसा।</t>
         </is>
       </c>
       <c r="N233" s="37" t="inlineStr">
@@ -22690,24 +22690,24 @@
       <c r="R233" s="37" t="inlineStr"/>
       <c r="S233" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T233" s="39" t="inlineStr">
         <is>
-          <t>s:agenda</t>
+          <t>s:funding</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B234" s="34" t="inlineStr">
         <is>
-          <t>annual leave</t>
+          <t>generative AI</t>
         </is>
       </c>
       <c r="C234" s="35" t="n">
@@ -22715,17 +22715,17 @@
       </c>
       <c r="D234" s="14" t="inlineStr">
         <is>
-          <t>Paid days off you get each year for holidays.</t>
+          <t>AI that creates new text, images, sound or code.</t>
         </is>
       </c>
       <c r="E234" s="14" t="inlineStr">
         <is>
-          <t>AN-yoo-ul leev</t>
+          <t>JEN-er-uh-tiv ay EYE</t>
         </is>
       </c>
       <c r="F234" s="14" t="inlineStr">
         <is>
-          <t>/ˈænjuəl liːv/</t>
+          <t>/ˈdʒenərətɪv ˌeɪ ˈaɪ/</t>
         </is>
       </c>
       <c r="G234" s="14" t="inlineStr">
@@ -22735,28 +22735,28 @@
       </c>
       <c r="H234" s="14" t="inlineStr">
         <is>
-          <t>She took annual leave in August.</t>
+          <t>Generative AI became popular in 2022.</t>
         </is>
       </c>
       <c r="I234" s="14" t="inlineStr">
         <is>
-          <t>I have ten days of annual leave left.</t>
+          <t>Generative AI writes drafts in seconds.</t>
         </is>
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>I will book annual leave for Christmas.</t>
+          <t>Generative AI will change how we write emails.</t>
         </is>
       </c>
       <c r="K234" s="14" t="inlineStr"/>
       <c r="L234" s="36" t="inlineStr">
         <is>
-          <t>वार्षिक छुट्टी</t>
+          <t>जनरेटिव AI</t>
         </is>
       </c>
       <c r="M234" s="36" t="inlineStr">
         <is>
-          <t>हर साल मिलने वाली वेतन सहित छुट्टियाँ।</t>
+          <t>AI जो नया टेक्स्ट, चित्र, आवाज़ या कोड बनाती है।</t>
         </is>
       </c>
       <c r="N234" s="37" t="inlineStr">
@@ -22780,42 +22780,42 @@
       <c r="R234" s="37" t="inlineStr"/>
       <c r="S234" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T234" s="39" t="inlineStr">
         <is>
-          <t>s:annual-leave</t>
+          <t>s:generative-ai</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B235" s="34" t="inlineStr">
         <is>
-          <t>benefits</t>
+          <t>human-in-the-loop</t>
         </is>
       </c>
       <c r="C235" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D235" s="14" t="inlineStr">
         <is>
-          <t>Extra things your job gives you besides salary, like health insurance.</t>
+          <t>A person reviews AI work before it reaches a customer.</t>
         </is>
       </c>
       <c r="E235" s="14" t="inlineStr">
         <is>
-          <t>BEN-i-fits</t>
+          <t>HYOO-mun in thuh LOOP</t>
         </is>
       </c>
       <c r="F235" s="14" t="inlineStr">
         <is>
-          <t>/ˈbenɪfɪts/</t>
+          <t>/ˈhjuːmən ɪn ðə luːp/</t>
         </is>
       </c>
       <c r="G235" s="14" t="inlineStr">
@@ -22825,28 +22825,28 @@
       </c>
       <c r="H235" s="14" t="inlineStr">
         <is>
-          <t>HR explained the benefits on day one.</t>
+          <t>Human-in-the-loop caught two wrong answers yesterday.</t>
         </is>
       </c>
       <c r="I235" s="14" t="inlineStr">
         <is>
-          <t>The benefits include health insurance.</t>
+          <t>Human-in-the-loop means I check every AI draft.</t>
         </is>
       </c>
       <c r="J235" s="14" t="inlineStr">
         <is>
-          <t>Your benefits will start after probation.</t>
+          <t>Human-in-the-loop will stay part of our process.</t>
         </is>
       </c>
       <c r="K235" s="14" t="inlineStr"/>
       <c r="L235" s="36" t="inlineStr">
         <is>
-          <t>अतिरिक्त सुविधाएँ, लाभ</t>
+          <t>मानवीय निगरानी (ह्यूमन-इन-द-लूप)</t>
         </is>
       </c>
       <c r="M235" s="36" t="inlineStr">
         <is>
-          <t>वेतन के अलावा नौकरी से मिलने वाली सुविधाएँ, जैसे स्वास्थ्य बीमा।</t>
+          <t>AI का काम ग्राहक तक पहुँचने से पहले इंसान उसकी जांच करता है।</t>
         </is>
       </c>
       <c r="N235" s="37" t="inlineStr">
@@ -22870,24 +22870,24 @@
       <c r="R235" s="37" t="inlineStr"/>
       <c r="S235" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,cs</t>
         </is>
       </c>
       <c r="T235" s="39" t="inlineStr">
         <is>
-          <t>s:benefits</t>
+          <t>s:human-in-the-loop</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B236" s="34" t="inlineStr">
         <is>
-          <t>clock in</t>
+          <t>hype</t>
         </is>
       </c>
       <c r="C236" s="35" t="n">
@@ -22895,48 +22895,48 @@
       </c>
       <c r="D236" s="14" t="inlineStr">
         <is>
-          <t>To record the time you start work.</t>
+          <t>Too much excitement or promotion, often more than something deserves.</t>
         </is>
       </c>
       <c r="E236" s="14" t="inlineStr">
         <is>
-          <t>klok IN</t>
+          <t>hyp</t>
         </is>
       </c>
       <c r="F236" s="14" t="inlineStr">
         <is>
-          <t>/klɒk ɪn/</t>
+          <t>/haɪp/</t>
         </is>
       </c>
       <c r="G236" s="14" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H236" s="14" t="inlineStr">
         <is>
-          <t>I clocked in at 7:55.</t>
+          <t>The hype faded when the results were weak.</t>
         </is>
       </c>
       <c r="I236" s="14" t="inlineStr">
         <is>
-          <t>We clock in with our ID card.</t>
+          <t>There is a lot of hype around new AI tools.</t>
         </is>
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>You will clock in on the new app.</t>
+          <t>Real results will matter more than hype.</t>
         </is>
       </c>
       <c r="K236" s="14" t="inlineStr"/>
       <c r="L236" s="36" t="inlineStr">
         <is>
-          <t>काम शुरू होने का समय दर्ज करना</t>
+          <t>अतिप्रचार</t>
         </is>
       </c>
       <c r="M236" s="36" t="inlineStr">
         <is>
-          <t>काम शुरू करने का समय सिस्टम में दर्ज करना।</t>
+          <t>किसी चीज़ को लेकर ज़रूरत से ज़्यादा उत्साह या प्रचार।</t>
         </is>
       </c>
       <c r="N236" s="37" t="inlineStr">
@@ -22960,42 +22960,42 @@
       <c r="R236" s="37" t="inlineStr"/>
       <c r="S236" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T236" s="39" t="inlineStr">
         <is>
-          <t>s:clock-in</t>
+          <t>s:hype</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B237" s="34" t="inlineStr">
         <is>
-          <t>comp off</t>
+          <t>hype cycle</t>
         </is>
       </c>
       <c r="C237" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D237" s="14" t="inlineStr">
         <is>
-          <t>A day off you get for working on a holiday or weekend.</t>
+          <t>The pattern where excitement about new technology rises, falls, then settles into real use.</t>
         </is>
       </c>
       <c r="E237" s="14" t="inlineStr">
         <is>
-          <t>KOMP off</t>
+          <t>hyp SY-kul</t>
         </is>
       </c>
       <c r="F237" s="14" t="inlineStr">
         <is>
-          <t>/ˈkɒmp ɒf/</t>
+          <t>/haɪp ˈsaɪkl/</t>
         </is>
       </c>
       <c r="G237" s="14" t="inlineStr">
@@ -23005,28 +23005,28 @@
       </c>
       <c r="H237" s="14" t="inlineStr">
         <is>
-          <t>She used her comp off on Friday.</t>
+          <t>Early chatbots went through a hype cycle too.</t>
         </is>
       </c>
       <c r="I237" s="14" t="inlineStr">
         <is>
-          <t>I have a comp off for last Sunday.</t>
+          <t>Every new technology goes through a hype cycle.</t>
         </is>
       </c>
       <c r="J237" s="14" t="inlineStr">
         <is>
-          <t>You will get a comp off for the weekend shift.</t>
+          <t>The hype cycle will explain why interest drops.</t>
         </is>
       </c>
       <c r="K237" s="14" t="inlineStr"/>
       <c r="L237" s="36" t="inlineStr">
         <is>
-          <t>प्रतिपूरक छुट्टी, कॉम्प ऑफ</t>
+          <t>हाइप चक्र</t>
         </is>
       </c>
       <c r="M237" s="36" t="inlineStr">
         <is>
-          <t>छुट्टी या वीकेंड पर काम करने के बदले मिलने वाली छुट्टी।</t>
+          <t>नई तकनीक को लेकर उत्साह बढ़ने, गिरने और फिर संतुलित होने का क्रम।</t>
         </is>
       </c>
       <c r="N237" s="37" t="inlineStr">
@@ -23050,73 +23050,73 @@
       <c r="R237" s="37" t="inlineStr"/>
       <c r="S237" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T237" s="39" t="inlineStr">
         <is>
-          <t>s:comp-off</t>
+          <t>s:hype-cycle</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B238" s="34" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>hypothetical</t>
         </is>
       </c>
       <c r="C238" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D238" s="14" t="inlineStr">
         <is>
-          <t>A written agreement about your job, pay and rules.</t>
+          <t>Imagined as possible, but not real.</t>
         </is>
       </c>
       <c r="E238" s="14" t="inlineStr">
         <is>
-          <t>KON-trakt</t>
+          <t>hy-puh-THET-i-kul</t>
         </is>
       </c>
       <c r="F238" s="14" t="inlineStr">
         <is>
-          <t>/ˈkɒntrækt/</t>
+          <t>/ˌhaɪpəˈθetɪkl/</t>
         </is>
       </c>
       <c r="G238" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="H238" s="14" t="inlineStr">
         <is>
-          <t>I signed the contract last week.</t>
+          <t>She asked a hypothetical question about refunds.</t>
         </is>
       </c>
       <c r="I238" s="14" t="inlineStr">
         <is>
-          <t>My contract is for one year.</t>
+          <t>ASI is a hypothetical stage of AI.</t>
         </is>
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>HR will email you the contract.</t>
+          <t>We will use a hypothetical customer in the role-play.</t>
         </is>
       </c>
       <c r="K238" s="14" t="inlineStr"/>
       <c r="L238" s="36" t="inlineStr">
         <is>
-          <t>अनुबंध, कॉन्ट्रैक्ट</t>
+          <t>काल्पनिक</t>
         </is>
       </c>
       <c r="M238" s="36" t="inlineStr">
         <is>
-          <t>नौकरी, वेतन और नियमों के बारे में लिखित समझौता।</t>
+          <t>संभव माना गया, लेकिन असली नहीं।</t>
         </is>
       </c>
       <c r="N238" s="37" t="inlineStr">
@@ -23140,42 +23140,42 @@
       <c r="R238" s="37" t="inlineStr"/>
       <c r="S238" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai</t>
         </is>
       </c>
       <c r="T238" s="39" t="inlineStr">
         <is>
-          <t>s:contract</t>
+          <t>s:hypothetical</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B239" s="34" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>impulse</t>
         </is>
       </c>
       <c r="C239" s="35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D239" s="14" t="inlineStr">
         <is>
-          <t>A person who works for a company and gets paid.</t>
+          <t>A sudden wish to do something without thinking.</t>
         </is>
       </c>
       <c r="E239" s="14" t="inlineStr">
         <is>
-          <t>im-PLOY-ee</t>
+          <t>IM-puls</t>
         </is>
       </c>
       <c r="F239" s="14" t="inlineStr">
         <is>
-          <t>/ɪmˈplɔɪiː/</t>
+          <t>/ˈɪmpʌls/</t>
         </is>
       </c>
       <c r="G239" s="14" t="inlineStr">
@@ -23185,28 +23185,28 @@
       </c>
       <c r="H239" s="14" t="inlineStr">
         <is>
-          <t>She was employee of the month.</t>
+          <t>He acted on impulse and sent the email too fast.</t>
         </is>
       </c>
       <c r="I239" s="14" t="inlineStr">
         <is>
-          <t>Every employee gets a laptop.</t>
+          <t>I fight the impulse to interrupt.</t>
         </is>
       </c>
       <c r="J239" s="14" t="inlineStr">
         <is>
-          <t>New employees will start on Monday.</t>
+          <t>Taking a breath will help you control the impulse.</t>
         </is>
       </c>
       <c r="K239" s="14" t="inlineStr"/>
       <c r="L239" s="36" t="inlineStr">
         <is>
-          <t>कर्मचारी</t>
+          <t>आवेग</t>
         </is>
       </c>
       <c r="M239" s="36" t="inlineStr">
         <is>
-          <t>वह व्यक्ति जो किसी कंपनी में काम करता है और वेतन पाता है।</t>
+          <t>बिना सोचे कुछ करने की अचानक इच्छा।</t>
         </is>
       </c>
       <c r="N239" s="37" t="inlineStr">
@@ -23230,42 +23230,42 @@
       <c r="R239" s="37" t="inlineStr"/>
       <c r="S239" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T239" s="39" t="inlineStr">
         <is>
-          <t>s:employee</t>
+          <t>s:impulse</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B240" s="34" t="inlineStr">
         <is>
-          <t>employer</t>
+          <t>instruction-following</t>
         </is>
       </c>
       <c r="C240" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D240" s="14" t="inlineStr">
         <is>
-          <t>The company or person that pays you to work.</t>
+          <t>How well an AI does exactly what you asked.</t>
         </is>
       </c>
       <c r="E240" s="14" t="inlineStr">
         <is>
-          <t>im-PLOY-er</t>
+          <t>in-STRUK-shun FOL-oh-ing</t>
         </is>
       </c>
       <c r="F240" s="14" t="inlineStr">
         <is>
-          <t>/ɪmˈplɔɪə/</t>
+          <t>/ɪnˈstrʌkʃn ˈfɒləʊɪŋ/</t>
         </is>
       </c>
       <c r="G240" s="14" t="inlineStr">
@@ -23275,28 +23275,28 @@
       </c>
       <c r="H240" s="14" t="inlineStr">
         <is>
-          <t>My last employer gave me a good reference.</t>
+          <t>The old model's instruction-following was weak.</t>
         </is>
       </c>
       <c r="I240" s="14" t="inlineStr">
         <is>
-          <t>My employer pays on the last day of the month.</t>
+          <t>Newer models have better instruction-following.</t>
         </is>
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>Your employer will send the contract.</t>
+          <t>Clear prompts will improve instruction-following.</t>
         </is>
       </c>
       <c r="K240" s="14" t="inlineStr"/>
       <c r="L240" s="36" t="inlineStr">
         <is>
-          <t>नियोक्ता</t>
+          <t>निर्देशों का पालन</t>
         </is>
       </c>
       <c r="M240" s="36" t="inlineStr">
         <is>
-          <t>वह कंपनी या व्यक्ति जो आपको काम के लिए पैसे देता है।</t>
+          <t>AI ठीक वही करता है या नहीं जो आपने कहा।</t>
         </is>
       </c>
       <c r="N240" s="37" t="inlineStr">
@@ -23320,24 +23320,24 @@
       <c r="R240" s="37" t="inlineStr"/>
       <c r="S240" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T240" s="39" t="inlineStr">
         <is>
-          <t>s:employer</t>
+          <t>s:instruction-following</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B241" s="34" t="inlineStr">
         <is>
-          <t>fixed-term contract</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="C241" s="35" t="n">
@@ -23345,48 +23345,48 @@
       </c>
       <c r="D241" s="14" t="inlineStr">
         <is>
-          <t>A job contract that ends on a set date.</t>
+          <t>Old but still in use, and often being replaced by something newer.</t>
         </is>
       </c>
       <c r="E241" s="14" t="inlineStr">
         <is>
-          <t>fikst-turm KON-trakt</t>
+          <t>LEG-uh-see</t>
         </is>
       </c>
       <c r="F241" s="14" t="inlineStr">
         <is>
-          <t>/ˌfɪkst tɜːm ˈkɒntrækt/</t>
+          <t>/ˈleɡəsi/</t>
         </is>
       </c>
       <c r="G241" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="H241" s="14" t="inlineStr">
         <is>
-          <t>They offered me a fixed-term contract.</t>
+          <t>We moved off the legacy system last year.</t>
         </is>
       </c>
       <c r="I241" s="14" t="inlineStr">
         <is>
-          <t>My fixed-term contract ends in June.</t>
+          <t>GPT-3.5 is now a legacy model.</t>
         </is>
       </c>
       <c r="J241" s="14" t="inlineStr">
         <is>
-          <t>The fixed-term contract will become permanent.</t>
+          <t>Legacy models will retire on a schedule.</t>
         </is>
       </c>
       <c r="K241" s="14" t="inlineStr"/>
       <c r="L241" s="36" t="inlineStr">
         <is>
-          <t>निश्चित अवधि का अनुबंध</t>
+          <t>पुराना (लेगेसी)</t>
         </is>
       </c>
       <c r="M241" s="36" t="inlineStr">
         <is>
-          <t>ऐसा अनुबंध जो तय तारीख पर खत्म होता है।</t>
+          <t>पुराना लेकिन अभी भी इस्तेमाल में, अक्सर नए से बदला जाने वाला।</t>
         </is>
       </c>
       <c r="N241" s="37" t="inlineStr">
@@ -23410,42 +23410,42 @@
       <c r="R241" s="37" t="inlineStr"/>
       <c r="S241" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T241" s="39" t="inlineStr">
         <is>
-          <t>s:fixed-term-contract</t>
+          <t>s:legacy</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B242" s="34" t="inlineStr">
         <is>
-          <t>Google Meet</t>
+          <t>machine learning</t>
         </is>
       </c>
       <c r="C242" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242" s="14" t="inlineStr">
         <is>
-          <t>Google's app for video meetings.</t>
+          <t>When computers learn patterns from data instead of being told every rule.</t>
         </is>
       </c>
       <c r="E242" s="14" t="inlineStr">
         <is>
-          <t>GOO-gul meet</t>
+          <t>muh-SHEEN LUR-ning</t>
         </is>
       </c>
       <c r="F242" s="14" t="inlineStr">
         <is>
-          <t>/ˈɡuːɡl miːt/</t>
+          <t>/məˈʃiːn ˈlɜːnɪŋ/</t>
         </is>
       </c>
       <c r="G242" s="14" t="inlineStr">
@@ -23455,28 +23455,28 @@
       </c>
       <c r="H242" s="14" t="inlineStr">
         <is>
-          <t>I shared my screen on Google Meet.</t>
+          <t>Machine learning changed AI in the 2010s.</t>
         </is>
       </c>
       <c r="I242" s="14" t="inlineStr">
         <is>
-          <t>The training is on Google Meet.</t>
+          <t>Machine learning powers our spam filter.</t>
         </is>
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>I will send you the Google Meet link.</t>
+          <t>Machine learning will improve as it gets more data.</t>
         </is>
       </c>
       <c r="K242" s="14" t="inlineStr"/>
       <c r="L242" s="36" t="inlineStr">
         <is>
-          <t>गूगल मीट (वीडियो मीटिंग ऐप)</t>
+          <t>मशीन लर्निंग</t>
         </is>
       </c>
       <c r="M242" s="36" t="inlineStr">
         <is>
-          <t>वीडियो मीटिंग के लिए गूगल का ऐप।</t>
+          <t>जब कंप्यूटर हर नियम बताए जाने की जगह डेटा से पैटर्न सीखते हैं।</t>
         </is>
       </c>
       <c r="N242" s="37" t="inlineStr">
@@ -23500,24 +23500,24 @@
       <c r="R242" s="37" t="inlineStr"/>
       <c r="S242" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T242" s="39" t="inlineStr">
         <is>
-          <t>s:google-meet</t>
+          <t>s:machine-learning</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B243" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C243" s="35" t="n">
@@ -23525,17 +23525,17 @@
       </c>
       <c r="D243" s="14" t="inlineStr">
         <is>
-          <t>Human Resources, the team that handles hiring, contracts, pay and staff questions.</t>
+          <t>The inner drive to reach your goals.</t>
         </is>
       </c>
       <c r="E243" s="14" t="inlineStr">
         <is>
-          <t>aych AR</t>
+          <t>moh-ti-VAY-shun</t>
         </is>
       </c>
       <c r="F243" s="14" t="inlineStr">
         <is>
-          <t>/ˌeɪtʃ ˈɑː/</t>
+          <t>/ˌməʊtɪˈveɪʃn/</t>
         </is>
       </c>
       <c r="G243" s="14" t="inlineStr">
@@ -23545,28 +23545,28 @@
       </c>
       <c r="H243" s="14" t="inlineStr">
         <is>
-          <t>I emailed HR about my payslip.</t>
+          <t>Her motivation was high in the first week.</t>
         </is>
       </c>
       <c r="I243" s="14" t="inlineStr">
         <is>
-          <t>HR handles all leave requests.</t>
+          <t>My motivation is to help people well.</t>
         </is>
       </c>
       <c r="J243" s="14" t="inlineStr">
         <is>
-          <t>HR will explain your benefits.</t>
+          <t>Clear goals will keep your motivation strong.</t>
         </is>
       </c>
       <c r="K243" s="14" t="inlineStr"/>
       <c r="L243" s="36" t="inlineStr">
         <is>
-          <t>मानव संसाधन विभाग, एचआर</t>
+          <t>प्रेरणा</t>
         </is>
       </c>
       <c r="M243" s="36" t="inlineStr">
         <is>
-          <t>वह टीम जो भर्ती, अनुबंध, वेतन और कर्मचारियों के सवाल संभालती है।</t>
+          <t>अपने लक्ष्य पाने की अंदरूनी इच्छा।</t>
         </is>
       </c>
       <c r="N243" s="37" t="inlineStr">
@@ -23590,73 +23590,73 @@
       <c r="R243" s="37" t="inlineStr"/>
       <c r="S243" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T243" s="39" t="inlineStr">
         <is>
-          <t>s:hr</t>
+          <t>s:motivation</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B244" s="34" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>multimodal</t>
         </is>
       </c>
       <c r="C244" s="35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D244" s="14" t="inlineStr">
         <is>
-          <t>The person who leads a team and checks its work.</t>
+          <t>Able to work with text, images and audio together.</t>
         </is>
       </c>
       <c r="E244" s="14" t="inlineStr">
         <is>
-          <t>MAN-ij-er</t>
+          <t>mul-tee-MOH-dul</t>
         </is>
       </c>
       <c r="F244" s="14" t="inlineStr">
         <is>
-          <t>/ˈmænɪdʒə/</t>
+          <t>/ˌmʌltiˈməʊdl/</t>
         </is>
       </c>
       <c r="G244" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="H244" s="14" t="inlineStr">
         <is>
-          <t>The manager praised our team.</t>
+          <t>The first multimodal model surprised many users.</t>
         </is>
       </c>
       <c r="I244" s="14" t="inlineStr">
         <is>
-          <t>My manager approves my leave.</t>
+          <t>GPT-4o is multimodal.</t>
         </is>
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>Your manager will call you today.</t>
+          <t>Multimodal tools will read screenshots for us.</t>
         </is>
       </c>
       <c r="K244" s="14" t="inlineStr"/>
       <c r="L244" s="36" t="inlineStr">
         <is>
-          <t>प्रबंधक, मैनेजर</t>
+          <t>बहु-माध्यम (मल्टीमोडल)</t>
         </is>
       </c>
       <c r="M244" s="36" t="inlineStr">
         <is>
-          <t>वह व्यक्ति जो टीम का नेतृत्व करता है और काम देखता है।</t>
+          <t>टेक्स्ट, चित्र और आवाज़ के साथ एक साथ काम कर सकने वाला।</t>
         </is>
       </c>
       <c r="N244" s="37" t="inlineStr">
@@ -23680,42 +23680,42 @@
       <c r="R244" s="37" t="inlineStr"/>
       <c r="S244" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T244" s="39" t="inlineStr">
         <is>
-          <t>s:manager</t>
+          <t>s:multimodal</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B245" s="34" t="inlineStr">
         <is>
-          <t>meeting</t>
+          <t>narrow AI</t>
         </is>
       </c>
       <c r="C245" s="35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D245" s="14" t="inlineStr">
         <is>
-          <t>A planned time when people come together to talk about work.</t>
+          <t>AI built for specific tasks, also called ANI. All AI today is narrow AI.</t>
         </is>
       </c>
       <c r="E245" s="14" t="inlineStr">
         <is>
-          <t>MEE-ting</t>
+          <t>NAR-oh ay EYE</t>
         </is>
       </c>
       <c r="F245" s="14" t="inlineStr">
         <is>
-          <t>/ˈmiːtɪŋ/</t>
+          <t>/ˈnærəʊ ˌeɪ ˈaɪ/</t>
         </is>
       </c>
       <c r="G245" s="14" t="inlineStr">
@@ -23725,28 +23725,28 @@
       </c>
       <c r="H245" s="14" t="inlineStr">
         <is>
-          <t>The meeting ran late yesterday.</t>
+          <t>The trainer gave spam filters as an example of narrow AI.</t>
         </is>
       </c>
       <c r="I245" s="14" t="inlineStr">
         <is>
-          <t>We have a team meeting every Monday.</t>
+          <t>ChatGPT is still narrow AI, even though it is versatile.</t>
         </is>
       </c>
       <c r="J245" s="14" t="inlineStr">
         <is>
-          <t>I will join the meeting at three.</t>
+          <t>Narrow AI will stay the norm for now.</t>
         </is>
       </c>
       <c r="K245" s="14" t="inlineStr"/>
       <c r="L245" s="36" t="inlineStr">
         <is>
-          <t>बैठक, मीटिंग</t>
+          <t>संकीर्ण AI (ANI)</t>
         </is>
       </c>
       <c r="M245" s="36" t="inlineStr">
         <is>
-          <t>काम पर बात करने के लिए लोगों का तय समय पर मिलना।</t>
+          <t>खास कामों के लिए बनी AI; आज की सारी AI इसी तरह की है।</t>
         </is>
       </c>
       <c r="N245" s="37" t="inlineStr">
@@ -23770,42 +23770,42 @@
       <c r="R245" s="37" t="inlineStr"/>
       <c r="S245" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>training,ai</t>
         </is>
       </c>
       <c r="T245" s="39" t="inlineStr">
         <is>
-          <t>s:meeting</t>
+          <t>s:narrow-ai</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B246" s="34" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>neural network</t>
         </is>
       </c>
       <c r="C246" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D246" s="14" t="inlineStr">
         <is>
-          <t>The written record of what was said in a meeting.</t>
+          <t>A computer system loosely inspired by the brain, made of connected layers that learn from data.</t>
         </is>
       </c>
       <c r="E246" s="14" t="inlineStr">
         <is>
-          <t>MIN-its</t>
+          <t>NYOOR-ul NET-wurk</t>
         </is>
       </c>
       <c r="F246" s="14" t="inlineStr">
         <is>
-          <t>/ˈmɪnɪts/</t>
+          <t>/ˈnjʊərəl ˈnetwɜːk/</t>
         </is>
       </c>
       <c r="G246" s="14" t="inlineStr">
@@ -23815,28 +23815,28 @@
       </c>
       <c r="H246" s="14" t="inlineStr">
         <is>
-          <t>He sent the minutes after the meeting.</t>
+          <t>Researchers trained a neural network on millions of images.</t>
         </is>
       </c>
       <c r="I246" s="14" t="inlineStr">
         <is>
-          <t>The minutes are in the shared folder.</t>
+          <t>A neural network learns from examples.</t>
         </is>
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>I will share the minutes by noon.</t>
+          <t>A bigger neural network will need more computing power.</t>
         </is>
       </c>
       <c r="K246" s="14" t="inlineStr"/>
       <c r="L246" s="36" t="inlineStr">
         <is>
-          <t>बैठक का लिखित ब्योरा</t>
+          <t>न्यूरल नेटवर्क</t>
         </is>
       </c>
       <c r="M246" s="36" t="inlineStr">
         <is>
-          <t>मीटिंग में हुई बातों का लिखा हुआ रिकॉर्ड।</t>
+          <t>दिमाग से प्रेरित कंप्यूटर सिस्टम, जुड़ी परतों से बना, जो डेटा से सीखता है।</t>
         </is>
       </c>
       <c r="N246" s="37" t="inlineStr">
@@ -23860,73 +23860,73 @@
       <c r="R246" s="37" t="inlineStr"/>
       <c r="S246" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T246" s="39" t="inlineStr">
         <is>
-          <t>s:minutes</t>
+          <t>s:neural-network</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B247" s="34" t="inlineStr">
         <is>
-          <t>mute</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="C247" s="35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D247" s="14" t="inlineStr">
         <is>
-          <t>To turn off your microphone.</t>
+          <t>A setting or number inside a model or system that shapes how it works.</t>
         </is>
       </c>
       <c r="E247" s="14" t="inlineStr">
         <is>
-          <t>myoot</t>
+          <t>puh-RAM-i-ter</t>
         </is>
       </c>
       <c r="F247" s="14" t="inlineStr">
         <is>
-          <t>/mjuːt/</t>
+          <t>/pəˈræmɪtə/</t>
         </is>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H247" s="14" t="inlineStr">
         <is>
-          <t>I forgot I was muted.</t>
+          <t>They changed one parameter and the results improved.</t>
         </is>
       </c>
       <c r="I247" s="14" t="inlineStr">
         <is>
-          <t>Please mute yourself when you aren't speaking.</t>
+          <t>Each model has billions of parameters.</t>
         </is>
       </c>
       <c r="J247" s="14" t="inlineStr">
         <is>
-          <t>I will mute my mic during the training.</t>
+          <t>The new parameter will control reply length.</t>
         </is>
       </c>
       <c r="K247" s="14" t="inlineStr"/>
       <c r="L247" s="36" t="inlineStr">
         <is>
-          <t>म्यूट करना, आवाज़ बंद करना</t>
+          <t>पैरामीटर</t>
         </is>
       </c>
       <c r="M247" s="36" t="inlineStr">
         <is>
-          <t>कॉल पर अपना माइक बंद करना।</t>
+          <t>मॉडल या सिस्टम के अंदर की सेटिंग या संख्या जो उसके काम को तय करती है।</t>
         </is>
       </c>
       <c r="N247" s="37" t="inlineStr">
@@ -23950,42 +23950,42 @@
       <c r="R247" s="37" t="inlineStr"/>
       <c r="S247" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T247" s="39" t="inlineStr">
         <is>
-          <t>s:mute</t>
+          <t>s:parameter</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B248" s="34" t="inlineStr">
         <is>
-          <t>notice period</t>
+          <t>prompt engineering</t>
         </is>
       </c>
       <c r="C248" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D248" s="14" t="inlineStr">
         <is>
-          <t>The time you must keep working after you say you are leaving.</t>
+          <t>Writing and improving prompts to get better AI answers.</t>
         </is>
       </c>
       <c r="E248" s="14" t="inlineStr">
         <is>
-          <t>NOH-tis PEER-ee-ud</t>
+          <t>prompt en-ji-NEER-ing</t>
         </is>
       </c>
       <c r="F248" s="14" t="inlineStr">
         <is>
-          <t>/ˈnəʊtɪs ˈpɪəriəd/</t>
+          <t>/prɒmpt ˌendʒɪˈnɪərɪŋ/</t>
         </is>
       </c>
       <c r="G248" s="14" t="inlineStr">
@@ -23995,28 +23995,28 @@
       </c>
       <c r="H248" s="14" t="inlineStr">
         <is>
-          <t>She worked her full notice period.</t>
+          <t>Good prompt engineering fixed the vague answers.</t>
         </is>
       </c>
       <c r="I248" s="14" t="inlineStr">
         <is>
-          <t>My notice period is one month.</t>
+          <t>Prompt engineering is a useful support skill.</t>
         </is>
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>Your notice period will start today.</t>
+          <t>Prompt engineering will save you time every day.</t>
         </is>
       </c>
       <c r="K248" s="14" t="inlineStr"/>
       <c r="L248" s="36" t="inlineStr">
         <is>
-          <t>नोटिस अवधि</t>
+          <t>प्रॉम्प्ट इंजीनियरिंग</t>
         </is>
       </c>
       <c r="M248" s="36" t="inlineStr">
         <is>
-          <t>नौकरी छोड़ने की सूचना देने के बाद काम करने का ज़रूरी समय।</t>
+          <t>बेहतर AI जवाब पाने के लिए प्रॉम्प्ट लिखना और सुधारना।</t>
         </is>
       </c>
       <c r="N248" s="37" t="inlineStr">
@@ -24040,42 +24040,42 @@
       <c r="R248" s="37" t="inlineStr"/>
       <c r="S248" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T248" s="39" t="inlineStr">
         <is>
-          <t>s:notice-period</t>
+          <t>s:prompt-engineering</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B249" s="34" t="inlineStr">
         <is>
-          <t>one-on-one</t>
+          <t>reasoning model</t>
         </is>
       </c>
       <c r="C249" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D249" s="14" t="inlineStr">
         <is>
-          <t>A private meeting between you and your manager.</t>
+          <t>An AI model that works through steps before answering. Good for maths and logic.</t>
         </is>
       </c>
       <c r="E249" s="14" t="inlineStr">
         <is>
-          <t>wun-on-WUN</t>
+          <t>REE-zuh-ning MOD-ul</t>
         </is>
       </c>
       <c r="F249" s="14" t="inlineStr">
         <is>
-          <t>/ˌwʌn ɒn ˈwʌn/</t>
+          <t>/ˈriːzənɪŋ ˈmɒdl/</t>
         </is>
       </c>
       <c r="G249" s="14" t="inlineStr">
@@ -24085,28 +24085,28 @@
       </c>
       <c r="H249" s="14" t="inlineStr">
         <is>
-          <t>We talked about my goals in our one-on-one.</t>
+          <t>He used a reasoning model for the budget problem.</t>
         </is>
       </c>
       <c r="I249" s="14" t="inlineStr">
         <is>
-          <t>I have a one-on-one with my manager every Friday.</t>
+          <t>A reasoning model is slower but more careful.</t>
         </is>
       </c>
       <c r="J249" s="14" t="inlineStr">
         <is>
-          <t>I will raise this in my next one-on-one.</t>
+          <t>A reasoning model will help with tricky logic.</t>
         </is>
       </c>
       <c r="K249" s="14" t="inlineStr"/>
       <c r="L249" s="36" t="inlineStr">
         <is>
-          <t>आमने-सामने की निजी बैठक</t>
+          <t>तर्क करने वाला मॉडल</t>
         </is>
       </c>
       <c r="M249" s="36" t="inlineStr">
         <is>
-          <t>आपकी और आपके मैनेजर की अकेले में होने वाली मीटिंग।</t>
+          <t>AI मॉडल जो जवाब से पहले कदम-दर-कदम सोचता है, गणित और तर्क में अच्छा।</t>
         </is>
       </c>
       <c r="N249" s="37" t="inlineStr">
@@ -24130,73 +24130,73 @@
       <c r="R249" s="37" t="inlineStr"/>
       <c r="S249" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T249" s="39" t="inlineStr">
         <is>
-          <t>s:one-on-one</t>
+          <t>s:reasoning-model</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B250" s="34" t="inlineStr">
         <is>
-          <t>out of office</t>
+          <t>rule-based</t>
         </is>
       </c>
       <c r="C250" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D250" s="14" t="inlineStr">
         <is>
-          <t>Away from work, so you can't reply for a while.</t>
+          <t>Working by following fixed rules written by people.</t>
         </is>
       </c>
       <c r="E250" s="14" t="inlineStr">
         <is>
-          <t>owt uv OF-is</t>
+          <t>ROOL-bayst</t>
         </is>
       </c>
       <c r="F250" s="14" t="inlineStr">
         <is>
-          <t>/aʊt əv ˈɒfɪs/</t>
+          <t>/ˈruːl beɪst/</t>
         </is>
       </c>
       <c r="G250" s="14" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="H250" s="14" t="inlineStr">
         <is>
-          <t>She set an out of office reply.</t>
+          <t>The first system was rule-based and rigid.</t>
         </is>
       </c>
       <c r="I250" s="14" t="inlineStr">
         <is>
-          <t>I'm out of office until Monday.</t>
+          <t>Old chatbots were rule-based.</t>
         </is>
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>I will be out of office next week.</t>
+          <t>A rule-based filter will miss new tricks.</t>
         </is>
       </c>
       <c r="K250" s="14" t="inlineStr"/>
       <c r="L250" s="36" t="inlineStr">
         <is>
-          <t>कार्यालय से बाहर</t>
+          <t>नियम-आधारित</t>
         </is>
       </c>
       <c r="M250" s="36" t="inlineStr">
         <is>
-          <t>काम से दूर, इसलिए कुछ समय तक जवाब नहीं दे सकते।</t>
+          <t>लोगों के लिखे तय नियमों के हिसाब से चलने वाला।</t>
         </is>
       </c>
       <c r="N250" s="37" t="inlineStr">
@@ -24220,42 +24220,42 @@
       <c r="R250" s="37" t="inlineStr"/>
       <c r="S250" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T250" s="39" t="inlineStr">
         <is>
-          <t>s:out-of-office</t>
+          <t>s:rule-based</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B251" s="34" t="inlineStr">
         <is>
-          <t>overtime</t>
+          <t>self-awareness</t>
         </is>
       </c>
       <c r="C251" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D251" s="14" t="inlineStr">
         <is>
-          <t>Extra hours you work beyond your normal hours.</t>
+          <t>Knowing your own feelings and how they affect what you do.</t>
         </is>
       </c>
       <c r="E251" s="14" t="inlineStr">
         <is>
-          <t>OH-ver-tym</t>
+          <t>self uh-WAIR-nus</t>
         </is>
       </c>
       <c r="F251" s="14" t="inlineStr">
         <is>
-          <t>/ˈəʊvətaɪm/</t>
+          <t>/ˌself əˈweənəs/</t>
         </is>
       </c>
       <c r="G251" s="14" t="inlineStr">
@@ -24265,28 +24265,28 @@
       </c>
       <c r="H251" s="14" t="inlineStr">
         <is>
-          <t>I did three hours of overtime yesterday.</t>
+          <t>Her self-awareness grew after the coaching.</t>
         </is>
       </c>
       <c r="I251" s="14" t="inlineStr">
         <is>
-          <t>Overtime is paid at a higher rate.</t>
+          <t>Self-awareness helps me notice when I am getting stressed.</t>
         </is>
       </c>
       <c r="J251" s="14" t="inlineStr">
         <is>
-          <t>We will need overtime during the launch.</t>
+          <t>More self-awareness will help you pause before you reply.</t>
         </is>
       </c>
       <c r="K251" s="14" t="inlineStr"/>
       <c r="L251" s="36" t="inlineStr">
         <is>
-          <t>ओवरटाइम, अतिरिक्त समय</t>
+          <t>आत्म-जागरूकता</t>
         </is>
       </c>
       <c r="M251" s="36" t="inlineStr">
         <is>
-          <t>सामान्य घंटों से ज़्यादा किया गया काम।</t>
+          <t>अपनी भावनाओं और उनके असर को पहचानना।</t>
         </is>
       </c>
       <c r="N251" s="37" t="inlineStr">
@@ -24310,42 +24310,42 @@
       <c r="R251" s="37" t="inlineStr"/>
       <c r="S251" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T251" s="39" t="inlineStr">
         <is>
-          <t>s:overtime</t>
+          <t>s:self-awareness</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B252" s="34" t="inlineStr">
         <is>
-          <t>paid time off</t>
+          <t>self-regulation</t>
         </is>
       </c>
       <c r="C252" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D252" s="14" t="inlineStr">
         <is>
-          <t>Days off when you still get paid. Often called PTO.</t>
+          <t>Controlling strong feelings so they don't take over.</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
         <is>
-          <t>payd tym OFF</t>
+          <t>self reg-yoo-LAY-shun</t>
         </is>
       </c>
       <c r="F252" s="14" t="inlineStr">
         <is>
-          <t>/peɪd taɪm ɒf/</t>
+          <t>/ˌself ˌreɡjuˈleɪʃn/</t>
         </is>
       </c>
       <c r="G252" s="14" t="inlineStr">
@@ -24355,28 +24355,28 @@
       </c>
       <c r="H252" s="14" t="inlineStr">
         <is>
-          <t>I used my paid time off for a family trip.</t>
+          <t>His self-regulation slipped during a long shift.</t>
         </is>
       </c>
       <c r="I252" s="14" t="inlineStr">
         <is>
-          <t>PTO includes holidays and sick days.</t>
+          <t>Self-regulation keeps me polite when a caller shouts.</t>
         </is>
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>New staff will get 22 days of paid time off.</t>
+          <t>Short breaks will help your self-regulation.</t>
         </is>
       </c>
       <c r="K252" s="14" t="inlineStr"/>
       <c r="L252" s="36" t="inlineStr">
         <is>
-          <t>वेतन सहित छुट्टी</t>
+          <t>आत्म-नियंत्रण</t>
         </is>
       </c>
       <c r="M252" s="36" t="inlineStr">
         <is>
-          <t>ऐसी छुट्टी जिसमें आपको फिर भी वेतन मिलता है।</t>
+          <t>तेज़ भावनाओं को काबू में रखना ताकि वे आप पर हावी न हों।</t>
         </is>
       </c>
       <c r="N252" s="37" t="inlineStr">
@@ -24400,24 +24400,24 @@
       <c r="R252" s="37" t="inlineStr"/>
       <c r="S252" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T252" s="39" t="inlineStr">
         <is>
-          <t>s:paid-time-off</t>
+          <t>s:self-regulation</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B253" s="34" t="inlineStr">
         <is>
-          <t>payslip</t>
+          <t>social skills</t>
         </is>
       </c>
       <c r="C253" s="35" t="n">
@@ -24425,17 +24425,17 @@
       </c>
       <c r="D253" s="14" t="inlineStr">
         <is>
-          <t>A document that shows your pay and what was taken off it. Also called a salary slip.</t>
+          <t>Skills for getting on well with people, like listening and solving disagreements.</t>
         </is>
       </c>
       <c r="E253" s="14" t="inlineStr">
         <is>
-          <t>PAY-slip</t>
+          <t>SOH-shul SKILZ</t>
         </is>
       </c>
       <c r="F253" s="14" t="inlineStr">
         <is>
-          <t>/ˈpeɪslɪp/</t>
+          <t>/ˈsəʊʃl skɪlz/</t>
         </is>
       </c>
       <c r="G253" s="14" t="inlineStr">
@@ -24445,28 +24445,28 @@
       </c>
       <c r="H253" s="14" t="inlineStr">
         <is>
-          <t>I downloaded my payslip yesterday.</t>
+          <t>She used her social skills to calm the meeting.</t>
         </is>
       </c>
       <c r="I253" s="14" t="inlineStr">
         <is>
-          <t>My payslip shows tax and overtime.</t>
+          <t>Social skills help you work well in a team.</t>
         </is>
       </c>
       <c r="J253" s="14" t="inlineStr">
         <is>
-          <t>You will get your payslip by email.</t>
+          <t>Training will build your social skills.</t>
         </is>
       </c>
       <c r="K253" s="14" t="inlineStr"/>
       <c r="L253" s="36" t="inlineStr">
         <is>
-          <t>वेतन पर्ची, सैलरी स्लिप</t>
+          <t>सामाजिक कौशल</t>
         </is>
       </c>
       <c r="M253" s="36" t="inlineStr">
         <is>
-          <t>वह दस्तावेज़ जिसमें आपका वेतन और कटौतियाँ दिखती हैं।</t>
+          <t>लोगों के साथ अच्छे से घुलने-मिलने के कौशल, जैसे सुनना और मतभेद सुलझाना।</t>
         </is>
       </c>
       <c r="N253" s="37" t="inlineStr">
@@ -24490,42 +24490,42 @@
       <c r="R253" s="37" t="inlineStr"/>
       <c r="S253" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T253" s="39" t="inlineStr">
         <is>
-          <t>s:payslip</t>
+          <t>s:social-skills</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B254" s="34" t="inlineStr">
         <is>
-          <t>performance review</t>
+          <t>superintelligence</t>
         </is>
       </c>
       <c r="C254" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D254" s="14" t="inlineStr">
         <is>
-          <t>A meeting where your manager talks about how well you did your job. Also called an appraisal.</t>
+          <t>A possible future AI that is smarter than humans in every field. Often called ASI.</t>
         </is>
       </c>
       <c r="E254" s="14" t="inlineStr">
         <is>
-          <t>per-FOR-muns ri-VYOO</t>
+          <t>soo-per-in-TEL-i-juns</t>
         </is>
       </c>
       <c r="F254" s="14" t="inlineStr">
         <is>
-          <t>/pəˈfɔːməns rɪˈvjuː/</t>
+          <t>/ˌsuːpərɪnˈtelɪdʒəns/</t>
         </is>
       </c>
       <c r="G254" s="14" t="inlineStr">
@@ -24535,28 +24535,28 @@
       </c>
       <c r="H254" s="14" t="inlineStr">
         <is>
-          <t>My performance review went well.</t>
+          <t>The article discussed superintelligence and its risks.</t>
         </is>
       </c>
       <c r="I254" s="14" t="inlineStr">
         <is>
-          <t>Performance reviews happen twice a year.</t>
+          <t>Superintelligence is a hypothetical idea.</t>
         </is>
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>We will set goals in your performance review.</t>
+          <t>Superintelligence will remain science fiction for now.</t>
         </is>
       </c>
       <c r="K254" s="14" t="inlineStr"/>
       <c r="L254" s="36" t="inlineStr">
         <is>
-          <t>कार्य मूल्यांकन</t>
+          <t>अति-बुद्धिमत्ता (ASI)</t>
         </is>
       </c>
       <c r="M254" s="36" t="inlineStr">
         <is>
-          <t>वह मीटिंग जिसमें मैनेजर आपके काम का मूल्यांकन करता है।</t>
+          <t>भविष्य की संभावित AI जो हर क्षेत्र में इंसानों से ज़्यादा समझदार हो।</t>
         </is>
       </c>
       <c r="N254" s="37" t="inlineStr">
@@ -24580,73 +24580,73 @@
       <c r="R254" s="37" t="inlineStr"/>
       <c r="S254" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai</t>
         </is>
       </c>
       <c r="T254" s="39" t="inlineStr">
         <is>
-          <t>s:performance-review</t>
+          <t>s:superintelligence</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B255" s="34" t="inlineStr">
         <is>
-          <t>permanent contract</t>
+          <t>surpass</t>
         </is>
       </c>
       <c r="C255" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D255" s="14" t="inlineStr">
         <is>
-          <t>A job contract with no end date.</t>
+          <t>To do better than someone or something.</t>
         </is>
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>PUR-muh-nunt KON-trakt</t>
+          <t>ser-PASS</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
         <is>
-          <t>/ˈpɜːmənənt ˈkɒntrækt/</t>
+          <t>/səˈpɑːs/</t>
         </is>
       </c>
       <c r="G255" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="H255" s="14" t="inlineStr">
         <is>
-          <t>He got a permanent contract after one year.</t>
+          <t>Sales surpassed the forecast in May.</t>
         </is>
       </c>
       <c r="I255" s="14" t="inlineStr">
         <is>
-          <t>She has a permanent contract now.</t>
+          <t>Our team often surpasses its CSAT target.</t>
         </is>
       </c>
       <c r="J255" s="14" t="inlineStr">
         <is>
-          <t>You will get a permanent contract after probation.</t>
+          <t>Some people say AI will surpass humans one day.</t>
         </is>
       </c>
       <c r="K255" s="14" t="inlineStr"/>
       <c r="L255" s="36" t="inlineStr">
         <is>
-          <t>स्थायी अनुबंध</t>
+          <t>पार करना, आगे निकलना</t>
         </is>
       </c>
       <c r="M255" s="36" t="inlineStr">
         <is>
-          <t>ऐसा नौकरी का अनुबंध जिसकी कोई अंतिम तारीख न हो।</t>
+          <t>किसी से बेहतर करना या आगे निकल जाना।</t>
         </is>
       </c>
       <c r="N255" s="37" t="inlineStr">
@@ -24670,73 +24670,73 @@
       <c r="R255" s="37" t="inlineStr"/>
       <c r="S255" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai</t>
         </is>
       </c>
       <c r="T255" s="39" t="inlineStr">
         <is>
-          <t>s:permanent-contract</t>
+          <t>s:surpass</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B256" s="34" t="inlineStr">
         <is>
-          <t>probation period</t>
+          <t>theoretical</t>
         </is>
       </c>
       <c r="C256" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D256" s="14" t="inlineStr">
         <is>
-          <t>The first months of a job when the company checks if you fit the role.</t>
+          <t>Based on ideas, not yet real or tested.</t>
         </is>
       </c>
       <c r="E256" s="14" t="inlineStr">
         <is>
-          <t>pruh-BAY-shun PEER-ee-ud</t>
+          <t>theer-RET-i-kul</t>
         </is>
       </c>
       <c r="F256" s="14" t="inlineStr">
         <is>
-          <t>/prəˈbeɪʃn ˈpɪəriəd/</t>
+          <t>/ˌθɪəˈretɪkl/</t>
         </is>
       </c>
       <c r="G256" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="H256" s="14" t="inlineStr">
         <is>
-          <t>He passed his probation period.</t>
+          <t>The risk was only theoretical at first.</t>
         </is>
       </c>
       <c r="I256" s="14" t="inlineStr">
         <is>
-          <t>My probation period is six months.</t>
+          <t>AGI is still theoretical.</t>
         </is>
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>Your probation period will end in March.</t>
+          <t>This plan will stay theoretical until we test it.</t>
         </is>
       </c>
       <c r="K256" s="14" t="inlineStr"/>
       <c r="L256" s="36" t="inlineStr">
         <is>
-          <t>परिवीक्षा अवधि</t>
+          <t>सैद्धांतिक</t>
         </is>
       </c>
       <c r="M256" s="36" t="inlineStr">
         <is>
-          <t>नौकरी के शुरुआती महीने जिनमें कंपनी देखती है कि आप काम के लिए सही हैं या नहीं।</t>
+          <t>विचारों पर आधारित, अभी असल में या जांचा हुआ नहीं।</t>
         </is>
       </c>
       <c r="N256" s="37" t="inlineStr">
@@ -24760,24 +24760,24 @@
       <c r="R256" s="37" t="inlineStr"/>
       <c r="S256" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai</t>
         </is>
       </c>
       <c r="T256" s="39" t="inlineStr">
         <is>
-          <t>s:probation-period</t>
+          <t>s:theoretical</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B257" s="34" t="inlineStr">
         <is>
-          <t>promotion</t>
+          <t>tone of voice</t>
         </is>
       </c>
       <c r="C257" s="35" t="n">
@@ -24785,17 +24785,17 @@
       </c>
       <c r="D257" s="14" t="inlineStr">
         <is>
-          <t>A move to a higher job with more responsibility.</t>
+          <t>The way your voice sounds, which shows your feelings.</t>
         </is>
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>pruh-MOH-shun</t>
+          <t>tohn uv VOYS</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">
         <is>
-          <t>/prəˈməʊʃn/</t>
+          <t>/təʊn əv vɔɪs/</t>
         </is>
       </c>
       <c r="G257" s="14" t="inlineStr">
@@ -24805,28 +24805,28 @@
       </c>
       <c r="H257" s="14" t="inlineStr">
         <is>
-          <t>She got a promotion to team lead.</t>
+          <t>Her tone of voice calmed the angry customer.</t>
         </is>
       </c>
       <c r="I257" s="14" t="inlineStr">
         <is>
-          <t>A promotion usually comes with a raise.</t>
+          <t>Your tone of voice matters as much as your words.</t>
         </is>
       </c>
       <c r="J257" s="14" t="inlineStr">
         <is>
-          <t>I will apply for the promotion.</t>
+          <t>A warm tone of voice will help on every call.</t>
         </is>
       </c>
       <c r="K257" s="14" t="inlineStr"/>
       <c r="L257" s="36" t="inlineStr">
         <is>
-          <t>पदोन्नति, प्रमोशन</t>
+          <t>आवाज़ का लहजा</t>
         </is>
       </c>
       <c r="M257" s="36" t="inlineStr">
         <is>
-          <t>ज़्यादा ज़िम्मेदारी वाले ऊँचे पद पर जाना।</t>
+          <t>आपकी आवाज़ कैसी लगती है, जिससे आपकी भावना दिखती है।</t>
         </is>
       </c>
       <c r="N257" s="37" t="inlineStr">
@@ -24850,42 +24850,42 @@
       <c r="R257" s="37" t="inlineStr"/>
       <c r="S257" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,cs,comm</t>
         </is>
       </c>
       <c r="T257" s="39" t="inlineStr">
         <is>
-          <t>s:promotion</t>
+          <t>s:tone-of-voice</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B258" s="34" t="inlineStr">
         <is>
-          <t>public holiday</t>
+          <t>Turing Test</t>
         </is>
       </c>
       <c r="C258" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D258" s="14" t="inlineStr">
         <is>
-          <t>A day off for the whole country.</t>
+          <t>A test from 1950: can a machine chat so well that a person thinks it is human?</t>
         </is>
       </c>
       <c r="E258" s="14" t="inlineStr">
         <is>
-          <t>PUB-lik HOL-uh-day</t>
+          <t>TYOOR-ing test</t>
         </is>
       </c>
       <c r="F258" s="14" t="inlineStr">
         <is>
-          <t>/ˌpʌblɪk ˈhɒlədeɪ/</t>
+          <t>/ˈtjʊərɪŋ test/</t>
         </is>
       </c>
       <c r="G258" s="14" t="inlineStr">
@@ -24895,28 +24895,28 @@
       </c>
       <c r="H258" s="14" t="inlineStr">
         <is>
-          <t>We worked on the public holiday.</t>
+          <t>Alan Turing proposed the Turing Test in 1950.</t>
         </is>
       </c>
       <c r="I258" s="14" t="inlineStr">
         <is>
-          <t>Monday is a public holiday in Portugal.</t>
+          <t>The Turing Test asks if a machine can pass as human.</t>
         </is>
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>The office will close on the public holiday.</t>
+          <t>Some chatbots will pass the Turing Test in short chats.</t>
         </is>
       </c>
       <c r="K258" s="14" t="inlineStr"/>
       <c r="L258" s="36" t="inlineStr">
         <is>
-          <t>सार्वजनिक अवकाश</t>
+          <t>ट्यूरिंग टेस्ट</t>
         </is>
       </c>
       <c r="M258" s="36" t="inlineStr">
         <is>
-          <t>वह दिन जब पूरे देश में छुट्टी होती है।</t>
+          <t>1950 का परीक्षण: क्या मशीन इतनी अच्छी बात कर सकती है कि इंसान उसे इंसान समझे?</t>
         </is>
       </c>
       <c r="N258" s="37" t="inlineStr">
@@ -24940,73 +24940,73 @@
       <c r="R258" s="37" t="inlineStr"/>
       <c r="S258" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>training,ai,tech</t>
         </is>
       </c>
       <c r="T258" s="39" t="inlineStr">
         <is>
-          <t>s:public-holiday</t>
+          <t>s:turing-test</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>TP training</t>
         </is>
       </c>
       <c r="B259" s="34" t="inlineStr">
         <is>
-          <t>reschedule</t>
+          <t>versatile</t>
         </is>
       </c>
       <c r="C259" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D259" s="14" t="inlineStr">
         <is>
-          <t>To move a meeting or task to a new time.</t>
+          <t>Able to do many different things well.</t>
         </is>
       </c>
       <c r="E259" s="14" t="inlineStr">
         <is>
-          <t>ree-SHED-yool</t>
+          <t>VUR-suh-tyl</t>
         </is>
       </c>
       <c r="F259" s="14" t="inlineStr">
         <is>
-          <t>/ˌriːˈʃedjuːl/</t>
+          <t>/ˈvɜːsətaɪl/</t>
         </is>
       </c>
       <c r="G259" s="14" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="H259" s="14" t="inlineStr">
         <is>
-          <t>She rescheduled the training to Tuesday.</t>
+          <t>She was versatile and covered chat and email.</t>
         </is>
       </c>
       <c r="I259" s="14" t="inlineStr">
         <is>
-          <t>Can we reschedule our call?</t>
+          <t>ChatGPT is versatile but still narrow AI.</t>
         </is>
       </c>
       <c r="J259" s="14" t="inlineStr">
         <is>
-          <t>I will reschedule the meeting for next week.</t>
+          <t>A versatile agent will handle any queue.</t>
         </is>
       </c>
       <c r="K259" s="14" t="inlineStr"/>
       <c r="L259" s="36" t="inlineStr">
         <is>
-          <t>समय बदलना</t>
+          <t>बहुमुखी</t>
         </is>
       </c>
       <c r="M259" s="36" t="inlineStr">
         <is>
-          <t>मीटिंग या काम को नए समय पर रखना।</t>
+          <t>कई अलग-अलग काम अच्छे से कर सकने वाला।</t>
         </is>
       </c>
       <c r="N259" s="37" t="inlineStr">
@@ -25030,42 +25030,42 @@
       <c r="R259" s="37" t="inlineStr"/>
       <c r="S259" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>training,ai,cs</t>
         </is>
       </c>
       <c r="T259" s="39" t="inlineStr">
         <is>
-          <t>s:reschedule</t>
+          <t>s:versatile</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B260" s="34" t="inlineStr">
         <is>
-          <t>resign</t>
+          <t>authenticate</t>
         </is>
       </c>
       <c r="C260" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D260" s="14" t="inlineStr">
         <is>
-          <t>To tell your employer you are leaving your job.</t>
+          <t>To prove who you are, for example with a code or password.</t>
         </is>
       </c>
       <c r="E260" s="14" t="inlineStr">
         <is>
-          <t>ri-ZYN</t>
+          <t>aw-THEN-ti-kayt</t>
         </is>
       </c>
       <c r="F260" s="14" t="inlineStr">
         <is>
-          <t>/rɪˈzaɪn/</t>
+          <t>/ɔːˈθentɪkeɪt/</t>
         </is>
       </c>
       <c r="G260" s="14" t="inlineStr">
@@ -25075,28 +25075,28 @@
       </c>
       <c r="H260" s="14" t="inlineStr">
         <is>
-          <t>He resigned to start his own business.</t>
+          <t>He authenticated his account using Google.</t>
         </is>
       </c>
       <c r="I260" s="14" t="inlineStr">
         <is>
-          <t>Many people resign in January.</t>
+          <t>Users authenticate with a code sent to their phone.</t>
         </is>
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>I will resign after I get the new offer.</t>
+          <t>You will need to authenticate again after the update.</t>
         </is>
       </c>
       <c r="K260" s="14" t="inlineStr"/>
       <c r="L260" s="36" t="inlineStr">
         <is>
-          <t>इस्तीफ़ा देना</t>
+          <t>प्रमाणित करना</t>
         </is>
       </c>
       <c r="M260" s="36" t="inlineStr">
         <is>
-          <t>अपने नियोक्ता को बताना कि आप नौकरी छोड़ रहे हैं।</t>
+          <t>साबित करना कि आप वही हैं जो आप कहते हैं, जैसे कोड या पासवर्ड से।</t>
         </is>
       </c>
       <c r="N260" s="37" t="inlineStr">
@@ -25120,24 +25120,24 @@
       <c r="R260" s="37" t="inlineStr"/>
       <c r="S260" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="T260" s="39" t="inlineStr">
         <is>
-          <t>s:resign</t>
+          <t>s:authenticate</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B261" s="34" t="inlineStr">
         <is>
-          <t>roster</t>
+          <t>bug report</t>
         </is>
       </c>
       <c r="C261" s="35" t="n">
@@ -25145,17 +25145,17 @@
       </c>
       <c r="D261" s="14" t="inlineStr">
         <is>
-          <t>A list showing who works on which days and shifts.</t>
+          <t>A message telling the tech team about a problem in the product.</t>
         </is>
       </c>
       <c r="E261" s="14" t="inlineStr">
         <is>
-          <t>ROS-ter</t>
+          <t>bug ri-PORT</t>
         </is>
       </c>
       <c r="F261" s="14" t="inlineStr">
         <is>
-          <t>/ˈrɒstə/</t>
+          <t>/bʌɡ rɪˈpɔːt/</t>
         </is>
       </c>
       <c r="G261" s="14" t="inlineStr">
@@ -25165,28 +25165,28 @@
       </c>
       <c r="H261" s="14" t="inlineStr">
         <is>
-          <t>My manager changed the roster.</t>
+          <t>I filed a bug report this morning.</t>
         </is>
       </c>
       <c r="I261" s="14" t="inlineStr">
         <is>
-          <t>The new roster is out.</t>
+          <t>A good bug report has clear steps.</t>
         </is>
       </c>
       <c r="J261" s="14" t="inlineStr">
         <is>
-          <t>I will check the roster for next month.</t>
+          <t>The team will read your bug report today.</t>
         </is>
       </c>
       <c r="K261" s="14" t="inlineStr"/>
       <c r="L261" s="36" t="inlineStr">
         <is>
-          <t>ड्यूटी सूची, रोस्टर</t>
+          <t>बग रिपोर्ट, गड़बड़ी की रिपोर्ट</t>
         </is>
       </c>
       <c r="M261" s="36" t="inlineStr">
         <is>
-          <t>यह सूची कि कौन किस दिन और किस पारी में काम करेगा।</t>
+          <t>प्रोडक्ट की समस्या के बारे में टेक टीम को भेजा गया संदेश।</t>
         </is>
       </c>
       <c r="N261" s="37" t="inlineStr">
@@ -25210,73 +25210,73 @@
       <c r="R261" s="37" t="inlineStr"/>
       <c r="S261" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech,cs</t>
         </is>
       </c>
       <c r="T261" s="39" t="inlineStr">
         <is>
-          <t>s:roster</t>
+          <t>s:bug-report</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B262" s="34" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>clear the cache</t>
         </is>
       </c>
       <c r="C262" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D262" s="14" t="inlineStr">
         <is>
-          <t>The fixed money you get for your job, usually every month.</t>
+          <t>To delete saved website data so a page loads fresh.</t>
         </is>
       </c>
       <c r="E262" s="14" t="inlineStr">
         <is>
-          <t>SAL-uh-ree</t>
+          <t>kleer thuh KASH</t>
         </is>
       </c>
       <c r="F262" s="14" t="inlineStr">
         <is>
-          <t>/ˈsæləri/</t>
+          <t>/klɪə ðə kæʃ/</t>
         </is>
       </c>
       <c r="G262" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="H262" s="14" t="inlineStr">
         <is>
-          <t>Her salary went up last year.</t>
+          <t>She cleared the cache and it worked.</t>
         </is>
       </c>
       <c r="I262" s="14" t="inlineStr">
         <is>
-          <t>The salary is paid monthly.</t>
+          <t>Try to clear the cache and reload the page.</t>
         </is>
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>We will discuss salary in the next round.</t>
+          <t>You will need to clear the cache after the update.</t>
         </is>
       </c>
       <c r="K262" s="14" t="inlineStr"/>
       <c r="L262" s="36" t="inlineStr">
         <is>
-          <t>वेतन, तनख्वाह</t>
+          <t>कैश साफ़ करना</t>
         </is>
       </c>
       <c r="M262" s="36" t="inlineStr">
         <is>
-          <t>नौकरी के लिए हर महीने मिलने वाला तय पैसा।</t>
+          <t>ब्राउज़र में सेव डेटा हटाना ताकि पेज नए सिरे से खुले।</t>
         </is>
       </c>
       <c r="N262" s="37" t="inlineStr">
@@ -25300,73 +25300,73 @@
       <c r="R262" s="37" t="inlineStr"/>
       <c r="S262" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="T262" s="39" t="inlineStr">
         <is>
-          <t>s:salary</t>
+          <t>s:clear-the-cache</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B263" s="34" t="inlineStr">
         <is>
-          <t>screen share</t>
+          <t>credentials</t>
         </is>
       </c>
       <c r="C263" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D263" s="14" t="inlineStr">
         <is>
-          <t>To show your computer screen to others on a call.</t>
+          <t>Login details like your email and password.</t>
         </is>
       </c>
       <c r="E263" s="14" t="inlineStr">
         <is>
-          <t>SKREEN shair</t>
+          <t>kruh-DEN-shulz</t>
         </is>
       </c>
       <c r="F263" s="14" t="inlineStr">
         <is>
-          <t>/skriːn ʃeə/</t>
+          <t>/krəˈdenʃlz/</t>
         </is>
       </c>
       <c r="G263" s="14" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="H263" s="14" t="inlineStr">
         <is>
-          <t>He screen shared his dashboard.</t>
+          <t>She entered the wrong credentials three times.</t>
         </is>
       </c>
       <c r="I263" s="14" t="inlineStr">
         <is>
-          <t>Can you screen share the report?</t>
+          <t>Never share your credentials with anyone.</t>
         </is>
       </c>
       <c r="J263" s="14" t="inlineStr">
         <is>
-          <t>I will screen share the steps.</t>
+          <t>You will get new credentials by email.</t>
         </is>
       </c>
       <c r="K263" s="14" t="inlineStr"/>
       <c r="L263" s="36" t="inlineStr">
         <is>
-          <t>स्क्रीन शेयर करना</t>
+          <t>लॉगिन विवरण</t>
         </is>
       </c>
       <c r="M263" s="36" t="inlineStr">
         <is>
-          <t>कॉल पर अपनी कंप्यूटर स्क्रीन दूसरों को दिखाना।</t>
+          <t>लॉगिन करने की जानकारी, जैसे ईमेल और पासवर्ड।</t>
         </is>
       </c>
       <c r="N263" s="37" t="inlineStr">
@@ -25390,42 +25390,42 @@
       <c r="R263" s="37" t="inlineStr"/>
       <c r="S263" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="T263" s="39" t="inlineStr">
         <is>
-          <t>s:screen-share</t>
+          <t>s:credentials</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B264" s="34" t="inlineStr">
         <is>
-          <t>shift</t>
+          <t>data privacy</t>
         </is>
       </c>
       <c r="C264" s="35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D264" s="14" t="inlineStr">
         <is>
-          <t>A set block of working hours, like morning or night.</t>
+          <t>Keeping people's personal information safe and private.</t>
         </is>
       </c>
       <c r="E264" s="14" t="inlineStr">
         <is>
-          <t>shift</t>
+          <t>DAY-tuh PRIV-uh-see</t>
         </is>
       </c>
       <c r="F264" s="14" t="inlineStr">
         <is>
-          <t>/ʃɪft/</t>
+          <t>/ˈdeɪtə ˈprɪvəsi/</t>
         </is>
       </c>
       <c r="G264" s="14" t="inlineStr">
@@ -25435,28 +25435,28 @@
       </c>
       <c r="H264" s="14" t="inlineStr">
         <is>
-          <t>Her shift ended late.</t>
+          <t>The training covered data privacy.</t>
         </is>
       </c>
       <c r="I264" s="14" t="inlineStr">
         <is>
-          <t>My shift starts at 8 a.m.</t>
+          <t>Data privacy rules are strict in Europe.</t>
         </is>
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>I will be on the night shift next week.</t>
+          <t>We will never break data privacy rules.</t>
         </is>
       </c>
       <c r="K264" s="14" t="inlineStr"/>
       <c r="L264" s="36" t="inlineStr">
         <is>
-          <t>पारी, शिफ्ट</t>
+          <t>डेटा गोपनीयता</t>
         </is>
       </c>
       <c r="M264" s="36" t="inlineStr">
         <is>
-          <t>काम के तय घंटे, जैसे सुबह या रात की पारी।</t>
+          <t>लोगों की निजी जानकारी को सुरक्षित और गोपनीय रखना।</t>
         </is>
       </c>
       <c r="N264" s="37" t="inlineStr">
@@ -25480,73 +25480,73 @@
       <c r="R264" s="37" t="inlineStr"/>
       <c r="S264" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech,corp</t>
         </is>
       </c>
       <c r="T264" s="39" t="inlineStr">
         <is>
-          <t>s:shift</t>
+          <t>s:data-privacy</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B265" s="34" t="inlineStr">
         <is>
-          <t>sick leave</t>
+          <t>deactivate</t>
         </is>
       </c>
       <c r="C265" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D265" s="14" t="inlineStr">
         <is>
-          <t>Time off work because you are ill. One day off is a sick day.</t>
+          <t>To turn off an account or feature.</t>
         </is>
       </c>
       <c r="E265" s="14" t="inlineStr">
         <is>
-          <t>sik LEEV</t>
+          <t>dee-AK-ti-vayt</t>
         </is>
       </c>
       <c r="F265" s="14" t="inlineStr">
         <is>
-          <t>/sɪk liːv/</t>
+          <t>/diˈæktɪveɪt/</t>
         </is>
       </c>
       <c r="G265" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="H265" s="14" t="inlineStr">
         <is>
-          <t>He took two sick days last week.</t>
+          <t>She deactivated the old account.</t>
         </is>
       </c>
       <c r="I265" s="14" t="inlineStr">
         <is>
-          <t>I'm on sick leave today.</t>
+          <t>You can deactivate your account in settings.</t>
         </is>
       </c>
       <c r="J265" s="14" t="inlineStr">
         <is>
-          <t>You will need a doctor's note for long sick leave.</t>
+          <t>We will deactivate the feature tonight.</t>
         </is>
       </c>
       <c r="K265" s="14" t="inlineStr"/>
       <c r="L265" s="36" t="inlineStr">
         <is>
-          <t>बीमारी की छुट्टी</t>
+          <t>निष्क्रिय करना</t>
         </is>
       </c>
       <c r="M265" s="36" t="inlineStr">
         <is>
-          <t>बीमार होने पर काम से ली गई छुट्टी।</t>
+          <t>किसी खाते या फीचर को बंद करना।</t>
         </is>
       </c>
       <c r="N265" s="37" t="inlineStr">
@@ -25570,73 +25570,73 @@
       <c r="R265" s="37" t="inlineStr"/>
       <c r="S265" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech,cs</t>
         </is>
       </c>
       <c r="T265" s="39" t="inlineStr">
         <is>
-          <t>s:sick-leave</t>
+          <t>s:deactivate</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B266" s="34" t="inlineStr">
         <is>
-          <t>take notes</t>
+          <t>deprecate</t>
         </is>
       </c>
       <c r="C266" s="35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D266" s="14" t="inlineStr">
         <is>
-          <t>To write down the main points while someone speaks.</t>
+          <t>To mark an old feature as no longer supported.</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
         <is>
-          <t>tayk NOHTS</t>
+          <t>DEP-ruh-kayt</t>
         </is>
       </c>
       <c r="F266" s="14" t="inlineStr">
         <is>
-          <t>/teɪk nəʊts/</t>
+          <t>/ˈdeprəkeɪt/</t>
         </is>
       </c>
       <c r="G266" s="14" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="H266" s="14" t="inlineStr">
         <is>
-          <t>She took notes for the whole team.</t>
+          <t>They deprecated the old API last year.</t>
         </is>
       </c>
       <c r="I266" s="14" t="inlineStr">
         <is>
-          <t>I take notes in every meeting.</t>
+          <t>The company deprecates old models over time.</t>
         </is>
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>Who will take notes today?</t>
+          <t>This feature will be deprecated in March.</t>
         </is>
       </c>
       <c r="K266" s="14" t="inlineStr"/>
       <c r="L266" s="36" t="inlineStr">
         <is>
-          <t>नोट्स लिखना</t>
+          <t>बंद करने के लिए चिह्नित करना</t>
         </is>
       </c>
       <c r="M266" s="36" t="inlineStr">
         <is>
-          <t>बातचीत के मुख्य बिंदु लिख लेना।</t>
+          <t>किसी पुराने फीचर को धीरे-धीरे बंद करने की घोषणा करना।</t>
         </is>
       </c>
       <c r="N266" s="37" t="inlineStr">
@@ -25660,24 +25660,24 @@
       <c r="R266" s="37" t="inlineStr"/>
       <c r="S266" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>tech,ai</t>
         </is>
       </c>
       <c r="T266" s="39" t="inlineStr">
         <is>
-          <t>s:take-notes</t>
+          <t>s:deprecate</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B267" s="34" t="inlineStr">
         <is>
-          <t>team lead</t>
+          <t>error message</t>
         </is>
       </c>
       <c r="C267" s="35" t="n">
@@ -25685,17 +25685,17 @@
       </c>
       <c r="D267" s="14" t="inlineStr">
         <is>
-          <t>The person who guides a small team day to day.</t>
+          <t>Text on the screen that says something went wrong.</t>
         </is>
       </c>
       <c r="E267" s="14" t="inlineStr">
         <is>
-          <t>teem LEED</t>
+          <t>ER-er MES-ij</t>
         </is>
       </c>
       <c r="F267" s="14" t="inlineStr">
         <is>
-          <t>/tiːm liːd/</t>
+          <t>/ˈerə ˈmesɪdʒ/</t>
         </is>
       </c>
       <c r="G267" s="14" t="inlineStr">
@@ -25705,28 +25705,28 @@
       </c>
       <c r="H267" s="14" t="inlineStr">
         <is>
-          <t>The team lead ran the morning huddle.</t>
+          <t>The error message appeared after login.</t>
         </is>
       </c>
       <c r="I267" s="14" t="inlineStr">
         <is>
-          <t>My team lead checks my tickets.</t>
+          <t>What does the error message say?</t>
         </is>
       </c>
       <c r="J267" s="14" t="inlineStr">
         <is>
-          <t>The team lead will update the roster.</t>
+          <t>The fix will remove this error message.</t>
         </is>
       </c>
       <c r="K267" s="14" t="inlineStr"/>
       <c r="L267" s="36" t="inlineStr">
         <is>
-          <t>टीम प्रमुख</t>
+          <t>त्रुटि संदेश</t>
         </is>
       </c>
       <c r="M267" s="36" t="inlineStr">
         <is>
-          <t>वह व्यक्ति जो रोज़ एक छोटी टीम का मार्गदर्शन करता है।</t>
+          <t>स्क्रीन पर दिखने वाला संदेश कि कुछ गलत हुआ है।</t>
         </is>
       </c>
       <c r="N267" s="37" t="inlineStr">
@@ -25750,42 +25750,42 @@
       <c r="R267" s="37" t="inlineStr"/>
       <c r="S267" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="T267" s="39" t="inlineStr">
         <is>
-          <t>s:team-lead</t>
+          <t>s:error-message</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B268" s="34" t="inlineStr">
         <is>
-          <t>termination</t>
+          <t>feature request</t>
         </is>
       </c>
       <c r="C268" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D268" s="14" t="inlineStr">
         <is>
-          <t>The end of someone's job, decided by the company.</t>
+          <t>A customer's idea for something new the product should do.</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
         <is>
-          <t>tur-mi-NAY-shun</t>
+          <t>FEE-cher ri-KWEST</t>
         </is>
       </c>
       <c r="F268" s="14" t="inlineStr">
         <is>
-          <t>/ˌtɜːmɪˈneɪʃn/</t>
+          <t>/ˈfiːtʃə rɪˈkwest/</t>
         </is>
       </c>
       <c r="G268" s="14" t="inlineStr">
@@ -25795,28 +25795,28 @@
       </c>
       <c r="H268" s="14" t="inlineStr">
         <is>
-          <t>His termination was a surprise.</t>
+          <t>I logged his feature request for the product team.</t>
         </is>
       </c>
       <c r="I268" s="14" t="inlineStr">
         <is>
-          <t>Termination needs a written reason.</t>
+          <t>Many users send the same feature request.</t>
         </is>
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>Breaking the rules will lead to termination.</t>
+          <t>The product team will review feature requests in June.</t>
         </is>
       </c>
       <c r="K268" s="14" t="inlineStr"/>
       <c r="L268" s="36" t="inlineStr">
         <is>
-          <t>बर्खास्तगी, नौकरी समाप्ति</t>
+          <t>नई सुविधा का अनुरोध</t>
         </is>
       </c>
       <c r="M268" s="36" t="inlineStr">
         <is>
-          <t>कंपनी द्वारा किसी की नौकरी खत्म करना।</t>
+          <t>ग्राहक का सुझाव कि प्रोडक्ट में कोई नई चीज़ जोड़ी जाए।</t>
         </is>
       </c>
       <c r="N268" s="37" t="inlineStr">
@@ -25840,24 +25840,24 @@
       <c r="R268" s="37" t="inlineStr"/>
       <c r="S268" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech,cs</t>
         </is>
       </c>
       <c r="T268" s="39" t="inlineStr">
         <is>
-          <t>s:termination</t>
+          <t>s:feature-request</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B269" s="34" t="inlineStr">
         <is>
-          <t>timesheet</t>
+          <t>glitch</t>
         </is>
       </c>
       <c r="C269" s="35" t="n">
@@ -25865,17 +25865,17 @@
       </c>
       <c r="D269" s="14" t="inlineStr">
         <is>
-          <t>A record of the hours you worked.</t>
+          <t>A small, short problem in a system.</t>
         </is>
       </c>
       <c r="E269" s="14" t="inlineStr">
         <is>
-          <t>TYM-sheet</t>
+          <t>glich</t>
         </is>
       </c>
       <c r="F269" s="14" t="inlineStr">
         <is>
-          <t>/ˈtaɪmʃiːt/</t>
+          <t>/ɡlɪtʃ/</t>
         </is>
       </c>
       <c r="G269" s="14" t="inlineStr">
@@ -25885,28 +25885,28 @@
       </c>
       <c r="H269" s="14" t="inlineStr">
         <is>
-          <t>He forgot to submit his timesheet.</t>
+          <t>The glitch stopped after the restart.</t>
         </is>
       </c>
       <c r="I269" s="14" t="inlineStr">
         <is>
-          <t>I fill in my timesheet every Friday.</t>
+          <t>A glitch sometimes logs users out.</t>
         </is>
       </c>
       <c r="J269" s="14" t="inlineStr">
         <is>
-          <t>Your overtime will show on the timesheet.</t>
+          <t>This glitch will be fixed in the next update.</t>
         </is>
       </c>
       <c r="K269" s="14" t="inlineStr"/>
       <c r="L269" s="36" t="inlineStr">
         <is>
-          <t>समय-पत्रक</t>
+          <t>छोटी तकनीकी गड़बड़ी</t>
         </is>
       </c>
       <c r="M269" s="36" t="inlineStr">
         <is>
-          <t>आपके काम किए गए घंटों का रिकॉर्ड।</t>
+          <t>सिस्टम में थोड़ी देर की छोटी खराबी।</t>
         </is>
       </c>
       <c r="N269" s="37" t="inlineStr">
@@ -25930,73 +25930,73 @@
       <c r="R269" s="37" t="inlineStr"/>
       <c r="S269" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="T269" s="39" t="inlineStr">
         <is>
-          <t>s:timesheet</t>
+          <t>s:glitch</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B270" s="34" t="inlineStr">
         <is>
-          <t>trainee</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="C270" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D270" s="14" t="inlineStr">
         <is>
-          <t>A new person who is learning the job.</t>
+          <t>Stopping and starting again, not happening all the time.</t>
         </is>
       </c>
       <c r="E270" s="14" t="inlineStr">
         <is>
-          <t>tray-NEE</t>
+          <t>in-ter-MIT-unt</t>
         </is>
       </c>
       <c r="F270" s="14" t="inlineStr">
         <is>
-          <t>/ˌtreɪˈniː/</t>
+          <t>/ˌɪntəˈmɪtənt/</t>
         </is>
       </c>
       <c r="G270" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="H270" s="14" t="inlineStr">
         <is>
-          <t>I was a trainee last year.</t>
+          <t>The errors were intermittent all morning.</t>
         </is>
       </c>
       <c r="I270" s="14" t="inlineStr">
         <is>
-          <t>Each trainee sits with a senior agent.</t>
+          <t>The user has intermittent connection problems.</t>
         </is>
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>The trainees will take calls next week.</t>
+          <t>Intermittent issues will be harder to track.</t>
         </is>
       </c>
       <c r="K270" s="14" t="inlineStr"/>
       <c r="L270" s="36" t="inlineStr">
         <is>
-          <t>प्रशिक्षु</t>
+          <t>रुक-रुककर होने वाला</t>
         </is>
       </c>
       <c r="M270" s="36" t="inlineStr">
         <is>
-          <t>वह नया व्यक्ति जो काम सीख रहा है।</t>
+          <t>जो लगातार न होकर बीच-बीच में होता है।</t>
         </is>
       </c>
       <c r="N270" s="37" t="inlineStr">
@@ -26020,42 +26020,42 @@
       <c r="R270" s="37" t="inlineStr"/>
       <c r="S270" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="T270" s="39" t="inlineStr">
         <is>
-          <t>s:trainee</t>
+          <t>s:intermittent</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B271" s="34" t="inlineStr">
         <is>
-          <t>trainer</t>
+          <t>latency</t>
         </is>
       </c>
       <c r="C271" s="35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D271" s="14" t="inlineStr">
         <is>
-          <t>The person who teaches new staff how to do the job.</t>
+          <t>The delay before a system responds.</t>
         </is>
       </c>
       <c r="E271" s="14" t="inlineStr">
         <is>
-          <t>TRAY-ner</t>
+          <t>LAY-tun-see</t>
         </is>
       </c>
       <c r="F271" s="14" t="inlineStr">
         <is>
-          <t>/ˈtreɪnə/</t>
+          <t>/ˈleɪtənsi/</t>
         </is>
       </c>
       <c r="G271" s="14" t="inlineStr">
@@ -26065,28 +26065,28 @@
       </c>
       <c r="H271" s="14" t="inlineStr">
         <is>
-          <t>The trainer gave us a quiz.</t>
+          <t>Latency was higher during the update.</t>
         </is>
       </c>
       <c r="I271" s="14" t="inlineStr">
         <is>
-          <t>Our trainer explains each tool.</t>
+          <t>High latency makes the chat feel slow.</t>
         </is>
       </c>
       <c r="J271" s="14" t="inlineStr">
         <is>
-          <t>Your trainer will meet you at nine.</t>
+          <t>The fix will reduce latency.</t>
         </is>
       </c>
       <c r="K271" s="14" t="inlineStr"/>
       <c r="L271" s="36" t="inlineStr">
         <is>
-          <t>प्रशिक्षक, ट्रेनर</t>
+          <t>विलंब, देरी</t>
         </is>
       </c>
       <c r="M271" s="36" t="inlineStr">
         <is>
-          <t>वह व्यक्ति जो नए कर्मचारियों को काम सिखाता है।</t>
+          <t>सिस्टम के जवाब देने से पहले होने वाली देरी।</t>
         </is>
       </c>
       <c r="N271" s="37" t="inlineStr">
@@ -26110,24 +26110,24 @@
       <c r="R271" s="37" t="inlineStr"/>
       <c r="S271" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="T271" s="39" t="inlineStr">
         <is>
-          <t>s:trainer</t>
+          <t>s:latency</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B272" s="34" t="inlineStr">
         <is>
-          <t>training period</t>
+          <t>limitation</t>
         </is>
       </c>
       <c r="C272" s="35" t="n">
@@ -26135,17 +26135,17 @@
       </c>
       <c r="D272" s="14" t="inlineStr">
         <is>
-          <t>The time when new staff learn the job before working alone.</t>
+          <t>Something a product or person cannot do.</t>
         </is>
       </c>
       <c r="E272" s="14" t="inlineStr">
         <is>
-          <t>TRAY-ning PEER-ee-ud</t>
+          <t>lim-i-TAY-shun</t>
         </is>
       </c>
       <c r="F272" s="14" t="inlineStr">
         <is>
-          <t>/ˈtreɪnɪŋ ˈpɪəriəd/</t>
+          <t>/ˌlɪmɪˈteɪʃn/</t>
         </is>
       </c>
       <c r="G272" s="14" t="inlineStr">
@@ -26155,28 +26155,28 @@
       </c>
       <c r="H272" s="14" t="inlineStr">
         <is>
-          <t>I learned a lot in my training period.</t>
+          <t>We explained the limitation to the user.</t>
         </is>
       </c>
       <c r="I272" s="14" t="inlineStr">
         <is>
-          <t>The training period lasts four weeks.</t>
+          <t>This is a known limitation of the model.</t>
         </is>
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>You will be paid during the training period.</t>
+          <t>The new version will remove this limitation.</t>
         </is>
       </c>
       <c r="K272" s="14" t="inlineStr"/>
       <c r="L272" s="36" t="inlineStr">
         <is>
-          <t>प्रशिक्षण अवधि</t>
+          <t>सीमा, कमी</t>
         </is>
       </c>
       <c r="M272" s="36" t="inlineStr">
         <is>
-          <t>वह समय जब नए कर्मचारी अकेले काम करने से पहले काम सीखते हैं।</t>
+          <t>कोई चीज़ जो प्रोडक्ट या व्यक्ति नहीं कर सकता।</t>
         </is>
       </c>
       <c r="N272" s="37" t="inlineStr">
@@ -26200,24 +26200,24 @@
       <c r="R272" s="37" t="inlineStr"/>
       <c r="S272" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech,ai</t>
         </is>
       </c>
       <c r="T272" s="39" t="inlineStr">
         <is>
-          <t>s:training-period</t>
+          <t>s:limitation</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B273" s="34" t="inlineStr">
         <is>
-          <t>unpaid leave</t>
+          <t>outage</t>
         </is>
       </c>
       <c r="C273" s="35" t="n">
@@ -26225,17 +26225,17 @@
       </c>
       <c r="D273" s="14" t="inlineStr">
         <is>
-          <t>Time off work without pay.</t>
+          <t>A time when a service stops working.</t>
         </is>
       </c>
       <c r="E273" s="14" t="inlineStr">
         <is>
-          <t>un-PAYD leev</t>
+          <t>OW-tij</t>
         </is>
       </c>
       <c r="F273" s="14" t="inlineStr">
         <is>
-          <t>/ʌnˈpeɪd liːv/</t>
+          <t>/ˈaʊtɪdʒ/</t>
         </is>
       </c>
       <c r="G273" s="14" t="inlineStr">
@@ -26245,28 +26245,28 @@
       </c>
       <c r="H273" s="14" t="inlineStr">
         <is>
-          <t>She took unpaid leave to move house.</t>
+          <t>The outage lasted two hours.</t>
         </is>
       </c>
       <c r="I273" s="14" t="inlineStr">
         <is>
-          <t>He is asking for a week of unpaid leave.</t>
+          <t>There is an outage in Europe right now.</t>
         </is>
       </c>
       <c r="J273" s="14" t="inlineStr">
         <is>
-          <t>Unpaid leave will not affect your contract.</t>
+          <t>We will post an update if there is another outage.</t>
         </is>
       </c>
       <c r="K273" s="14" t="inlineStr"/>
       <c r="L273" s="36" t="inlineStr">
         <is>
-          <t>बिना वेतन की छुट्टी</t>
+          <t>सेवा ठप होना, आउटेज</t>
         </is>
       </c>
       <c r="M273" s="36" t="inlineStr">
         <is>
-          <t>ऐसी छुट्टी जिसमें वेतन नहीं मिलता।</t>
+          <t>वह समय जब कोई सेवा काम करना बंद कर देती है।</t>
         </is>
       </c>
       <c r="N273" s="37" t="inlineStr">
@@ -26290,42 +26290,42 @@
       <c r="R273" s="37" t="inlineStr"/>
       <c r="S273" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech,cs</t>
         </is>
       </c>
       <c r="T273" s="39" t="inlineStr">
         <is>
-          <t>s:unpaid-leave</t>
+          <t>s:outage</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B274" s="34" t="inlineStr">
         <is>
-          <t>video call</t>
+          <t>password reset</t>
         </is>
       </c>
       <c r="C274" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D274" s="14" t="inlineStr">
         <is>
-          <t>A call where people can see and hear each other.</t>
+          <t>Making a new password when you forget the old one.</t>
         </is>
       </c>
       <c r="E274" s="14" t="inlineStr">
         <is>
-          <t>VID-ee-oh kawl</t>
+          <t>PASS-wurd ree-SET</t>
         </is>
       </c>
       <c r="F274" s="14" t="inlineStr">
         <is>
-          <t>/ˈvɪdiəʊ kɔːl/</t>
+          <t>/ˈpɑːswɜːd ˌriːˈset/</t>
         </is>
       </c>
       <c r="G274" s="14" t="inlineStr">
@@ -26335,28 +26335,28 @@
       </c>
       <c r="H274" s="14" t="inlineStr">
         <is>
-          <t>We solved it on a video call.</t>
+          <t>I sent him a password reset email.</t>
         </is>
       </c>
       <c r="I274" s="14" t="inlineStr">
         <is>
-          <t>I prefer a video call to a long email.</t>
+          <t>The password reset link lasts one hour.</t>
         </is>
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>We will do a video call tomorrow.</t>
+          <t>The password reset will log you out everywhere.</t>
         </is>
       </c>
       <c r="K274" s="14" t="inlineStr"/>
       <c r="L274" s="36" t="inlineStr">
         <is>
-          <t>वीडियो कॉल</t>
+          <t>पासवर्ड रीसेट</t>
         </is>
       </c>
       <c r="M274" s="36" t="inlineStr">
         <is>
-          <t>ऐसी कॉल जिसमें लोग एक दूसरे को देख और सुन सकते हैं।</t>
+          <t>पुराना पासवर्ड भूलने पर नया पासवर्ड बनाना।</t>
         </is>
       </c>
       <c r="N274" s="37" t="inlineStr">
@@ -26380,73 +26380,73 @@
       <c r="R274" s="37" t="inlineStr"/>
       <c r="S274" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>tech,cs</t>
         </is>
       </c>
       <c r="T274" s="39" t="inlineStr">
         <is>
-          <t>s:video-call</t>
+          <t>s:password-reset</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B275" s="34" t="inlineStr">
         <is>
-          <t>weekend shift</t>
+          <t>remediate</t>
         </is>
       </c>
       <c r="C275" s="35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D275" s="14" t="inlineStr">
         <is>
-          <t>Working hours on Saturday or Sunday.</t>
+          <t>To fix a problem, often a serious or risky one.</t>
         </is>
       </c>
       <c r="E275" s="14" t="inlineStr">
         <is>
-          <t>week-END shift</t>
+          <t>ri-MEE-dee-ayt</t>
         </is>
       </c>
       <c r="F275" s="14" t="inlineStr">
         <is>
-          <t>/ˌwiːkˈend ʃɪft/</t>
+          <t>/rɪˈmiːdieɪt/</t>
         </is>
       </c>
       <c r="G275" s="14" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="H275" s="14" t="inlineStr">
         <is>
-          <t>She covered my weekend shift.</t>
+          <t>They remediated the data issue overnight.</t>
         </is>
       </c>
       <c r="I275" s="14" t="inlineStr">
         <is>
-          <t>I work a weekend shift once a month.</t>
+          <t>The security team remediates risks quickly.</t>
         </is>
       </c>
       <c r="J275" s="14" t="inlineStr">
         <is>
-          <t>I will swap my weekend shift with Ana.</t>
+          <t>We will remediate the bug in the next release.</t>
         </is>
       </c>
       <c r="K275" s="14" t="inlineStr"/>
       <c r="L275" s="36" t="inlineStr">
         <is>
-          <t>सप्ताहांत की पारी</t>
+          <t>सुधार करना, ठीक करना</t>
         </is>
       </c>
       <c r="M275" s="36" t="inlineStr">
         <is>
-          <t>शनिवार या रविवार को काम के घंटे।</t>
+          <t>किसी गंभीर समस्या या जोखिम को ठीक करना।</t>
         </is>
       </c>
       <c r="N275" s="37" t="inlineStr">
@@ -26470,73 +26470,73 @@
       <c r="R275" s="37" t="inlineStr"/>
       <c r="S275" s="39" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tech,corp</t>
         </is>
       </c>
       <c r="T275" s="39" t="inlineStr">
         <is>
-          <t>s:weekend-shift</t>
+          <t>s:remediate</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B276" s="34" t="inlineStr">
         <is>
-          <t>work from home</t>
+          <t>reproduce</t>
         </is>
       </c>
       <c r="C276" s="35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D276" s="14" t="inlineStr">
         <is>
-          <t>To do your job from your house instead of the office.</t>
+          <t>To make a bug happen again so you can see it.</t>
         </is>
       </c>
       <c r="E276" s="14" t="inlineStr">
         <is>
-          <t>wurk frum HOHM</t>
+          <t>ree-pruh-DYOOS</t>
         </is>
       </c>
       <c r="F276" s="14" t="inlineStr">
         <is>
-          <t>/wɜːk frəm həʊm/</t>
+          <t>/ˌriːprəˈdjuːs/</t>
         </is>
       </c>
       <c r="G276" s="14" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="H276" s="14" t="inlineStr">
         <is>
-          <t>We worked from home during the storm.</t>
+          <t>We reproduced the bug in five minutes.</t>
         </is>
       </c>
       <c r="I276" s="14" t="inlineStr">
         <is>
-          <t>I work from home on Fridays.</t>
+          <t>Can you reproduce the error on your phone?</t>
         </is>
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>You will be able to work from home after training.</t>
+          <t>The team will try to reproduce it tomorrow.</t>
         </is>
       </c>
       <c r="K276" s="14" t="inlineStr"/>
       <c r="L276" s="36" t="inlineStr">
         <is>
-          <t>घर से काम करना</t>
+          <t>गड़बड़ी को दोबारा करके देखना</t>
         </is>
       </c>
       <c r="M276" s="36" t="inlineStr">
         <is>
-          <t>ऑफिस की जगह घर से नौकरी का काम करना।</t>
+          <t>बग को फिर से होते हुए देखना ताकि उसे समझा जा सके।</t>
         </is>
       </c>
       <c r="N276" s="37" t="inlineStr">
@@ -26560,24 +26560,24 @@
       <c r="R276" s="37" t="inlineStr"/>
       <c r="S276" s="39" t="inlineStr">
         <is>
-          <t>hr,corp</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="T276" s="39" t="inlineStr">
         <is>
-          <t>s:work-from-home</t>
+          <t>s:reproduce</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="33" t="inlineStr">
         <is>
-          <t>Workplace and HR</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="B277" s="34" t="inlineStr">
         <is>
-          <t>Zoom call</t>
+          <t>screenshot</t>
         </is>
       </c>
       <c r="C277" s="35" t="n">
@@ -26585,17 +26585,17 @@
       </c>
       <c r="D277" s="14" t="inlineStr">
         <is>
-          <t>A video meeting on the Zoom app.</t>
+          <t>A picture of what is on your screen.</t>
         </is>
       </c>
       <c r="E277" s="14" t="inlineStr">
         <is>
-          <t>zoom KAWL</t>
+          <t>SKREEN-shot</t>
         </is>
       </c>
       <c r="F277" s="14" t="inlineStr">
         <is>
-          <t>/zuːm kɔːl/</t>
+          <t>/ˈskriːnʃɒt/</t>
         </is>
       </c>
       <c r="G277" s="14" t="inlineStr">
@@ -26605,28 +26605,28 @@
       </c>
       <c r="H277" s="14" t="inlineStr">
         <is>
-          <t>We had a quick Zoom call with the client.</t>
+          <t>He shared a screenshot of the bill.</t>
         </is>
       </c>
       <c r="I277" s="14" t="inlineStr">
         <is>
-          <t>Our weekly Zoom call starts at ten.</t>
+          <t>Please send a screenshot of the error.</t>
         </is>
       </c>
       <c r="J277" s="14" t="inlineStr">
         <is>
-          <t>I will set up a Zoom call for Friday.</t>
+          <t>I will add your screenshot to the ticket.</t>
         </is>
       </c>
       <c r="K277" s="14" t="inlineStr"/>
       <c r="L277" s="36" t="inlineStr">
         <is>
-          <t>ज़ूम कॉल (वीडियो मीटिंग)</t>
+          <t>स्क्रीनशॉट</t>
         </is>
       </c>
       <c r="M277" s="36" t="inlineStr">
         <is>
-          <t>ज़ूम ऐप पर होने वाली वीडियो मीटिंग।</t>
+          <t>आपकी स्क्रीन पर जो दिख रहा है उसकी तस्वीर।</t>
         </is>
       </c>
       <c r="N277" s="37" t="inlineStr">
@@ -26650,10 +26650,4240 @@
       <c r="R277" s="37" t="inlineStr"/>
       <c r="S277" s="39" t="inlineStr">
         <is>
+          <t>tech,cs</t>
+        </is>
+      </c>
+      <c r="T277" s="39" t="inlineStr">
+        <is>
+          <t>s:screenshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="33" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B278" s="34" t="inlineStr">
+        <is>
+          <t>two-factor authentication</t>
+        </is>
+      </c>
+      <c r="C278" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D278" s="14" t="inlineStr">
+        <is>
+          <t>A second login step, like a code sent to your phone.</t>
+        </is>
+      </c>
+      <c r="E278" s="14" t="inlineStr">
+        <is>
+          <t>too FAK-ter aw-then-ti-KAY-shun</t>
+        </is>
+      </c>
+      <c r="F278" s="14" t="inlineStr">
+        <is>
+          <t>/tuː ˈfæktə ɔːˌθentɪˈkeɪʃn/</t>
+        </is>
+      </c>
+      <c r="G278" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H278" s="14" t="inlineStr">
+        <is>
+          <t>She turned on two-factor authentication yesterday.</t>
+        </is>
+      </c>
+      <c r="I278" s="14" t="inlineStr">
+        <is>
+          <t>Two-factor authentication keeps accounts safe.</t>
+        </is>
+      </c>
+      <c r="J278" s="14" t="inlineStr">
+        <is>
+          <t>You will need the code for two-factor authentication.</t>
+        </is>
+      </c>
+      <c r="K278" s="14" t="inlineStr"/>
+      <c r="L278" s="36" t="inlineStr">
+        <is>
+          <t>दो-चरणीय सत्यापन</t>
+        </is>
+      </c>
+      <c r="M278" s="36" t="inlineStr">
+        <is>
+          <t>लॉगिन का दूसरा कदम, जैसे फ़ोन पर आया कोड।</t>
+        </is>
+      </c>
+      <c r="N278" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O278" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P278" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q278" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R278" s="37" t="inlineStr"/>
+      <c r="S278" s="39" t="inlineStr">
+        <is>
+          <t>tech,cs</t>
+        </is>
+      </c>
+      <c r="T278" s="39" t="inlineStr">
+        <is>
+          <t>s:two-factor-authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="33" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B279" s="34" t="inlineStr">
+        <is>
+          <t>workaround</t>
+        </is>
+      </c>
+      <c r="C279" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D279" s="14" t="inlineStr">
+        <is>
+          <t>A temporary way to avoid a problem until it is fixed.</t>
+        </is>
+      </c>
+      <c r="E279" s="14" t="inlineStr">
+        <is>
+          <t>WURK-uh-round</t>
+        </is>
+      </c>
+      <c r="F279" s="14" t="inlineStr">
+        <is>
+          <t>/ˈwɜːkəraʊnd/</t>
+        </is>
+      </c>
+      <c r="G279" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H279" s="14" t="inlineStr">
+        <is>
+          <t>I shared a workaround with the user.</t>
+        </is>
+      </c>
+      <c r="I279" s="14" t="inlineStr">
+        <is>
+          <t>There is a simple workaround for this bug.</t>
+        </is>
+      </c>
+      <c r="J279" s="14" t="inlineStr">
+        <is>
+          <t>We will find a workaround until the update is out.</t>
+        </is>
+      </c>
+      <c r="K279" s="14" t="inlineStr"/>
+      <c r="L279" s="36" t="inlineStr">
+        <is>
+          <t>अस्थायी उपाय</t>
+        </is>
+      </c>
+      <c r="M279" s="36" t="inlineStr">
+        <is>
+          <t>समस्या ठीक होने तक काम चलाने का कोई दूसरा तरीका।</t>
+        </is>
+      </c>
+      <c r="N279" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O279" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P279" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q279" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R279" s="37" t="inlineStr"/>
+      <c r="S279" s="39" t="inlineStr">
+        <is>
+          <t>tech,cs</t>
+        </is>
+      </c>
+      <c r="T279" s="39" t="inlineStr">
+        <is>
+          <t>s:workaround</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B280" s="34" t="inlineStr">
+        <is>
+          <t>agenda</t>
+        </is>
+      </c>
+      <c r="C280" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D280" s="14" t="inlineStr">
+        <is>
+          <t>The list of topics for a meeting.</t>
+        </is>
+      </c>
+      <c r="E280" s="14" t="inlineStr">
+        <is>
+          <t>uh-JEN-duh</t>
+        </is>
+      </c>
+      <c r="F280" s="14" t="inlineStr">
+        <is>
+          <t>/əˈdʒendə/</t>
+        </is>
+      </c>
+      <c r="G280" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H280" s="14" t="inlineStr">
+        <is>
+          <t>She shared the agenda before the call.</t>
+        </is>
+      </c>
+      <c r="I280" s="14" t="inlineStr">
+        <is>
+          <t>The agenda has four points.</t>
+        </is>
+      </c>
+      <c r="J280" s="14" t="inlineStr">
+        <is>
+          <t>I will send the agenda tonight.</t>
+        </is>
+      </c>
+      <c r="K280" s="14" t="inlineStr"/>
+      <c r="L280" s="36" t="inlineStr">
+        <is>
+          <t>कार्यसूची, एजेंडा</t>
+        </is>
+      </c>
+      <c r="M280" s="36" t="inlineStr">
+        <is>
+          <t>मीटिंग में बात होने वाले विषयों की सूची।</t>
+        </is>
+      </c>
+      <c r="N280" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O280" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P280" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q280" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R280" s="37" t="inlineStr"/>
+      <c r="S280" s="39" t="inlineStr">
+        <is>
           <t>hr,corp</t>
         </is>
       </c>
-      <c r="T277" s="39" t="inlineStr">
+      <c r="T280" s="39" t="inlineStr">
+        <is>
+          <t>s:agenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B281" s="34" t="inlineStr">
+        <is>
+          <t>annual leave</t>
+        </is>
+      </c>
+      <c r="C281" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D281" s="14" t="inlineStr">
+        <is>
+          <t>Paid days off you get each year for holidays.</t>
+        </is>
+      </c>
+      <c r="E281" s="14" t="inlineStr">
+        <is>
+          <t>AN-yoo-ul leev</t>
+        </is>
+      </c>
+      <c r="F281" s="14" t="inlineStr">
+        <is>
+          <t>/ˈænjuəl liːv/</t>
+        </is>
+      </c>
+      <c r="G281" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H281" s="14" t="inlineStr">
+        <is>
+          <t>She took annual leave in August.</t>
+        </is>
+      </c>
+      <c r="I281" s="14" t="inlineStr">
+        <is>
+          <t>I have ten days of annual leave left.</t>
+        </is>
+      </c>
+      <c r="J281" s="14" t="inlineStr">
+        <is>
+          <t>I will book annual leave for Christmas.</t>
+        </is>
+      </c>
+      <c r="K281" s="14" t="inlineStr"/>
+      <c r="L281" s="36" t="inlineStr">
+        <is>
+          <t>वार्षिक छुट्टी</t>
+        </is>
+      </c>
+      <c r="M281" s="36" t="inlineStr">
+        <is>
+          <t>हर साल मिलने वाली वेतन सहित छुट्टियाँ।</t>
+        </is>
+      </c>
+      <c r="N281" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O281" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P281" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q281" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R281" s="37" t="inlineStr"/>
+      <c r="S281" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T281" s="39" t="inlineStr">
+        <is>
+          <t>s:annual-leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B282" s="34" t="inlineStr">
+        <is>
+          <t>benefits</t>
+        </is>
+      </c>
+      <c r="C282" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D282" s="14" t="inlineStr">
+        <is>
+          <t>Extra things your job gives you besides salary, like health insurance.</t>
+        </is>
+      </c>
+      <c r="E282" s="14" t="inlineStr">
+        <is>
+          <t>BEN-i-fits</t>
+        </is>
+      </c>
+      <c r="F282" s="14" t="inlineStr">
+        <is>
+          <t>/ˈbenɪfɪts/</t>
+        </is>
+      </c>
+      <c r="G282" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H282" s="14" t="inlineStr">
+        <is>
+          <t>HR explained the benefits on day one.</t>
+        </is>
+      </c>
+      <c r="I282" s="14" t="inlineStr">
+        <is>
+          <t>The benefits include health insurance.</t>
+        </is>
+      </c>
+      <c r="J282" s="14" t="inlineStr">
+        <is>
+          <t>Your benefits will start after probation.</t>
+        </is>
+      </c>
+      <c r="K282" s="14" t="inlineStr"/>
+      <c r="L282" s="36" t="inlineStr">
+        <is>
+          <t>अतिरिक्त सुविधाएँ, लाभ</t>
+        </is>
+      </c>
+      <c r="M282" s="36" t="inlineStr">
+        <is>
+          <t>वेतन के अलावा नौकरी से मिलने वाली सुविधाएँ, जैसे स्वास्थ्य बीमा।</t>
+        </is>
+      </c>
+      <c r="N282" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O282" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P282" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q282" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R282" s="37" t="inlineStr"/>
+      <c r="S282" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T282" s="39" t="inlineStr">
+        <is>
+          <t>s:benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B283" s="34" t="inlineStr">
+        <is>
+          <t>clock in</t>
+        </is>
+      </c>
+      <c r="C283" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D283" s="14" t="inlineStr">
+        <is>
+          <t>To record the time you start work.</t>
+        </is>
+      </c>
+      <c r="E283" s="14" t="inlineStr">
+        <is>
+          <t>klok IN</t>
+        </is>
+      </c>
+      <c r="F283" s="14" t="inlineStr">
+        <is>
+          <t>/klɒk ɪn/</t>
+        </is>
+      </c>
+      <c r="G283" s="14" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="H283" s="14" t="inlineStr">
+        <is>
+          <t>I clocked in at 7:55.</t>
+        </is>
+      </c>
+      <c r="I283" s="14" t="inlineStr">
+        <is>
+          <t>We clock in with our ID card.</t>
+        </is>
+      </c>
+      <c r="J283" s="14" t="inlineStr">
+        <is>
+          <t>You will clock in on the new app.</t>
+        </is>
+      </c>
+      <c r="K283" s="14" t="inlineStr"/>
+      <c r="L283" s="36" t="inlineStr">
+        <is>
+          <t>काम शुरू होने का समय दर्ज करना</t>
+        </is>
+      </c>
+      <c r="M283" s="36" t="inlineStr">
+        <is>
+          <t>काम शुरू करने का समय सिस्टम में दर्ज करना।</t>
+        </is>
+      </c>
+      <c r="N283" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O283" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P283" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q283" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R283" s="37" t="inlineStr"/>
+      <c r="S283" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T283" s="39" t="inlineStr">
+        <is>
+          <t>s:clock-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B284" s="34" t="inlineStr">
+        <is>
+          <t>comp off</t>
+        </is>
+      </c>
+      <c r="C284" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D284" s="14" t="inlineStr">
+        <is>
+          <t>A day off you get for working on a holiday or weekend.</t>
+        </is>
+      </c>
+      <c r="E284" s="14" t="inlineStr">
+        <is>
+          <t>KOMP off</t>
+        </is>
+      </c>
+      <c r="F284" s="14" t="inlineStr">
+        <is>
+          <t>/ˈkɒmp ɒf/</t>
+        </is>
+      </c>
+      <c r="G284" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H284" s="14" t="inlineStr">
+        <is>
+          <t>She used her comp off on Friday.</t>
+        </is>
+      </c>
+      <c r="I284" s="14" t="inlineStr">
+        <is>
+          <t>I have a comp off for last Sunday.</t>
+        </is>
+      </c>
+      <c r="J284" s="14" t="inlineStr">
+        <is>
+          <t>You will get a comp off for the weekend shift.</t>
+        </is>
+      </c>
+      <c r="K284" s="14" t="inlineStr"/>
+      <c r="L284" s="36" t="inlineStr">
+        <is>
+          <t>प्रतिपूरक छुट्टी, कॉम्प ऑफ</t>
+        </is>
+      </c>
+      <c r="M284" s="36" t="inlineStr">
+        <is>
+          <t>छुट्टी या वीकेंड पर काम करने के बदले मिलने वाली छुट्टी।</t>
+        </is>
+      </c>
+      <c r="N284" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O284" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P284" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q284" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R284" s="37" t="inlineStr"/>
+      <c r="S284" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T284" s="39" t="inlineStr">
+        <is>
+          <t>s:comp-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B285" s="34" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="C285" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D285" s="14" t="inlineStr">
+        <is>
+          <t>A written agreement about your job, pay and rules.</t>
+        </is>
+      </c>
+      <c r="E285" s="14" t="inlineStr">
+        <is>
+          <t>KON-trakt</t>
+        </is>
+      </c>
+      <c r="F285" s="14" t="inlineStr">
+        <is>
+          <t>/ˈkɒntrækt/</t>
+        </is>
+      </c>
+      <c r="G285" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H285" s="14" t="inlineStr">
+        <is>
+          <t>I signed the contract last week.</t>
+        </is>
+      </c>
+      <c r="I285" s="14" t="inlineStr">
+        <is>
+          <t>My contract is for one year.</t>
+        </is>
+      </c>
+      <c r="J285" s="14" t="inlineStr">
+        <is>
+          <t>HR will email you the contract.</t>
+        </is>
+      </c>
+      <c r="K285" s="14" t="inlineStr"/>
+      <c r="L285" s="36" t="inlineStr">
+        <is>
+          <t>अनुबंध, कॉन्ट्रैक्ट</t>
+        </is>
+      </c>
+      <c r="M285" s="36" t="inlineStr">
+        <is>
+          <t>नौकरी, वेतन और नियमों के बारे में लिखित समझौता।</t>
+        </is>
+      </c>
+      <c r="N285" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O285" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P285" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q285" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R285" s="37" t="inlineStr"/>
+      <c r="S285" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T285" s="39" t="inlineStr">
+        <is>
+          <t>s:contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B286" s="34" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="C286" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D286" s="14" t="inlineStr">
+        <is>
+          <t>A person who works for a company and gets paid.</t>
+        </is>
+      </c>
+      <c r="E286" s="14" t="inlineStr">
+        <is>
+          <t>im-PLOY-ee</t>
+        </is>
+      </c>
+      <c r="F286" s="14" t="inlineStr">
+        <is>
+          <t>/ɪmˈplɔɪiː/</t>
+        </is>
+      </c>
+      <c r="G286" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H286" s="14" t="inlineStr">
+        <is>
+          <t>She was employee of the month.</t>
+        </is>
+      </c>
+      <c r="I286" s="14" t="inlineStr">
+        <is>
+          <t>Every employee gets a laptop.</t>
+        </is>
+      </c>
+      <c r="J286" s="14" t="inlineStr">
+        <is>
+          <t>New employees will start on Monday.</t>
+        </is>
+      </c>
+      <c r="K286" s="14" t="inlineStr"/>
+      <c r="L286" s="36" t="inlineStr">
+        <is>
+          <t>कर्मचारी</t>
+        </is>
+      </c>
+      <c r="M286" s="36" t="inlineStr">
+        <is>
+          <t>वह व्यक्ति जो किसी कंपनी में काम करता है और वेतन पाता है।</t>
+        </is>
+      </c>
+      <c r="N286" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O286" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P286" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q286" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R286" s="37" t="inlineStr"/>
+      <c r="S286" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T286" s="39" t="inlineStr">
+        <is>
+          <t>s:employee</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B287" s="34" t="inlineStr">
+        <is>
+          <t>employer</t>
+        </is>
+      </c>
+      <c r="C287" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D287" s="14" t="inlineStr">
+        <is>
+          <t>The company or person that pays you to work.</t>
+        </is>
+      </c>
+      <c r="E287" s="14" t="inlineStr">
+        <is>
+          <t>im-PLOY-er</t>
+        </is>
+      </c>
+      <c r="F287" s="14" t="inlineStr">
+        <is>
+          <t>/ɪmˈplɔɪə/</t>
+        </is>
+      </c>
+      <c r="G287" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H287" s="14" t="inlineStr">
+        <is>
+          <t>My last employer gave me a good reference.</t>
+        </is>
+      </c>
+      <c r="I287" s="14" t="inlineStr">
+        <is>
+          <t>My employer pays on the last day of the month.</t>
+        </is>
+      </c>
+      <c r="J287" s="14" t="inlineStr">
+        <is>
+          <t>Your employer will send the contract.</t>
+        </is>
+      </c>
+      <c r="K287" s="14" t="inlineStr"/>
+      <c r="L287" s="36" t="inlineStr">
+        <is>
+          <t>नियोक्ता</t>
+        </is>
+      </c>
+      <c r="M287" s="36" t="inlineStr">
+        <is>
+          <t>वह कंपनी या व्यक्ति जो आपको काम के लिए पैसे देता है।</t>
+        </is>
+      </c>
+      <c r="N287" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O287" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P287" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q287" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R287" s="37" t="inlineStr"/>
+      <c r="S287" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T287" s="39" t="inlineStr">
+        <is>
+          <t>s:employer</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B288" s="34" t="inlineStr">
+        <is>
+          <t>fixed-term contract</t>
+        </is>
+      </c>
+      <c r="C288" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D288" s="14" t="inlineStr">
+        <is>
+          <t>A job contract that ends on a set date.</t>
+        </is>
+      </c>
+      <c r="E288" s="14" t="inlineStr">
+        <is>
+          <t>fikst-turm KON-trakt</t>
+        </is>
+      </c>
+      <c r="F288" s="14" t="inlineStr">
+        <is>
+          <t>/ˌfɪkst tɜːm ˈkɒntrækt/</t>
+        </is>
+      </c>
+      <c r="G288" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H288" s="14" t="inlineStr">
+        <is>
+          <t>They offered me a fixed-term contract.</t>
+        </is>
+      </c>
+      <c r="I288" s="14" t="inlineStr">
+        <is>
+          <t>My fixed-term contract ends in June.</t>
+        </is>
+      </c>
+      <c r="J288" s="14" t="inlineStr">
+        <is>
+          <t>The fixed-term contract will become permanent.</t>
+        </is>
+      </c>
+      <c r="K288" s="14" t="inlineStr"/>
+      <c r="L288" s="36" t="inlineStr">
+        <is>
+          <t>निश्चित अवधि का अनुबंध</t>
+        </is>
+      </c>
+      <c r="M288" s="36" t="inlineStr">
+        <is>
+          <t>ऐसा अनुबंध जो तय तारीख पर खत्म होता है।</t>
+        </is>
+      </c>
+      <c r="N288" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O288" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P288" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q288" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R288" s="37" t="inlineStr"/>
+      <c r="S288" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T288" s="39" t="inlineStr">
+        <is>
+          <t>s:fixed-term-contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B289" s="34" t="inlineStr">
+        <is>
+          <t>Google Meet</t>
+        </is>
+      </c>
+      <c r="C289" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D289" s="14" t="inlineStr">
+        <is>
+          <t>Google's app for video meetings.</t>
+        </is>
+      </c>
+      <c r="E289" s="14" t="inlineStr">
+        <is>
+          <t>GOO-gul meet</t>
+        </is>
+      </c>
+      <c r="F289" s="14" t="inlineStr">
+        <is>
+          <t>/ˈɡuːɡl miːt/</t>
+        </is>
+      </c>
+      <c r="G289" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H289" s="14" t="inlineStr">
+        <is>
+          <t>I shared my screen on Google Meet.</t>
+        </is>
+      </c>
+      <c r="I289" s="14" t="inlineStr">
+        <is>
+          <t>The training is on Google Meet.</t>
+        </is>
+      </c>
+      <c r="J289" s="14" t="inlineStr">
+        <is>
+          <t>I will send you the Google Meet link.</t>
+        </is>
+      </c>
+      <c r="K289" s="14" t="inlineStr"/>
+      <c r="L289" s="36" t="inlineStr">
+        <is>
+          <t>गूगल मीट (वीडियो मीटिंग ऐप)</t>
+        </is>
+      </c>
+      <c r="M289" s="36" t="inlineStr">
+        <is>
+          <t>वीडियो मीटिंग के लिए गूगल का ऐप।</t>
+        </is>
+      </c>
+      <c r="N289" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O289" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P289" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q289" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R289" s="37" t="inlineStr"/>
+      <c r="S289" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T289" s="39" t="inlineStr">
+        <is>
+          <t>s:google-meet</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B290" s="34" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C290" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D290" s="14" t="inlineStr">
+        <is>
+          <t>Human Resources, the team that handles hiring, contracts, pay and staff questions.</t>
+        </is>
+      </c>
+      <c r="E290" s="14" t="inlineStr">
+        <is>
+          <t>aych AR</t>
+        </is>
+      </c>
+      <c r="F290" s="14" t="inlineStr">
+        <is>
+          <t>/ˌeɪtʃ ˈɑː/</t>
+        </is>
+      </c>
+      <c r="G290" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H290" s="14" t="inlineStr">
+        <is>
+          <t>I emailed HR about my payslip.</t>
+        </is>
+      </c>
+      <c r="I290" s="14" t="inlineStr">
+        <is>
+          <t>HR handles all leave requests.</t>
+        </is>
+      </c>
+      <c r="J290" s="14" t="inlineStr">
+        <is>
+          <t>HR will explain your benefits.</t>
+        </is>
+      </c>
+      <c r="K290" s="14" t="inlineStr"/>
+      <c r="L290" s="36" t="inlineStr">
+        <is>
+          <t>मानव संसाधन विभाग, एचआर</t>
+        </is>
+      </c>
+      <c r="M290" s="36" t="inlineStr">
+        <is>
+          <t>वह टीम जो भर्ती, अनुबंध, वेतन और कर्मचारियों के सवाल संभालती है।</t>
+        </is>
+      </c>
+      <c r="N290" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O290" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P290" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q290" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R290" s="37" t="inlineStr"/>
+      <c r="S290" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T290" s="39" t="inlineStr">
+        <is>
+          <t>s:hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B291" s="34" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="C291" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D291" s="14" t="inlineStr">
+        <is>
+          <t>The person who leads a team and checks its work.</t>
+        </is>
+      </c>
+      <c r="E291" s="14" t="inlineStr">
+        <is>
+          <t>MAN-ij-er</t>
+        </is>
+      </c>
+      <c r="F291" s="14" t="inlineStr">
+        <is>
+          <t>/ˈmænɪdʒə/</t>
+        </is>
+      </c>
+      <c r="G291" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H291" s="14" t="inlineStr">
+        <is>
+          <t>The manager praised our team.</t>
+        </is>
+      </c>
+      <c r="I291" s="14" t="inlineStr">
+        <is>
+          <t>My manager approves my leave.</t>
+        </is>
+      </c>
+      <c r="J291" s="14" t="inlineStr">
+        <is>
+          <t>Your manager will call you today.</t>
+        </is>
+      </c>
+      <c r="K291" s="14" t="inlineStr"/>
+      <c r="L291" s="36" t="inlineStr">
+        <is>
+          <t>प्रबंधक, मैनेजर</t>
+        </is>
+      </c>
+      <c r="M291" s="36" t="inlineStr">
+        <is>
+          <t>वह व्यक्ति जो टीम का नेतृत्व करता है और काम देखता है।</t>
+        </is>
+      </c>
+      <c r="N291" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O291" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P291" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q291" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R291" s="37" t="inlineStr"/>
+      <c r="S291" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T291" s="39" t="inlineStr">
+        <is>
+          <t>s:manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B292" s="34" t="inlineStr">
+        <is>
+          <t>meeting</t>
+        </is>
+      </c>
+      <c r="C292" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D292" s="14" t="inlineStr">
+        <is>
+          <t>A planned time when people come together to talk about work.</t>
+        </is>
+      </c>
+      <c r="E292" s="14" t="inlineStr">
+        <is>
+          <t>MEE-ting</t>
+        </is>
+      </c>
+      <c r="F292" s="14" t="inlineStr">
+        <is>
+          <t>/ˈmiːtɪŋ/</t>
+        </is>
+      </c>
+      <c r="G292" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H292" s="14" t="inlineStr">
+        <is>
+          <t>The meeting ran late yesterday.</t>
+        </is>
+      </c>
+      <c r="I292" s="14" t="inlineStr">
+        <is>
+          <t>We have a team meeting every Monday.</t>
+        </is>
+      </c>
+      <c r="J292" s="14" t="inlineStr">
+        <is>
+          <t>I will join the meeting at three.</t>
+        </is>
+      </c>
+      <c r="K292" s="14" t="inlineStr"/>
+      <c r="L292" s="36" t="inlineStr">
+        <is>
+          <t>बैठक, मीटिंग</t>
+        </is>
+      </c>
+      <c r="M292" s="36" t="inlineStr">
+        <is>
+          <t>काम पर बात करने के लिए लोगों का तय समय पर मिलना।</t>
+        </is>
+      </c>
+      <c r="N292" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O292" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P292" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q292" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R292" s="37" t="inlineStr"/>
+      <c r="S292" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T292" s="39" t="inlineStr">
+        <is>
+          <t>s:meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B293" s="34" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="C293" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D293" s="14" t="inlineStr">
+        <is>
+          <t>The written record of what was said in a meeting.</t>
+        </is>
+      </c>
+      <c r="E293" s="14" t="inlineStr">
+        <is>
+          <t>MIN-its</t>
+        </is>
+      </c>
+      <c r="F293" s="14" t="inlineStr">
+        <is>
+          <t>/ˈmɪnɪts/</t>
+        </is>
+      </c>
+      <c r="G293" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H293" s="14" t="inlineStr">
+        <is>
+          <t>He sent the minutes after the meeting.</t>
+        </is>
+      </c>
+      <c r="I293" s="14" t="inlineStr">
+        <is>
+          <t>The minutes are in the shared folder.</t>
+        </is>
+      </c>
+      <c r="J293" s="14" t="inlineStr">
+        <is>
+          <t>I will share the minutes by noon.</t>
+        </is>
+      </c>
+      <c r="K293" s="14" t="inlineStr"/>
+      <c r="L293" s="36" t="inlineStr">
+        <is>
+          <t>बैठक का लिखित ब्योरा</t>
+        </is>
+      </c>
+      <c r="M293" s="36" t="inlineStr">
+        <is>
+          <t>मीटिंग में हुई बातों का लिखा हुआ रिकॉर्ड।</t>
+        </is>
+      </c>
+      <c r="N293" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O293" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P293" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q293" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R293" s="37" t="inlineStr"/>
+      <c r="S293" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T293" s="39" t="inlineStr">
+        <is>
+          <t>s:minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B294" s="34" t="inlineStr">
+        <is>
+          <t>mute</t>
+        </is>
+      </c>
+      <c r="C294" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D294" s="14" t="inlineStr">
+        <is>
+          <t>To turn off your microphone.</t>
+        </is>
+      </c>
+      <c r="E294" s="14" t="inlineStr">
+        <is>
+          <t>myoot</t>
+        </is>
+      </c>
+      <c r="F294" s="14" t="inlineStr">
+        <is>
+          <t>/mjuːt/</t>
+        </is>
+      </c>
+      <c r="G294" s="14" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="H294" s="14" t="inlineStr">
+        <is>
+          <t>I forgot I was muted.</t>
+        </is>
+      </c>
+      <c r="I294" s="14" t="inlineStr">
+        <is>
+          <t>Please mute yourself when you aren't speaking.</t>
+        </is>
+      </c>
+      <c r="J294" s="14" t="inlineStr">
+        <is>
+          <t>I will mute my mic during the training.</t>
+        </is>
+      </c>
+      <c r="K294" s="14" t="inlineStr"/>
+      <c r="L294" s="36" t="inlineStr">
+        <is>
+          <t>म्यूट करना, आवाज़ बंद करना</t>
+        </is>
+      </c>
+      <c r="M294" s="36" t="inlineStr">
+        <is>
+          <t>कॉल पर अपना माइक बंद करना।</t>
+        </is>
+      </c>
+      <c r="N294" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O294" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P294" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q294" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R294" s="37" t="inlineStr"/>
+      <c r="S294" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T294" s="39" t="inlineStr">
+        <is>
+          <t>s:mute</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B295" s="34" t="inlineStr">
+        <is>
+          <t>notice period</t>
+        </is>
+      </c>
+      <c r="C295" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D295" s="14" t="inlineStr">
+        <is>
+          <t>The time you must keep working after you say you are leaving.</t>
+        </is>
+      </c>
+      <c r="E295" s="14" t="inlineStr">
+        <is>
+          <t>NOH-tis PEER-ee-ud</t>
+        </is>
+      </c>
+      <c r="F295" s="14" t="inlineStr">
+        <is>
+          <t>/ˈnəʊtɪs ˈpɪəriəd/</t>
+        </is>
+      </c>
+      <c r="G295" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H295" s="14" t="inlineStr">
+        <is>
+          <t>She worked her full notice period.</t>
+        </is>
+      </c>
+      <c r="I295" s="14" t="inlineStr">
+        <is>
+          <t>My notice period is one month.</t>
+        </is>
+      </c>
+      <c r="J295" s="14" t="inlineStr">
+        <is>
+          <t>Your notice period will start today.</t>
+        </is>
+      </c>
+      <c r="K295" s="14" t="inlineStr"/>
+      <c r="L295" s="36" t="inlineStr">
+        <is>
+          <t>नोटिस अवधि</t>
+        </is>
+      </c>
+      <c r="M295" s="36" t="inlineStr">
+        <is>
+          <t>नौकरी छोड़ने की सूचना देने के बाद काम करने का ज़रूरी समय।</t>
+        </is>
+      </c>
+      <c r="N295" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O295" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P295" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q295" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R295" s="37" t="inlineStr"/>
+      <c r="S295" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T295" s="39" t="inlineStr">
+        <is>
+          <t>s:notice-period</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B296" s="34" t="inlineStr">
+        <is>
+          <t>one-on-one</t>
+        </is>
+      </c>
+      <c r="C296" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D296" s="14" t="inlineStr">
+        <is>
+          <t>A private meeting between you and your manager.</t>
+        </is>
+      </c>
+      <c r="E296" s="14" t="inlineStr">
+        <is>
+          <t>wun-on-WUN</t>
+        </is>
+      </c>
+      <c r="F296" s="14" t="inlineStr">
+        <is>
+          <t>/ˌwʌn ɒn ˈwʌn/</t>
+        </is>
+      </c>
+      <c r="G296" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H296" s="14" t="inlineStr">
+        <is>
+          <t>We talked about my goals in our one-on-one.</t>
+        </is>
+      </c>
+      <c r="I296" s="14" t="inlineStr">
+        <is>
+          <t>I have a one-on-one with my manager every Friday.</t>
+        </is>
+      </c>
+      <c r="J296" s="14" t="inlineStr">
+        <is>
+          <t>I will raise this in my next one-on-one.</t>
+        </is>
+      </c>
+      <c r="K296" s="14" t="inlineStr"/>
+      <c r="L296" s="36" t="inlineStr">
+        <is>
+          <t>आमने-सामने की निजी बैठक</t>
+        </is>
+      </c>
+      <c r="M296" s="36" t="inlineStr">
+        <is>
+          <t>आपकी और आपके मैनेजर की अकेले में होने वाली मीटिंग।</t>
+        </is>
+      </c>
+      <c r="N296" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O296" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P296" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q296" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R296" s="37" t="inlineStr"/>
+      <c r="S296" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T296" s="39" t="inlineStr">
+        <is>
+          <t>s:one-on-one</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B297" s="34" t="inlineStr">
+        <is>
+          <t>out of office</t>
+        </is>
+      </c>
+      <c r="C297" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D297" s="14" t="inlineStr">
+        <is>
+          <t>Away from work, so you can't reply for a while.</t>
+        </is>
+      </c>
+      <c r="E297" s="14" t="inlineStr">
+        <is>
+          <t>owt uv OF-is</t>
+        </is>
+      </c>
+      <c r="F297" s="14" t="inlineStr">
+        <is>
+          <t>/aʊt əv ˈɒfɪs/</t>
+        </is>
+      </c>
+      <c r="G297" s="14" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="H297" s="14" t="inlineStr">
+        <is>
+          <t>She set an out of office reply.</t>
+        </is>
+      </c>
+      <c r="I297" s="14" t="inlineStr">
+        <is>
+          <t>I'm out of office until Monday.</t>
+        </is>
+      </c>
+      <c r="J297" s="14" t="inlineStr">
+        <is>
+          <t>I will be out of office next week.</t>
+        </is>
+      </c>
+      <c r="K297" s="14" t="inlineStr"/>
+      <c r="L297" s="36" t="inlineStr">
+        <is>
+          <t>कार्यालय से बाहर</t>
+        </is>
+      </c>
+      <c r="M297" s="36" t="inlineStr">
+        <is>
+          <t>काम से दूर, इसलिए कुछ समय तक जवाब नहीं दे सकते।</t>
+        </is>
+      </c>
+      <c r="N297" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O297" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P297" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q297" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R297" s="37" t="inlineStr"/>
+      <c r="S297" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T297" s="39" t="inlineStr">
+        <is>
+          <t>s:out-of-office</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B298" s="34" t="inlineStr">
+        <is>
+          <t>overtime</t>
+        </is>
+      </c>
+      <c r="C298" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D298" s="14" t="inlineStr">
+        <is>
+          <t>Extra hours you work beyond your normal hours.</t>
+        </is>
+      </c>
+      <c r="E298" s="14" t="inlineStr">
+        <is>
+          <t>OH-ver-tym</t>
+        </is>
+      </c>
+      <c r="F298" s="14" t="inlineStr">
+        <is>
+          <t>/ˈəʊvətaɪm/</t>
+        </is>
+      </c>
+      <c r="G298" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H298" s="14" t="inlineStr">
+        <is>
+          <t>I did three hours of overtime yesterday.</t>
+        </is>
+      </c>
+      <c r="I298" s="14" t="inlineStr">
+        <is>
+          <t>Overtime is paid at a higher rate.</t>
+        </is>
+      </c>
+      <c r="J298" s="14" t="inlineStr">
+        <is>
+          <t>We will need overtime during the launch.</t>
+        </is>
+      </c>
+      <c r="K298" s="14" t="inlineStr"/>
+      <c r="L298" s="36" t="inlineStr">
+        <is>
+          <t>ओवरटाइम, अतिरिक्त समय</t>
+        </is>
+      </c>
+      <c r="M298" s="36" t="inlineStr">
+        <is>
+          <t>सामान्य घंटों से ज़्यादा किया गया काम।</t>
+        </is>
+      </c>
+      <c r="N298" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O298" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P298" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q298" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R298" s="37" t="inlineStr"/>
+      <c r="S298" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T298" s="39" t="inlineStr">
+        <is>
+          <t>s:overtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B299" s="34" t="inlineStr">
+        <is>
+          <t>paid time off</t>
+        </is>
+      </c>
+      <c r="C299" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D299" s="14" t="inlineStr">
+        <is>
+          <t>Days off when you still get paid. Often called PTO.</t>
+        </is>
+      </c>
+      <c r="E299" s="14" t="inlineStr">
+        <is>
+          <t>payd tym OFF</t>
+        </is>
+      </c>
+      <c r="F299" s="14" t="inlineStr">
+        <is>
+          <t>/peɪd taɪm ɒf/</t>
+        </is>
+      </c>
+      <c r="G299" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H299" s="14" t="inlineStr">
+        <is>
+          <t>I used my paid time off for a family trip.</t>
+        </is>
+      </c>
+      <c r="I299" s="14" t="inlineStr">
+        <is>
+          <t>PTO includes holidays and sick days.</t>
+        </is>
+      </c>
+      <c r="J299" s="14" t="inlineStr">
+        <is>
+          <t>New staff will get 22 days of paid time off.</t>
+        </is>
+      </c>
+      <c r="K299" s="14" t="inlineStr"/>
+      <c r="L299" s="36" t="inlineStr">
+        <is>
+          <t>वेतन सहित छुट्टी</t>
+        </is>
+      </c>
+      <c r="M299" s="36" t="inlineStr">
+        <is>
+          <t>ऐसी छुट्टी जिसमें आपको फिर भी वेतन मिलता है।</t>
+        </is>
+      </c>
+      <c r="N299" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O299" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P299" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q299" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R299" s="37" t="inlineStr"/>
+      <c r="S299" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T299" s="39" t="inlineStr">
+        <is>
+          <t>s:paid-time-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B300" s="34" t="inlineStr">
+        <is>
+          <t>payslip</t>
+        </is>
+      </c>
+      <c r="C300" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" s="14" t="inlineStr">
+        <is>
+          <t>A document that shows your pay and what was taken off it. Also called a salary slip.</t>
+        </is>
+      </c>
+      <c r="E300" s="14" t="inlineStr">
+        <is>
+          <t>PAY-slip</t>
+        </is>
+      </c>
+      <c r="F300" s="14" t="inlineStr">
+        <is>
+          <t>/ˈpeɪslɪp/</t>
+        </is>
+      </c>
+      <c r="G300" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H300" s="14" t="inlineStr">
+        <is>
+          <t>I downloaded my payslip yesterday.</t>
+        </is>
+      </c>
+      <c r="I300" s="14" t="inlineStr">
+        <is>
+          <t>My payslip shows tax and overtime.</t>
+        </is>
+      </c>
+      <c r="J300" s="14" t="inlineStr">
+        <is>
+          <t>You will get your payslip by email.</t>
+        </is>
+      </c>
+      <c r="K300" s="14" t="inlineStr"/>
+      <c r="L300" s="36" t="inlineStr">
+        <is>
+          <t>वेतन पर्ची, सैलरी स्लिप</t>
+        </is>
+      </c>
+      <c r="M300" s="36" t="inlineStr">
+        <is>
+          <t>वह दस्तावेज़ जिसमें आपका वेतन और कटौतियाँ दिखती हैं।</t>
+        </is>
+      </c>
+      <c r="N300" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O300" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P300" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q300" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R300" s="37" t="inlineStr"/>
+      <c r="S300" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T300" s="39" t="inlineStr">
+        <is>
+          <t>s:payslip</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B301" s="34" t="inlineStr">
+        <is>
+          <t>performance review</t>
+        </is>
+      </c>
+      <c r="C301" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D301" s="14" t="inlineStr">
+        <is>
+          <t>A meeting where your manager talks about how well you did your job. Also called an appraisal.</t>
+        </is>
+      </c>
+      <c r="E301" s="14" t="inlineStr">
+        <is>
+          <t>per-FOR-muns ri-VYOO</t>
+        </is>
+      </c>
+      <c r="F301" s="14" t="inlineStr">
+        <is>
+          <t>/pəˈfɔːməns rɪˈvjuː/</t>
+        </is>
+      </c>
+      <c r="G301" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H301" s="14" t="inlineStr">
+        <is>
+          <t>My performance review went well.</t>
+        </is>
+      </c>
+      <c r="I301" s="14" t="inlineStr">
+        <is>
+          <t>Performance reviews happen twice a year.</t>
+        </is>
+      </c>
+      <c r="J301" s="14" t="inlineStr">
+        <is>
+          <t>We will set goals in your performance review.</t>
+        </is>
+      </c>
+      <c r="K301" s="14" t="inlineStr"/>
+      <c r="L301" s="36" t="inlineStr">
+        <is>
+          <t>कार्य मूल्यांकन</t>
+        </is>
+      </c>
+      <c r="M301" s="36" t="inlineStr">
+        <is>
+          <t>वह मीटिंग जिसमें मैनेजर आपके काम का मूल्यांकन करता है।</t>
+        </is>
+      </c>
+      <c r="N301" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O301" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P301" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q301" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R301" s="37" t="inlineStr"/>
+      <c r="S301" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T301" s="39" t="inlineStr">
+        <is>
+          <t>s:performance-review</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B302" s="34" t="inlineStr">
+        <is>
+          <t>permanent contract</t>
+        </is>
+      </c>
+      <c r="C302" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D302" s="14" t="inlineStr">
+        <is>
+          <t>A job contract with no end date.</t>
+        </is>
+      </c>
+      <c r="E302" s="14" t="inlineStr">
+        <is>
+          <t>PUR-muh-nunt KON-trakt</t>
+        </is>
+      </c>
+      <c r="F302" s="14" t="inlineStr">
+        <is>
+          <t>/ˈpɜːmənənt ˈkɒntrækt/</t>
+        </is>
+      </c>
+      <c r="G302" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H302" s="14" t="inlineStr">
+        <is>
+          <t>He got a permanent contract after one year.</t>
+        </is>
+      </c>
+      <c r="I302" s="14" t="inlineStr">
+        <is>
+          <t>She has a permanent contract now.</t>
+        </is>
+      </c>
+      <c r="J302" s="14" t="inlineStr">
+        <is>
+          <t>You will get a permanent contract after probation.</t>
+        </is>
+      </c>
+      <c r="K302" s="14" t="inlineStr"/>
+      <c r="L302" s="36" t="inlineStr">
+        <is>
+          <t>स्थायी अनुबंध</t>
+        </is>
+      </c>
+      <c r="M302" s="36" t="inlineStr">
+        <is>
+          <t>ऐसा नौकरी का अनुबंध जिसकी कोई अंतिम तारीख न हो।</t>
+        </is>
+      </c>
+      <c r="N302" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O302" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P302" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q302" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R302" s="37" t="inlineStr"/>
+      <c r="S302" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T302" s="39" t="inlineStr">
+        <is>
+          <t>s:permanent-contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B303" s="34" t="inlineStr">
+        <is>
+          <t>probation period</t>
+        </is>
+      </c>
+      <c r="C303" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D303" s="14" t="inlineStr">
+        <is>
+          <t>The first months of a job when the company checks if you fit the role.</t>
+        </is>
+      </c>
+      <c r="E303" s="14" t="inlineStr">
+        <is>
+          <t>pruh-BAY-shun PEER-ee-ud</t>
+        </is>
+      </c>
+      <c r="F303" s="14" t="inlineStr">
+        <is>
+          <t>/prəˈbeɪʃn ˈpɪəriəd/</t>
+        </is>
+      </c>
+      <c r="G303" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H303" s="14" t="inlineStr">
+        <is>
+          <t>He passed his probation period.</t>
+        </is>
+      </c>
+      <c r="I303" s="14" t="inlineStr">
+        <is>
+          <t>My probation period is six months.</t>
+        </is>
+      </c>
+      <c r="J303" s="14" t="inlineStr">
+        <is>
+          <t>Your probation period will end in March.</t>
+        </is>
+      </c>
+      <c r="K303" s="14" t="inlineStr"/>
+      <c r="L303" s="36" t="inlineStr">
+        <is>
+          <t>परिवीक्षा अवधि</t>
+        </is>
+      </c>
+      <c r="M303" s="36" t="inlineStr">
+        <is>
+          <t>नौकरी के शुरुआती महीने जिनमें कंपनी देखती है कि आप काम के लिए सही हैं या नहीं।</t>
+        </is>
+      </c>
+      <c r="N303" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O303" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P303" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q303" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R303" s="37" t="inlineStr"/>
+      <c r="S303" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T303" s="39" t="inlineStr">
+        <is>
+          <t>s:probation-period</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B304" s="34" t="inlineStr">
+        <is>
+          <t>promotion</t>
+        </is>
+      </c>
+      <c r="C304" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D304" s="14" t="inlineStr">
+        <is>
+          <t>A move to a higher job with more responsibility.</t>
+        </is>
+      </c>
+      <c r="E304" s="14" t="inlineStr">
+        <is>
+          <t>pruh-MOH-shun</t>
+        </is>
+      </c>
+      <c r="F304" s="14" t="inlineStr">
+        <is>
+          <t>/prəˈməʊʃn/</t>
+        </is>
+      </c>
+      <c r="G304" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H304" s="14" t="inlineStr">
+        <is>
+          <t>She got a promotion to team lead.</t>
+        </is>
+      </c>
+      <c r="I304" s="14" t="inlineStr">
+        <is>
+          <t>A promotion usually comes with a raise.</t>
+        </is>
+      </c>
+      <c r="J304" s="14" t="inlineStr">
+        <is>
+          <t>I will apply for the promotion.</t>
+        </is>
+      </c>
+      <c r="K304" s="14" t="inlineStr"/>
+      <c r="L304" s="36" t="inlineStr">
+        <is>
+          <t>पदोन्नति, प्रमोशन</t>
+        </is>
+      </c>
+      <c r="M304" s="36" t="inlineStr">
+        <is>
+          <t>ज़्यादा ज़िम्मेदारी वाले ऊँचे पद पर जाना।</t>
+        </is>
+      </c>
+      <c r="N304" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O304" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P304" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q304" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R304" s="37" t="inlineStr"/>
+      <c r="S304" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T304" s="39" t="inlineStr">
+        <is>
+          <t>s:promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B305" s="34" t="inlineStr">
+        <is>
+          <t>public holiday</t>
+        </is>
+      </c>
+      <c r="C305" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D305" s="14" t="inlineStr">
+        <is>
+          <t>A day off for the whole country.</t>
+        </is>
+      </c>
+      <c r="E305" s="14" t="inlineStr">
+        <is>
+          <t>PUB-lik HOL-uh-day</t>
+        </is>
+      </c>
+      <c r="F305" s="14" t="inlineStr">
+        <is>
+          <t>/ˌpʌblɪk ˈhɒlədeɪ/</t>
+        </is>
+      </c>
+      <c r="G305" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H305" s="14" t="inlineStr">
+        <is>
+          <t>We worked on the public holiday.</t>
+        </is>
+      </c>
+      <c r="I305" s="14" t="inlineStr">
+        <is>
+          <t>Monday is a public holiday in Portugal.</t>
+        </is>
+      </c>
+      <c r="J305" s="14" t="inlineStr">
+        <is>
+          <t>The office will close on the public holiday.</t>
+        </is>
+      </c>
+      <c r="K305" s="14" t="inlineStr"/>
+      <c r="L305" s="36" t="inlineStr">
+        <is>
+          <t>सार्वजनिक अवकाश</t>
+        </is>
+      </c>
+      <c r="M305" s="36" t="inlineStr">
+        <is>
+          <t>वह दिन जब पूरे देश में छुट्टी होती है।</t>
+        </is>
+      </c>
+      <c r="N305" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O305" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P305" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q305" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R305" s="37" t="inlineStr"/>
+      <c r="S305" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T305" s="39" t="inlineStr">
+        <is>
+          <t>s:public-holiday</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B306" s="34" t="inlineStr">
+        <is>
+          <t>reschedule</t>
+        </is>
+      </c>
+      <c r="C306" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D306" s="14" t="inlineStr">
+        <is>
+          <t>To move a meeting or task to a new time.</t>
+        </is>
+      </c>
+      <c r="E306" s="14" t="inlineStr">
+        <is>
+          <t>ree-SHED-yool</t>
+        </is>
+      </c>
+      <c r="F306" s="14" t="inlineStr">
+        <is>
+          <t>/ˌriːˈʃedjuːl/</t>
+        </is>
+      </c>
+      <c r="G306" s="14" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="H306" s="14" t="inlineStr">
+        <is>
+          <t>She rescheduled the training to Tuesday.</t>
+        </is>
+      </c>
+      <c r="I306" s="14" t="inlineStr">
+        <is>
+          <t>Can we reschedule our call?</t>
+        </is>
+      </c>
+      <c r="J306" s="14" t="inlineStr">
+        <is>
+          <t>I will reschedule the meeting for next week.</t>
+        </is>
+      </c>
+      <c r="K306" s="14" t="inlineStr"/>
+      <c r="L306" s="36" t="inlineStr">
+        <is>
+          <t>समय बदलना</t>
+        </is>
+      </c>
+      <c r="M306" s="36" t="inlineStr">
+        <is>
+          <t>मीटिंग या काम को नए समय पर रखना।</t>
+        </is>
+      </c>
+      <c r="N306" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O306" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P306" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q306" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R306" s="37" t="inlineStr"/>
+      <c r="S306" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T306" s="39" t="inlineStr">
+        <is>
+          <t>s:reschedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B307" s="34" t="inlineStr">
+        <is>
+          <t>resign</t>
+        </is>
+      </c>
+      <c r="C307" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D307" s="14" t="inlineStr">
+        <is>
+          <t>To tell your employer you are leaving your job.</t>
+        </is>
+      </c>
+      <c r="E307" s="14" t="inlineStr">
+        <is>
+          <t>ri-ZYN</t>
+        </is>
+      </c>
+      <c r="F307" s="14" t="inlineStr">
+        <is>
+          <t>/rɪˈzaɪn/</t>
+        </is>
+      </c>
+      <c r="G307" s="14" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="H307" s="14" t="inlineStr">
+        <is>
+          <t>He resigned to start his own business.</t>
+        </is>
+      </c>
+      <c r="I307" s="14" t="inlineStr">
+        <is>
+          <t>Many people resign in January.</t>
+        </is>
+      </c>
+      <c r="J307" s="14" t="inlineStr">
+        <is>
+          <t>I will resign after I get the new offer.</t>
+        </is>
+      </c>
+      <c r="K307" s="14" t="inlineStr"/>
+      <c r="L307" s="36" t="inlineStr">
+        <is>
+          <t>इस्तीफ़ा देना</t>
+        </is>
+      </c>
+      <c r="M307" s="36" t="inlineStr">
+        <is>
+          <t>अपने नियोक्ता को बताना कि आप नौकरी छोड़ रहे हैं।</t>
+        </is>
+      </c>
+      <c r="N307" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O307" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P307" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q307" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R307" s="37" t="inlineStr"/>
+      <c r="S307" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T307" s="39" t="inlineStr">
+        <is>
+          <t>s:resign</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B308" s="34" t="inlineStr">
+        <is>
+          <t>roster</t>
+        </is>
+      </c>
+      <c r="C308" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D308" s="14" t="inlineStr">
+        <is>
+          <t>A list showing who works on which days and shifts.</t>
+        </is>
+      </c>
+      <c r="E308" s="14" t="inlineStr">
+        <is>
+          <t>ROS-ter</t>
+        </is>
+      </c>
+      <c r="F308" s="14" t="inlineStr">
+        <is>
+          <t>/ˈrɒstə/</t>
+        </is>
+      </c>
+      <c r="G308" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H308" s="14" t="inlineStr">
+        <is>
+          <t>My manager changed the roster.</t>
+        </is>
+      </c>
+      <c r="I308" s="14" t="inlineStr">
+        <is>
+          <t>The new roster is out.</t>
+        </is>
+      </c>
+      <c r="J308" s="14" t="inlineStr">
+        <is>
+          <t>I will check the roster for next month.</t>
+        </is>
+      </c>
+      <c r="K308" s="14" t="inlineStr"/>
+      <c r="L308" s="36" t="inlineStr">
+        <is>
+          <t>ड्यूटी सूची, रोस्टर</t>
+        </is>
+      </c>
+      <c r="M308" s="36" t="inlineStr">
+        <is>
+          <t>यह सूची कि कौन किस दिन और किस पारी में काम करेगा।</t>
+        </is>
+      </c>
+      <c r="N308" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O308" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P308" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q308" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R308" s="37" t="inlineStr"/>
+      <c r="S308" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T308" s="39" t="inlineStr">
+        <is>
+          <t>s:roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B309" s="34" t="inlineStr">
+        <is>
+          <t>salary</t>
+        </is>
+      </c>
+      <c r="C309" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D309" s="14" t="inlineStr">
+        <is>
+          <t>The fixed money you get for your job, usually every month.</t>
+        </is>
+      </c>
+      <c r="E309" s="14" t="inlineStr">
+        <is>
+          <t>SAL-uh-ree</t>
+        </is>
+      </c>
+      <c r="F309" s="14" t="inlineStr">
+        <is>
+          <t>/ˈsæləri/</t>
+        </is>
+      </c>
+      <c r="G309" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H309" s="14" t="inlineStr">
+        <is>
+          <t>Her salary went up last year.</t>
+        </is>
+      </c>
+      <c r="I309" s="14" t="inlineStr">
+        <is>
+          <t>The salary is paid monthly.</t>
+        </is>
+      </c>
+      <c r="J309" s="14" t="inlineStr">
+        <is>
+          <t>We will discuss salary in the next round.</t>
+        </is>
+      </c>
+      <c r="K309" s="14" t="inlineStr"/>
+      <c r="L309" s="36" t="inlineStr">
+        <is>
+          <t>वेतन, तनख्वाह</t>
+        </is>
+      </c>
+      <c r="M309" s="36" t="inlineStr">
+        <is>
+          <t>नौकरी के लिए हर महीने मिलने वाला तय पैसा।</t>
+        </is>
+      </c>
+      <c r="N309" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O309" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P309" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q309" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R309" s="37" t="inlineStr"/>
+      <c r="S309" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T309" s="39" t="inlineStr">
+        <is>
+          <t>s:salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B310" s="34" t="inlineStr">
+        <is>
+          <t>screen share</t>
+        </is>
+      </c>
+      <c r="C310" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D310" s="14" t="inlineStr">
+        <is>
+          <t>To show your computer screen to others on a call.</t>
+        </is>
+      </c>
+      <c r="E310" s="14" t="inlineStr">
+        <is>
+          <t>SKREEN shair</t>
+        </is>
+      </c>
+      <c r="F310" s="14" t="inlineStr">
+        <is>
+          <t>/skriːn ʃeə/</t>
+        </is>
+      </c>
+      <c r="G310" s="14" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="H310" s="14" t="inlineStr">
+        <is>
+          <t>He screen shared his dashboard.</t>
+        </is>
+      </c>
+      <c r="I310" s="14" t="inlineStr">
+        <is>
+          <t>Can you screen share the report?</t>
+        </is>
+      </c>
+      <c r="J310" s="14" t="inlineStr">
+        <is>
+          <t>I will screen share the steps.</t>
+        </is>
+      </c>
+      <c r="K310" s="14" t="inlineStr"/>
+      <c r="L310" s="36" t="inlineStr">
+        <is>
+          <t>स्क्रीन शेयर करना</t>
+        </is>
+      </c>
+      <c r="M310" s="36" t="inlineStr">
+        <is>
+          <t>कॉल पर अपनी कंप्यूटर स्क्रीन दूसरों को दिखाना।</t>
+        </is>
+      </c>
+      <c r="N310" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O310" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P310" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q310" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R310" s="37" t="inlineStr"/>
+      <c r="S310" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T310" s="39" t="inlineStr">
+        <is>
+          <t>s:screen-share</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B311" s="34" t="inlineStr">
+        <is>
+          <t>shift</t>
+        </is>
+      </c>
+      <c r="C311" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" s="14" t="inlineStr">
+        <is>
+          <t>A set block of working hours, like morning or night.</t>
+        </is>
+      </c>
+      <c r="E311" s="14" t="inlineStr">
+        <is>
+          <t>shift</t>
+        </is>
+      </c>
+      <c r="F311" s="14" t="inlineStr">
+        <is>
+          <t>/ʃɪft/</t>
+        </is>
+      </c>
+      <c r="G311" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H311" s="14" t="inlineStr">
+        <is>
+          <t>Her shift ended late.</t>
+        </is>
+      </c>
+      <c r="I311" s="14" t="inlineStr">
+        <is>
+          <t>My shift starts at 8 a.m.</t>
+        </is>
+      </c>
+      <c r="J311" s="14" t="inlineStr">
+        <is>
+          <t>I will be on the night shift next week.</t>
+        </is>
+      </c>
+      <c r="K311" s="14" t="inlineStr"/>
+      <c r="L311" s="36" t="inlineStr">
+        <is>
+          <t>पारी, शिफ्ट</t>
+        </is>
+      </c>
+      <c r="M311" s="36" t="inlineStr">
+        <is>
+          <t>काम के तय घंटे, जैसे सुबह या रात की पारी।</t>
+        </is>
+      </c>
+      <c r="N311" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O311" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P311" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q311" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R311" s="37" t="inlineStr"/>
+      <c r="S311" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T311" s="39" t="inlineStr">
+        <is>
+          <t>s:shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B312" s="34" t="inlineStr">
+        <is>
+          <t>sick leave</t>
+        </is>
+      </c>
+      <c r="C312" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D312" s="14" t="inlineStr">
+        <is>
+          <t>Time off work because you are ill. One day off is a sick day.</t>
+        </is>
+      </c>
+      <c r="E312" s="14" t="inlineStr">
+        <is>
+          <t>sik LEEV</t>
+        </is>
+      </c>
+      <c r="F312" s="14" t="inlineStr">
+        <is>
+          <t>/sɪk liːv/</t>
+        </is>
+      </c>
+      <c r="G312" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H312" s="14" t="inlineStr">
+        <is>
+          <t>He took two sick days last week.</t>
+        </is>
+      </c>
+      <c r="I312" s="14" t="inlineStr">
+        <is>
+          <t>I'm on sick leave today.</t>
+        </is>
+      </c>
+      <c r="J312" s="14" t="inlineStr">
+        <is>
+          <t>You will need a doctor's note for long sick leave.</t>
+        </is>
+      </c>
+      <c r="K312" s="14" t="inlineStr"/>
+      <c r="L312" s="36" t="inlineStr">
+        <is>
+          <t>बीमारी की छुट्टी</t>
+        </is>
+      </c>
+      <c r="M312" s="36" t="inlineStr">
+        <is>
+          <t>बीमार होने पर काम से ली गई छुट्टी।</t>
+        </is>
+      </c>
+      <c r="N312" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O312" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P312" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q312" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R312" s="37" t="inlineStr"/>
+      <c r="S312" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T312" s="39" t="inlineStr">
+        <is>
+          <t>s:sick-leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B313" s="34" t="inlineStr">
+        <is>
+          <t>take notes</t>
+        </is>
+      </c>
+      <c r="C313" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D313" s="14" t="inlineStr">
+        <is>
+          <t>To write down the main points while someone speaks.</t>
+        </is>
+      </c>
+      <c r="E313" s="14" t="inlineStr">
+        <is>
+          <t>tayk NOHTS</t>
+        </is>
+      </c>
+      <c r="F313" s="14" t="inlineStr">
+        <is>
+          <t>/teɪk nəʊts/</t>
+        </is>
+      </c>
+      <c r="G313" s="14" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="H313" s="14" t="inlineStr">
+        <is>
+          <t>She took notes for the whole team.</t>
+        </is>
+      </c>
+      <c r="I313" s="14" t="inlineStr">
+        <is>
+          <t>I take notes in every meeting.</t>
+        </is>
+      </c>
+      <c r="J313" s="14" t="inlineStr">
+        <is>
+          <t>Who will take notes today?</t>
+        </is>
+      </c>
+      <c r="K313" s="14" t="inlineStr"/>
+      <c r="L313" s="36" t="inlineStr">
+        <is>
+          <t>नोट्स लिखना</t>
+        </is>
+      </c>
+      <c r="M313" s="36" t="inlineStr">
+        <is>
+          <t>बातचीत के मुख्य बिंदु लिख लेना।</t>
+        </is>
+      </c>
+      <c r="N313" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O313" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P313" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q313" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R313" s="37" t="inlineStr"/>
+      <c r="S313" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T313" s="39" t="inlineStr">
+        <is>
+          <t>s:take-notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B314" s="34" t="inlineStr">
+        <is>
+          <t>team lead</t>
+        </is>
+      </c>
+      <c r="C314" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D314" s="14" t="inlineStr">
+        <is>
+          <t>The person who guides a small team day to day.</t>
+        </is>
+      </c>
+      <c r="E314" s="14" t="inlineStr">
+        <is>
+          <t>teem LEED</t>
+        </is>
+      </c>
+      <c r="F314" s="14" t="inlineStr">
+        <is>
+          <t>/tiːm liːd/</t>
+        </is>
+      </c>
+      <c r="G314" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H314" s="14" t="inlineStr">
+        <is>
+          <t>The team lead ran the morning huddle.</t>
+        </is>
+      </c>
+      <c r="I314" s="14" t="inlineStr">
+        <is>
+          <t>My team lead checks my tickets.</t>
+        </is>
+      </c>
+      <c r="J314" s="14" t="inlineStr">
+        <is>
+          <t>The team lead will update the roster.</t>
+        </is>
+      </c>
+      <c r="K314" s="14" t="inlineStr"/>
+      <c r="L314" s="36" t="inlineStr">
+        <is>
+          <t>टीम प्रमुख</t>
+        </is>
+      </c>
+      <c r="M314" s="36" t="inlineStr">
+        <is>
+          <t>वह व्यक्ति जो रोज़ एक छोटी टीम का मार्गदर्शन करता है।</t>
+        </is>
+      </c>
+      <c r="N314" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O314" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P314" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q314" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R314" s="37" t="inlineStr"/>
+      <c r="S314" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T314" s="39" t="inlineStr">
+        <is>
+          <t>s:team-lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B315" s="34" t="inlineStr">
+        <is>
+          <t>termination</t>
+        </is>
+      </c>
+      <c r="C315" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D315" s="14" t="inlineStr">
+        <is>
+          <t>The end of someone's job, decided by the company.</t>
+        </is>
+      </c>
+      <c r="E315" s="14" t="inlineStr">
+        <is>
+          <t>tur-mi-NAY-shun</t>
+        </is>
+      </c>
+      <c r="F315" s="14" t="inlineStr">
+        <is>
+          <t>/ˌtɜːmɪˈneɪʃn/</t>
+        </is>
+      </c>
+      <c r="G315" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H315" s="14" t="inlineStr">
+        <is>
+          <t>His termination was a surprise.</t>
+        </is>
+      </c>
+      <c r="I315" s="14" t="inlineStr">
+        <is>
+          <t>Termination needs a written reason.</t>
+        </is>
+      </c>
+      <c r="J315" s="14" t="inlineStr">
+        <is>
+          <t>Breaking the rules will lead to termination.</t>
+        </is>
+      </c>
+      <c r="K315" s="14" t="inlineStr"/>
+      <c r="L315" s="36" t="inlineStr">
+        <is>
+          <t>बर्खास्तगी, नौकरी समाप्ति</t>
+        </is>
+      </c>
+      <c r="M315" s="36" t="inlineStr">
+        <is>
+          <t>कंपनी द्वारा किसी की नौकरी खत्म करना।</t>
+        </is>
+      </c>
+      <c r="N315" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O315" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P315" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q315" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R315" s="37" t="inlineStr"/>
+      <c r="S315" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T315" s="39" t="inlineStr">
+        <is>
+          <t>s:termination</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B316" s="34" t="inlineStr">
+        <is>
+          <t>timesheet</t>
+        </is>
+      </c>
+      <c r="C316" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D316" s="14" t="inlineStr">
+        <is>
+          <t>A record of the hours you worked.</t>
+        </is>
+      </c>
+      <c r="E316" s="14" t="inlineStr">
+        <is>
+          <t>TYM-sheet</t>
+        </is>
+      </c>
+      <c r="F316" s="14" t="inlineStr">
+        <is>
+          <t>/ˈtaɪmʃiːt/</t>
+        </is>
+      </c>
+      <c r="G316" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H316" s="14" t="inlineStr">
+        <is>
+          <t>He forgot to submit his timesheet.</t>
+        </is>
+      </c>
+      <c r="I316" s="14" t="inlineStr">
+        <is>
+          <t>I fill in my timesheet every Friday.</t>
+        </is>
+      </c>
+      <c r="J316" s="14" t="inlineStr">
+        <is>
+          <t>Your overtime will show on the timesheet.</t>
+        </is>
+      </c>
+      <c r="K316" s="14" t="inlineStr"/>
+      <c r="L316" s="36" t="inlineStr">
+        <is>
+          <t>समय-पत्रक</t>
+        </is>
+      </c>
+      <c r="M316" s="36" t="inlineStr">
+        <is>
+          <t>आपके काम किए गए घंटों का रिकॉर्ड।</t>
+        </is>
+      </c>
+      <c r="N316" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O316" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P316" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q316" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R316" s="37" t="inlineStr"/>
+      <c r="S316" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T316" s="39" t="inlineStr">
+        <is>
+          <t>s:timesheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B317" s="34" t="inlineStr">
+        <is>
+          <t>trainee</t>
+        </is>
+      </c>
+      <c r="C317" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D317" s="14" t="inlineStr">
+        <is>
+          <t>A new person who is learning the job.</t>
+        </is>
+      </c>
+      <c r="E317" s="14" t="inlineStr">
+        <is>
+          <t>tray-NEE</t>
+        </is>
+      </c>
+      <c r="F317" s="14" t="inlineStr">
+        <is>
+          <t>/ˌtreɪˈniː/</t>
+        </is>
+      </c>
+      <c r="G317" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H317" s="14" t="inlineStr">
+        <is>
+          <t>I was a trainee last year.</t>
+        </is>
+      </c>
+      <c r="I317" s="14" t="inlineStr">
+        <is>
+          <t>Each trainee sits with a senior agent.</t>
+        </is>
+      </c>
+      <c r="J317" s="14" t="inlineStr">
+        <is>
+          <t>The trainees will take calls next week.</t>
+        </is>
+      </c>
+      <c r="K317" s="14" t="inlineStr"/>
+      <c r="L317" s="36" t="inlineStr">
+        <is>
+          <t>प्रशिक्षु</t>
+        </is>
+      </c>
+      <c r="M317" s="36" t="inlineStr">
+        <is>
+          <t>वह नया व्यक्ति जो काम सीख रहा है।</t>
+        </is>
+      </c>
+      <c r="N317" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O317" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P317" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q317" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R317" s="37" t="inlineStr"/>
+      <c r="S317" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T317" s="39" t="inlineStr">
+        <is>
+          <t>s:trainee</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B318" s="34" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="C318" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D318" s="14" t="inlineStr">
+        <is>
+          <t>The person who teaches new staff how to do the job.</t>
+        </is>
+      </c>
+      <c r="E318" s="14" t="inlineStr">
+        <is>
+          <t>TRAY-ner</t>
+        </is>
+      </c>
+      <c r="F318" s="14" t="inlineStr">
+        <is>
+          <t>/ˈtreɪnə/</t>
+        </is>
+      </c>
+      <c r="G318" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H318" s="14" t="inlineStr">
+        <is>
+          <t>The trainer gave us a quiz.</t>
+        </is>
+      </c>
+      <c r="I318" s="14" t="inlineStr">
+        <is>
+          <t>Our trainer explains each tool.</t>
+        </is>
+      </c>
+      <c r="J318" s="14" t="inlineStr">
+        <is>
+          <t>Your trainer will meet you at nine.</t>
+        </is>
+      </c>
+      <c r="K318" s="14" t="inlineStr"/>
+      <c r="L318" s="36" t="inlineStr">
+        <is>
+          <t>प्रशिक्षक, ट्रेनर</t>
+        </is>
+      </c>
+      <c r="M318" s="36" t="inlineStr">
+        <is>
+          <t>वह व्यक्ति जो नए कर्मचारियों को काम सिखाता है।</t>
+        </is>
+      </c>
+      <c r="N318" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O318" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P318" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q318" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R318" s="37" t="inlineStr"/>
+      <c r="S318" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T318" s="39" t="inlineStr">
+        <is>
+          <t>s:trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B319" s="34" t="inlineStr">
+        <is>
+          <t>training period</t>
+        </is>
+      </c>
+      <c r="C319" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D319" s="14" t="inlineStr">
+        <is>
+          <t>The time when new staff learn the job before working alone.</t>
+        </is>
+      </c>
+      <c r="E319" s="14" t="inlineStr">
+        <is>
+          <t>TRAY-ning PEER-ee-ud</t>
+        </is>
+      </c>
+      <c r="F319" s="14" t="inlineStr">
+        <is>
+          <t>/ˈtreɪnɪŋ ˈpɪəriəd/</t>
+        </is>
+      </c>
+      <c r="G319" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H319" s="14" t="inlineStr">
+        <is>
+          <t>I learned a lot in my training period.</t>
+        </is>
+      </c>
+      <c r="I319" s="14" t="inlineStr">
+        <is>
+          <t>The training period lasts four weeks.</t>
+        </is>
+      </c>
+      <c r="J319" s="14" t="inlineStr">
+        <is>
+          <t>You will be paid during the training period.</t>
+        </is>
+      </c>
+      <c r="K319" s="14" t="inlineStr"/>
+      <c r="L319" s="36" t="inlineStr">
+        <is>
+          <t>प्रशिक्षण अवधि</t>
+        </is>
+      </c>
+      <c r="M319" s="36" t="inlineStr">
+        <is>
+          <t>वह समय जब नए कर्मचारी अकेले काम करने से पहले काम सीखते हैं।</t>
+        </is>
+      </c>
+      <c r="N319" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O319" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P319" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q319" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R319" s="37" t="inlineStr"/>
+      <c r="S319" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T319" s="39" t="inlineStr">
+        <is>
+          <t>s:training-period</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B320" s="34" t="inlineStr">
+        <is>
+          <t>unpaid leave</t>
+        </is>
+      </c>
+      <c r="C320" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D320" s="14" t="inlineStr">
+        <is>
+          <t>Time off work without pay.</t>
+        </is>
+      </c>
+      <c r="E320" s="14" t="inlineStr">
+        <is>
+          <t>un-PAYD leev</t>
+        </is>
+      </c>
+      <c r="F320" s="14" t="inlineStr">
+        <is>
+          <t>/ʌnˈpeɪd liːv/</t>
+        </is>
+      </c>
+      <c r="G320" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H320" s="14" t="inlineStr">
+        <is>
+          <t>She took unpaid leave to move house.</t>
+        </is>
+      </c>
+      <c r="I320" s="14" t="inlineStr">
+        <is>
+          <t>He is asking for a week of unpaid leave.</t>
+        </is>
+      </c>
+      <c r="J320" s="14" t="inlineStr">
+        <is>
+          <t>Unpaid leave will not affect your contract.</t>
+        </is>
+      </c>
+      <c r="K320" s="14" t="inlineStr"/>
+      <c r="L320" s="36" t="inlineStr">
+        <is>
+          <t>बिना वेतन की छुट्टी</t>
+        </is>
+      </c>
+      <c r="M320" s="36" t="inlineStr">
+        <is>
+          <t>ऐसी छुट्टी जिसमें वेतन नहीं मिलता।</t>
+        </is>
+      </c>
+      <c r="N320" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O320" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P320" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q320" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R320" s="37" t="inlineStr"/>
+      <c r="S320" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T320" s="39" t="inlineStr">
+        <is>
+          <t>s:unpaid-leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B321" s="34" t="inlineStr">
+        <is>
+          <t>video call</t>
+        </is>
+      </c>
+      <c r="C321" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D321" s="14" t="inlineStr">
+        <is>
+          <t>A call where people can see and hear each other.</t>
+        </is>
+      </c>
+      <c r="E321" s="14" t="inlineStr">
+        <is>
+          <t>VID-ee-oh kawl</t>
+        </is>
+      </c>
+      <c r="F321" s="14" t="inlineStr">
+        <is>
+          <t>/ˈvɪdiəʊ kɔːl/</t>
+        </is>
+      </c>
+      <c r="G321" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H321" s="14" t="inlineStr">
+        <is>
+          <t>We solved it on a video call.</t>
+        </is>
+      </c>
+      <c r="I321" s="14" t="inlineStr">
+        <is>
+          <t>I prefer a video call to a long email.</t>
+        </is>
+      </c>
+      <c r="J321" s="14" t="inlineStr">
+        <is>
+          <t>We will do a video call tomorrow.</t>
+        </is>
+      </c>
+      <c r="K321" s="14" t="inlineStr"/>
+      <c r="L321" s="36" t="inlineStr">
+        <is>
+          <t>वीडियो कॉल</t>
+        </is>
+      </c>
+      <c r="M321" s="36" t="inlineStr">
+        <is>
+          <t>ऐसी कॉल जिसमें लोग एक दूसरे को देख और सुन सकते हैं।</t>
+        </is>
+      </c>
+      <c r="N321" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O321" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P321" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q321" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R321" s="37" t="inlineStr"/>
+      <c r="S321" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T321" s="39" t="inlineStr">
+        <is>
+          <t>s:video-call</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B322" s="34" t="inlineStr">
+        <is>
+          <t>weekend shift</t>
+        </is>
+      </c>
+      <c r="C322" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D322" s="14" t="inlineStr">
+        <is>
+          <t>Working hours on Saturday or Sunday.</t>
+        </is>
+      </c>
+      <c r="E322" s="14" t="inlineStr">
+        <is>
+          <t>week-END shift</t>
+        </is>
+      </c>
+      <c r="F322" s="14" t="inlineStr">
+        <is>
+          <t>/ˌwiːkˈend ʃɪft/</t>
+        </is>
+      </c>
+      <c r="G322" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H322" s="14" t="inlineStr">
+        <is>
+          <t>She covered my weekend shift.</t>
+        </is>
+      </c>
+      <c r="I322" s="14" t="inlineStr">
+        <is>
+          <t>I work a weekend shift once a month.</t>
+        </is>
+      </c>
+      <c r="J322" s="14" t="inlineStr">
+        <is>
+          <t>I will swap my weekend shift with Ana.</t>
+        </is>
+      </c>
+      <c r="K322" s="14" t="inlineStr"/>
+      <c r="L322" s="36" t="inlineStr">
+        <is>
+          <t>सप्ताहांत की पारी</t>
+        </is>
+      </c>
+      <c r="M322" s="36" t="inlineStr">
+        <is>
+          <t>शनिवार या रविवार को काम के घंटे।</t>
+        </is>
+      </c>
+      <c r="N322" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O322" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P322" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q322" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R322" s="37" t="inlineStr"/>
+      <c r="S322" s="39" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="T322" s="39" t="inlineStr">
+        <is>
+          <t>s:weekend-shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B323" s="34" t="inlineStr">
+        <is>
+          <t>work from home</t>
+        </is>
+      </c>
+      <c r="C323" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D323" s="14" t="inlineStr">
+        <is>
+          <t>To do your job from your house instead of the office.</t>
+        </is>
+      </c>
+      <c r="E323" s="14" t="inlineStr">
+        <is>
+          <t>wurk frum HOHM</t>
+        </is>
+      </c>
+      <c r="F323" s="14" t="inlineStr">
+        <is>
+          <t>/wɜːk frəm həʊm/</t>
+        </is>
+      </c>
+      <c r="G323" s="14" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="H323" s="14" t="inlineStr">
+        <is>
+          <t>We worked from home during the storm.</t>
+        </is>
+      </c>
+      <c r="I323" s="14" t="inlineStr">
+        <is>
+          <t>I work from home on Fridays.</t>
+        </is>
+      </c>
+      <c r="J323" s="14" t="inlineStr">
+        <is>
+          <t>You will be able to work from home after training.</t>
+        </is>
+      </c>
+      <c r="K323" s="14" t="inlineStr"/>
+      <c r="L323" s="36" t="inlineStr">
+        <is>
+          <t>घर से काम करना</t>
+        </is>
+      </c>
+      <c r="M323" s="36" t="inlineStr">
+        <is>
+          <t>ऑफिस की जगह घर से नौकरी का काम करना।</t>
+        </is>
+      </c>
+      <c r="N323" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O323" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P323" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q323" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R323" s="37" t="inlineStr"/>
+      <c r="S323" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T323" s="39" t="inlineStr">
+        <is>
+          <t>s:work-from-home</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="33" t="inlineStr">
+        <is>
+          <t>Workplace and HR</t>
+        </is>
+      </c>
+      <c r="B324" s="34" t="inlineStr">
+        <is>
+          <t>Zoom call</t>
+        </is>
+      </c>
+      <c r="C324" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D324" s="14" t="inlineStr">
+        <is>
+          <t>A video meeting on the Zoom app.</t>
+        </is>
+      </c>
+      <c r="E324" s="14" t="inlineStr">
+        <is>
+          <t>zoom KAWL</t>
+        </is>
+      </c>
+      <c r="F324" s="14" t="inlineStr">
+        <is>
+          <t>/zuːm kɔːl/</t>
+        </is>
+      </c>
+      <c r="G324" s="14" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="H324" s="14" t="inlineStr">
+        <is>
+          <t>We had a quick Zoom call with the client.</t>
+        </is>
+      </c>
+      <c r="I324" s="14" t="inlineStr">
+        <is>
+          <t>Our weekly Zoom call starts at ten.</t>
+        </is>
+      </c>
+      <c r="J324" s="14" t="inlineStr">
+        <is>
+          <t>I will set up a Zoom call for Friday.</t>
+        </is>
+      </c>
+      <c r="K324" s="14" t="inlineStr"/>
+      <c r="L324" s="36" t="inlineStr">
+        <is>
+          <t>ज़ूम कॉल (वीडियो मीटिंग)</t>
+        </is>
+      </c>
+      <c r="M324" s="36" t="inlineStr">
+        <is>
+          <t>ज़ूम ऐप पर होने वाली वीडियो मीटिंग।</t>
+        </is>
+      </c>
+      <c r="N324" s="37" t="inlineStr">
+        <is>
+          <t>Starter pack</t>
+        </is>
+      </c>
+      <c r="O324" s="38" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P324" s="37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="Q324" s="37" t="inlineStr">
+        <is>
+          <t>WordNest</t>
+        </is>
+      </c>
+      <c r="R324" s="37" t="inlineStr"/>
+      <c r="S324" s="39" t="inlineStr">
+        <is>
+          <t>hr,corp</t>
+        </is>
+      </c>
+      <c r="T324" s="39" t="inlineStr">
         <is>
           <t>s:zoom-call</t>
         </is>
